--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Pep-Move\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B9A9F239-6B5F-4301-8811-C60FA73E936D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{46778B0F-05E1-4A20-BAF0-70C00B814C2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="93">
   <si>
     <t>Company Name</t>
   </si>
@@ -691,7 +691,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="D1:M7172"/>
+  <dimension ref="D1:M7173"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
@@ -1089,10 +1089,10 @@
         <v>16</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J15" s="2">
-        <v>0</v>
+        <v>6.8865740740740745E-3</v>
       </c>
       <c r="K15" s="1">
         <v>46212.758333333331</v>
@@ -1321,10 +1321,10 @@
         <v>16</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J23" s="2">
-        <v>0</v>
+        <v>3.2407407407407406E-4</v>
       </c>
       <c r="K23" s="1">
         <v>46212.762499999997</v>
@@ -1337,32 +1337,12 @@
       </c>
     </row>
     <row r="24" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="D24" t="s">
-        <v>18</v>
-      </c>
-      <c r="E24">
-        <v>5721</v>
-      </c>
-      <c r="F24" t="s">
-        <v>38</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="J24" s="2">
-        <v>0</v>
-      </c>
-      <c r="K24" s="1">
-        <v>46212.763194444444</v>
-      </c>
-      <c r="L24">
-        <v>0</v>
-      </c>
+      <c r="H24" s="2"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="1"/>
       <c r="M24" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" spans="4:13" x14ac:dyDescent="0.3">
@@ -1370,22 +1350,22 @@
         <v>18</v>
       </c>
       <c r="E25">
-        <v>5680</v>
+        <v>5721</v>
       </c>
       <c r="F25" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J25" s="2">
-        <v>1.6203703703703703E-4</v>
+        <v>0</v>
       </c>
       <c r="K25" s="1">
-        <v>46212.763888888891</v>
+        <v>46212.763194444444</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -1395,41 +1375,41 @@
       </c>
     </row>
     <row r="26" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H26" s="2"/>
-      <c r="I26" s="1"/>
-      <c r="J26" s="2"/>
-      <c r="K26" s="1"/>
+      <c r="D26" t="s">
+        <v>18</v>
+      </c>
+      <c r="E26">
+        <v>5680</v>
+      </c>
+      <c r="F26" t="s">
+        <v>39</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J26" s="2">
+        <v>1.6203703703703703E-4</v>
+      </c>
+      <c r="K26" s="1">
+        <v>46212.763888888891</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
       <c r="M26" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="H27" s="2"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="1"/>
+      <c r="M27" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="27" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="D27" t="s">
-        <v>18</v>
-      </c>
-      <c r="E27">
-        <v>5689</v>
-      </c>
-      <c r="F27" t="s">
-        <v>40</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="J27" s="2">
-        <v>0</v>
-      </c>
-      <c r="K27" s="1">
-        <v>46212.76458333333</v>
-      </c>
-      <c r="L27">
-        <v>0</v>
-      </c>
-      <c r="M27" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="28" spans="4:13" x14ac:dyDescent="0.3">
@@ -1437,10 +1417,10 @@
         <v>18</v>
       </c>
       <c r="E28">
-        <v>5687</v>
+        <v>5689</v>
       </c>
       <c r="F28" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>16</v>
@@ -1449,7 +1429,7 @@
         <v>10</v>
       </c>
       <c r="J28" s="2">
-        <v>8.7037037037037031E-3</v>
+        <v>9.6759259259259264E-3</v>
       </c>
       <c r="K28" s="1">
         <v>46212.76458333333</v>
@@ -1466,22 +1446,22 @@
         <v>18</v>
       </c>
       <c r="E29">
-        <v>5727</v>
+        <v>5687</v>
       </c>
       <c r="F29" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J29" s="2">
-        <v>0</v>
+        <v>8.7037037037037031E-3</v>
       </c>
       <c r="K29" s="1">
-        <v>46212.765277777777</v>
+        <v>46212.76458333333</v>
       </c>
       <c r="L29">
         <v>0</v>
@@ -1495,10 +1475,10 @@
         <v>18</v>
       </c>
       <c r="E30">
-        <v>5725</v>
+        <v>5727</v>
       </c>
       <c r="F30" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>16</v>
@@ -1510,7 +1490,7 @@
         <v>0</v>
       </c>
       <c r="K30" s="1">
-        <v>46212.765972222223</v>
+        <v>46212.765277777777</v>
       </c>
       <c r="L30">
         <v>0</v>
@@ -1524,10 +1504,10 @@
         <v>18</v>
       </c>
       <c r="E31">
-        <v>5709</v>
+        <v>5725</v>
       </c>
       <c r="F31" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>16</v>
@@ -1553,22 +1533,22 @@
         <v>18</v>
       </c>
       <c r="E32">
-        <v>5736</v>
+        <v>5709</v>
       </c>
       <c r="F32" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>16</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J32" s="2">
-        <v>6.851851851851852E-3</v>
+        <v>0</v>
       </c>
       <c r="K32" s="1">
-        <v>46212.76666666667</v>
+        <v>46212.765972222223</v>
       </c>
       <c r="L32">
         <v>0</v>
@@ -1582,22 +1562,22 @@
         <v>18</v>
       </c>
       <c r="E33">
-        <v>5682</v>
+        <v>5736</v>
       </c>
       <c r="F33" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>16</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J33" s="2">
-        <v>0</v>
+        <v>6.851851851851852E-3</v>
       </c>
       <c r="K33" s="1">
-        <v>46212.767361111109</v>
+        <v>46212.76666666667</v>
       </c>
       <c r="L33">
         <v>0</v>
@@ -1611,10 +1591,10 @@
         <v>18</v>
       </c>
       <c r="E34">
-        <v>5729</v>
+        <v>5682</v>
       </c>
       <c r="F34" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>16</v>
@@ -1623,10 +1603,10 @@
         <v>10</v>
       </c>
       <c r="J34" s="2">
-        <v>6.8171296296296296E-3</v>
+        <v>7.3379629629629628E-3</v>
       </c>
       <c r="K34" s="1">
-        <v>46212.768055555556</v>
+        <v>46212.767361111109</v>
       </c>
       <c r="L34">
         <v>0</v>
@@ -1640,19 +1620,19 @@
         <v>18</v>
       </c>
       <c r="E35">
-        <v>5696</v>
+        <v>5729</v>
       </c>
       <c r="F35" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>16</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J35" s="2">
-        <v>0</v>
+        <v>6.8171296296296296E-3</v>
       </c>
       <c r="K35" s="1">
         <v>46212.768055555556</v>
@@ -1669,10 +1649,10 @@
         <v>18</v>
       </c>
       <c r="E36">
-        <v>5716</v>
+        <v>5696</v>
       </c>
       <c r="F36" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>16</v>
@@ -1684,7 +1664,7 @@
         <v>0</v>
       </c>
       <c r="K36" s="1">
-        <v>46212.768750000003</v>
+        <v>46212.768055555556</v>
       </c>
       <c r="L36">
         <v>0</v>
@@ -1698,10 +1678,10 @@
         <v>18</v>
       </c>
       <c r="E37">
-        <v>5720</v>
+        <v>5716</v>
       </c>
       <c r="F37" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>16</v>
@@ -1713,7 +1693,7 @@
         <v>0</v>
       </c>
       <c r="K37" s="1">
-        <v>46212.769444444442</v>
+        <v>46212.768750000003</v>
       </c>
       <c r="L37">
         <v>0</v>
@@ -1727,22 +1707,22 @@
         <v>18</v>
       </c>
       <c r="E38">
-        <v>5679</v>
+        <v>5720</v>
       </c>
       <c r="F38" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>16</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J38" s="2">
         <v>0</v>
       </c>
       <c r="K38" s="1">
-        <v>46212.770138888889</v>
+        <v>46212.769444444442</v>
       </c>
       <c r="L38">
         <v>0</v>
@@ -1752,41 +1732,41 @@
       </c>
     </row>
     <row r="39" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H39" s="2"/>
-      <c r="I39" s="1"/>
-      <c r="J39" s="2"/>
-      <c r="K39" s="1"/>
+      <c r="D39" t="s">
+        <v>18</v>
+      </c>
+      <c r="E39">
+        <v>5679</v>
+      </c>
+      <c r="F39" t="s">
+        <v>51</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J39" s="2">
+        <v>0</v>
+      </c>
+      <c r="K39" s="1">
+        <v>46212.770138888889</v>
+      </c>
+      <c r="L39">
+        <v>0</v>
+      </c>
       <c r="M39" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="H40" s="2"/>
+      <c r="I40" s="1"/>
+      <c r="J40" s="2"/>
+      <c r="K40" s="1"/>
+      <c r="M40" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="40" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="D40" t="s">
-        <v>18</v>
-      </c>
-      <c r="E40">
-        <v>5711</v>
-      </c>
-      <c r="F40" t="s">
-        <v>52</v>
-      </c>
-      <c r="H40" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I40" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="J40" s="2">
-        <v>0</v>
-      </c>
-      <c r="K40" s="1">
-        <v>46212.770138888889</v>
-      </c>
-      <c r="L40">
-        <v>0</v>
-      </c>
-      <c r="M40" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="41" spans="4:13" x14ac:dyDescent="0.3">
@@ -1794,10 +1774,10 @@
         <v>18</v>
       </c>
       <c r="E41">
-        <v>5732</v>
+        <v>5711</v>
       </c>
       <c r="F41" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>16</v>
@@ -1809,7 +1789,7 @@
         <v>0</v>
       </c>
       <c r="K41" s="1">
-        <v>46212.770833333336</v>
+        <v>46212.770138888889</v>
       </c>
       <c r="L41">
         <v>0</v>
@@ -1823,22 +1803,22 @@
         <v>18</v>
       </c>
       <c r="E42">
-        <v>5739</v>
+        <v>5732</v>
       </c>
       <c r="F42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>16</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J42" s="2">
-        <v>1.273148148148148E-4</v>
+        <v>0</v>
       </c>
       <c r="K42" s="1">
-        <v>46212.771527777775</v>
+        <v>46212.770833333336</v>
       </c>
       <c r="L42">
         <v>0</v>
@@ -1848,41 +1828,41 @@
       </c>
     </row>
     <row r="43" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H43" s="2"/>
-      <c r="I43" s="1"/>
-      <c r="J43" s="2"/>
-      <c r="K43" s="1"/>
+      <c r="D43" t="s">
+        <v>18</v>
+      </c>
+      <c r="E43">
+        <v>5739</v>
+      </c>
+      <c r="F43" t="s">
+        <v>54</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J43" s="2">
+        <v>1.273148148148148E-4</v>
+      </c>
+      <c r="K43" s="1">
+        <v>46212.771527777775</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
       <c r="M43" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="44" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="H44" s="2"/>
+      <c r="I44" s="1"/>
+      <c r="J44" s="2"/>
+      <c r="K44" s="1"/>
+      <c r="M44" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="44" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="D44" t="s">
-        <v>18</v>
-      </c>
-      <c r="E44">
-        <v>5710</v>
-      </c>
-      <c r="F44" t="s">
-        <v>55</v>
-      </c>
-      <c r="H44" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I44" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="J44" s="2">
-        <v>0</v>
-      </c>
-      <c r="K44" s="1">
-        <v>46212.772222222222</v>
-      </c>
-      <c r="L44">
-        <v>0</v>
-      </c>
-      <c r="M44" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="45" spans="4:13" x14ac:dyDescent="0.3">
@@ -1890,10 +1870,10 @@
         <v>18</v>
       </c>
       <c r="E45">
-        <v>5746</v>
+        <v>5710</v>
       </c>
       <c r="F45" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>16</v>
@@ -1919,22 +1899,22 @@
         <v>18</v>
       </c>
       <c r="E46">
-        <v>5702</v>
+        <v>5746</v>
       </c>
       <c r="F46" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>16</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J46" s="2">
         <v>0</v>
       </c>
       <c r="K46" s="1">
-        <v>46212.772916666669</v>
+        <v>46212.772222222222</v>
       </c>
       <c r="L46">
         <v>0</v>
@@ -1944,41 +1924,41 @@
       </c>
     </row>
     <row r="47" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H47" s="2"/>
-      <c r="I47" s="1"/>
-      <c r="J47" s="2"/>
-      <c r="K47" s="1"/>
+      <c r="D47" t="s">
+        <v>18</v>
+      </c>
+      <c r="E47">
+        <v>5702</v>
+      </c>
+      <c r="F47" t="s">
+        <v>57</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J47" s="2">
+        <v>0</v>
+      </c>
+      <c r="K47" s="1">
+        <v>46212.772916666669</v>
+      </c>
+      <c r="L47">
+        <v>0</v>
+      </c>
       <c r="M47" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="48" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="H48" s="2"/>
+      <c r="I48" s="1"/>
+      <c r="J48" s="2"/>
+      <c r="K48" s="1"/>
+      <c r="M48" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="48" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="D48" t="s">
-        <v>18</v>
-      </c>
-      <c r="E48">
-        <v>5728</v>
-      </c>
-      <c r="F48" t="s">
-        <v>58</v>
-      </c>
-      <c r="H48" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I48" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="J48" s="2">
-        <v>0</v>
-      </c>
-      <c r="K48" s="1">
-        <v>46212.773611111108</v>
-      </c>
-      <c r="L48">
-        <v>0</v>
-      </c>
-      <c r="M48" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="49" spans="4:13" x14ac:dyDescent="0.3">
@@ -1986,10 +1966,10 @@
         <v>18</v>
       </c>
       <c r="E49">
-        <v>5683</v>
+        <v>5728</v>
       </c>
       <c r="F49" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>16</v>
@@ -2001,7 +1981,7 @@
         <v>0</v>
       </c>
       <c r="K49" s="1">
-        <v>46212.774305555555</v>
+        <v>46212.773611111108</v>
       </c>
       <c r="L49">
         <v>0</v>
@@ -2015,10 +1995,10 @@
         <v>18</v>
       </c>
       <c r="E50">
-        <v>5745</v>
+        <v>5683</v>
       </c>
       <c r="F50" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>16</v>
@@ -2044,10 +2024,10 @@
         <v>18</v>
       </c>
       <c r="E51">
-        <v>5733</v>
+        <v>5745</v>
       </c>
       <c r="F51" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>16</v>
@@ -2059,7 +2039,7 @@
         <v>0</v>
       </c>
       <c r="K51" s="1">
-        <v>46212.775000000001</v>
+        <v>46212.774305555555</v>
       </c>
       <c r="L51">
         <v>0</v>
@@ -2073,22 +2053,22 @@
         <v>18</v>
       </c>
       <c r="E52">
-        <v>5704</v>
+        <v>5733</v>
       </c>
       <c r="F52" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>16</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J52" s="2">
-        <v>7.3379629629629628E-3</v>
+        <v>0</v>
       </c>
       <c r="K52" s="1">
-        <v>46212.775694444441</v>
+        <v>46212.775000000001</v>
       </c>
       <c r="L52">
         <v>0</v>
@@ -2102,10 +2082,10 @@
         <v>18</v>
       </c>
       <c r="E53">
-        <v>5693</v>
+        <v>5704</v>
       </c>
       <c r="F53" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H53" s="2" t="s">
         <v>16</v>
@@ -2114,7 +2094,7 @@
         <v>10</v>
       </c>
       <c r="J53" s="2">
-        <v>7.8125E-3</v>
+        <v>7.3379629629629628E-3</v>
       </c>
       <c r="K53" s="1">
         <v>46212.775694444441</v>
@@ -2131,22 +2111,22 @@
         <v>18</v>
       </c>
       <c r="E54">
-        <v>5718</v>
+        <v>5693</v>
       </c>
       <c r="F54" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H54" s="2" t="s">
         <v>16</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J54" s="2">
-        <v>0</v>
+        <v>7.8125E-3</v>
       </c>
       <c r="K54" s="1">
-        <v>46212.776388888888</v>
+        <v>46212.775694444441</v>
       </c>
       <c r="L54">
         <v>0</v>
@@ -2160,10 +2140,10 @@
         <v>18</v>
       </c>
       <c r="E55">
-        <v>5700</v>
+        <v>5718</v>
       </c>
       <c r="F55" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H55" s="2" t="s">
         <v>16</v>
@@ -2175,7 +2155,7 @@
         <v>0</v>
       </c>
       <c r="K55" s="1">
-        <v>46212.777083333334</v>
+        <v>46212.776388888888</v>
       </c>
       <c r="L55">
         <v>0</v>
@@ -2189,10 +2169,10 @@
         <v>18</v>
       </c>
       <c r="E56">
-        <v>5726</v>
+        <v>5700</v>
       </c>
       <c r="F56" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>16</v>
@@ -2204,7 +2184,7 @@
         <v>0</v>
       </c>
       <c r="K56" s="1">
-        <v>46212.777777777781</v>
+        <v>46212.777083333334</v>
       </c>
       <c r="L56">
         <v>0</v>
@@ -2218,10 +2198,10 @@
         <v>18</v>
       </c>
       <c r="E57">
-        <v>5684</v>
+        <v>5726</v>
       </c>
       <c r="F57" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H57" s="2" t="s">
         <v>16</v>
@@ -2247,22 +2227,22 @@
         <v>18</v>
       </c>
       <c r="E58">
-        <v>5740</v>
+        <v>5684</v>
       </c>
       <c r="F58" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H58" s="2" t="s">
         <v>16</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J58" s="2">
-        <v>7.3148148148148148E-3</v>
+        <v>0</v>
       </c>
       <c r="K58" s="1">
-        <v>46212.77847222222</v>
+        <v>46212.777777777781</v>
       </c>
       <c r="L58">
         <v>0</v>
@@ -2276,10 +2256,10 @@
         <v>18</v>
       </c>
       <c r="E59">
-        <v>5701</v>
+        <v>5740</v>
       </c>
       <c r="F59" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H59" s="2" t="s">
         <v>16</v>
@@ -2288,10 +2268,10 @@
         <v>10</v>
       </c>
       <c r="J59" s="2">
-        <v>1.8194444444444444E-2</v>
+        <v>7.3148148148148148E-3</v>
       </c>
       <c r="K59" s="1">
-        <v>46212.779166666667</v>
+        <v>46212.77847222222</v>
       </c>
       <c r="L59">
         <v>0</v>
@@ -2305,22 +2285,22 @@
         <v>18</v>
       </c>
       <c r="E60">
-        <v>5695</v>
+        <v>5701</v>
       </c>
       <c r="F60" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H60" s="2" t="s">
         <v>16</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J60" s="2">
-        <v>0</v>
+        <v>1.8194444444444444E-2</v>
       </c>
       <c r="K60" s="1">
-        <v>46212.752893518518</v>
+        <v>46212.779166666667</v>
       </c>
       <c r="L60">
         <v>0</v>
@@ -2334,10 +2314,10 @@
         <v>18</v>
       </c>
       <c r="E61">
-        <v>5690</v>
+        <v>5695</v>
       </c>
       <c r="F61" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H61" s="2" t="s">
         <v>16</v>
@@ -2363,10 +2343,10 @@
         <v>18</v>
       </c>
       <c r="E62">
-        <v>5697</v>
+        <v>5690</v>
       </c>
       <c r="F62" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>16</v>
@@ -2378,7 +2358,7 @@
         <v>0</v>
       </c>
       <c r="K62" s="1">
-        <v>46212.753587962965</v>
+        <v>46212.752893518518</v>
       </c>
       <c r="L62">
         <v>0</v>
@@ -2392,22 +2372,22 @@
         <v>18</v>
       </c>
       <c r="E63">
-        <v>5744</v>
+        <v>5697</v>
       </c>
       <c r="F63" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>16</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J63" s="2">
         <v>0</v>
       </c>
       <c r="K63" s="1">
-        <v>46212.754282407404</v>
+        <v>46212.753587962965</v>
       </c>
       <c r="L63">
         <v>0</v>
@@ -2417,41 +2397,41 @@
       </c>
     </row>
     <row r="64" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H64" s="2"/>
-      <c r="I64" s="1"/>
-      <c r="J64" s="2"/>
-      <c r="K64" s="1"/>
+      <c r="D64" t="s">
+        <v>18</v>
+      </c>
+      <c r="E64">
+        <v>5744</v>
+      </c>
+      <c r="F64" t="s">
+        <v>73</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I64" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J64" s="2">
+        <v>0</v>
+      </c>
+      <c r="K64" s="1">
+        <v>46212.754282407404</v>
+      </c>
+      <c r="L64">
+        <v>0</v>
+      </c>
       <c r="M64" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="65" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="H65" s="2"/>
+      <c r="I65" s="1"/>
+      <c r="J65" s="2"/>
+      <c r="K65" s="1"/>
+      <c r="M65" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="65" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="D65" t="s">
-        <v>18</v>
-      </c>
-      <c r="E65">
-        <v>5738</v>
-      </c>
-      <c r="F65" t="s">
-        <v>74</v>
-      </c>
-      <c r="H65" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I65" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="J65" s="2">
-        <v>0</v>
-      </c>
-      <c r="K65" s="1">
-        <v>46212.754976851851</v>
-      </c>
-      <c r="L65">
-        <v>0</v>
-      </c>
-      <c r="M65" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="66" spans="4:13" x14ac:dyDescent="0.3">
@@ -2459,10 +2439,10 @@
         <v>18</v>
       </c>
       <c r="E66">
-        <v>5691</v>
+        <v>5738</v>
       </c>
       <c r="F66" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H66" s="2" t="s">
         <v>16</v>
@@ -2474,7 +2454,7 @@
         <v>0</v>
       </c>
       <c r="K66" s="1">
-        <v>46212.755671296298</v>
+        <v>46212.754976851851</v>
       </c>
       <c r="L66">
         <v>0</v>
@@ -2488,10 +2468,10 @@
         <v>18</v>
       </c>
       <c r="E67">
-        <v>5699</v>
+        <v>5691</v>
       </c>
       <c r="F67" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>16</v>
@@ -2503,7 +2483,7 @@
         <v>0</v>
       </c>
       <c r="K67" s="1">
-        <v>46212.756365740737</v>
+        <v>46212.755671296298</v>
       </c>
       <c r="L67">
         <v>0</v>
@@ -2517,10 +2497,10 @@
         <v>18</v>
       </c>
       <c r="E68">
-        <v>5694</v>
+        <v>5699</v>
       </c>
       <c r="F68" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H68" s="2" t="s">
         <v>16</v>
@@ -2546,10 +2526,10 @@
         <v>18</v>
       </c>
       <c r="E69">
-        <v>5730</v>
+        <v>5694</v>
       </c>
       <c r="F69" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H69" s="2" t="s">
         <v>16</v>
@@ -2561,7 +2541,7 @@
         <v>0</v>
       </c>
       <c r="K69" s="1">
-        <v>46212.757060185184</v>
+        <v>46212.756365740737</v>
       </c>
       <c r="L69">
         <v>0</v>
@@ -2575,10 +2555,10 @@
         <v>18</v>
       </c>
       <c r="E70">
-        <v>5681</v>
+        <v>5730</v>
       </c>
       <c r="F70" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H70" s="2" t="s">
         <v>16</v>
@@ -2590,7 +2570,7 @@
         <v>0</v>
       </c>
       <c r="K70" s="1">
-        <v>46212.757754629631</v>
+        <v>46212.757060185184</v>
       </c>
       <c r="L70">
         <v>0</v>
@@ -2604,10 +2584,10 @@
         <v>18</v>
       </c>
       <c r="E71">
-        <v>5735</v>
+        <v>5681</v>
       </c>
       <c r="F71" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H71" s="2" t="s">
         <v>16</v>
@@ -2619,7 +2599,7 @@
         <v>0</v>
       </c>
       <c r="K71" s="1">
-        <v>46212.758449074077</v>
+        <v>46212.757754629631</v>
       </c>
       <c r="L71">
         <v>0</v>
@@ -2633,10 +2613,10 @@
         <v>18</v>
       </c>
       <c r="E72">
-        <v>5692</v>
+        <v>5735</v>
       </c>
       <c r="F72" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>16</v>
@@ -2662,22 +2642,22 @@
         <v>18</v>
       </c>
       <c r="E73">
-        <v>5703</v>
+        <v>5692</v>
       </c>
       <c r="F73" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>16</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J73" s="2">
-        <v>8.1481481481481474E-3</v>
+        <v>0</v>
       </c>
       <c r="K73" s="1">
-        <v>46212.759143518517</v>
+        <v>46212.758449074077</v>
       </c>
       <c r="L73">
         <v>0</v>
@@ -2691,22 +2671,22 @@
         <v>18</v>
       </c>
       <c r="E74">
-        <v>5708</v>
+        <v>5703</v>
       </c>
       <c r="F74" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>16</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J74" s="2">
-        <v>0</v>
+        <v>8.1481481481481474E-3</v>
       </c>
       <c r="K74" s="1">
-        <v>46212.759837962964</v>
+        <v>46212.759143518517</v>
       </c>
       <c r="L74">
         <v>0</v>
@@ -2720,10 +2700,10 @@
         <v>18</v>
       </c>
       <c r="E75">
-        <v>5712</v>
+        <v>5708</v>
       </c>
       <c r="F75" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H75" s="2" t="s">
         <v>16</v>
@@ -2735,7 +2715,7 @@
         <v>0</v>
       </c>
       <c r="K75" s="1">
-        <v>46212.76053240741</v>
+        <v>46212.759837962964</v>
       </c>
       <c r="L75">
         <v>0</v>
@@ -2749,10 +2729,10 @@
         <v>18</v>
       </c>
       <c r="E76">
-        <v>5734</v>
+        <v>5712</v>
       </c>
       <c r="F76" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H76" s="2" t="s">
         <v>16</v>
@@ -2764,7 +2744,7 @@
         <v>0</v>
       </c>
       <c r="K76" s="1">
-        <v>46212.76122685185</v>
+        <v>46212.76053240741</v>
       </c>
       <c r="L76">
         <v>0</v>
@@ -2778,10 +2758,10 @@
         <v>18</v>
       </c>
       <c r="E77">
-        <v>5743</v>
+        <v>5734</v>
       </c>
       <c r="F77" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H77" s="2" t="s">
         <v>16</v>
@@ -2807,10 +2787,10 @@
         <v>18</v>
       </c>
       <c r="E78">
-        <v>5742</v>
+        <v>5743</v>
       </c>
       <c r="F78" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H78" s="2" t="s">
         <v>16</v>
@@ -2822,7 +2802,7 @@
         <v>0</v>
       </c>
       <c r="K78" s="1">
-        <v>46212.761921296296</v>
+        <v>46212.76122685185</v>
       </c>
       <c r="L78">
         <v>0</v>
@@ -2836,22 +2816,22 @@
         <v>18</v>
       </c>
       <c r="E79">
-        <v>5723</v>
+        <v>5742</v>
       </c>
       <c r="F79" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H79" s="2" t="s">
         <v>16</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J79" s="2">
         <v>0</v>
       </c>
       <c r="K79" s="1">
-        <v>46212.762615740743</v>
+        <v>46212.761921296296</v>
       </c>
       <c r="L79">
         <v>0</v>
@@ -2861,41 +2841,41 @@
       </c>
     </row>
     <row r="80" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H80" s="2"/>
-      <c r="I80" s="1"/>
-      <c r="J80" s="2"/>
-      <c r="K80" s="1"/>
+      <c r="D80" t="s">
+        <v>18</v>
+      </c>
+      <c r="E80">
+        <v>5723</v>
+      </c>
+      <c r="F80" t="s">
+        <v>88</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I80" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J80" s="2">
+        <v>0</v>
+      </c>
+      <c r="K80" s="1">
+        <v>46212.762615740743</v>
+      </c>
+      <c r="L80">
+        <v>0</v>
+      </c>
       <c r="M80" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="81" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="H81" s="2"/>
+      <c r="I81" s="1"/>
+      <c r="J81" s="2"/>
+      <c r="K81" s="1"/>
+      <c r="M81" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="81" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="D81" t="s">
-        <v>18</v>
-      </c>
-      <c r="E81">
-        <v>5706</v>
-      </c>
-      <c r="F81" t="s">
-        <v>89</v>
-      </c>
-      <c r="H81" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I81" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="J81" s="2">
-        <v>0</v>
-      </c>
-      <c r="K81" s="1">
-        <v>46212.763310185182</v>
-      </c>
-      <c r="L81">
-        <v>0</v>
-      </c>
-      <c r="M81" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="82" spans="4:13" x14ac:dyDescent="0.3">
@@ -2903,10 +2883,10 @@
         <v>18</v>
       </c>
       <c r="E82">
-        <v>5670</v>
+        <v>5706</v>
       </c>
       <c r="F82" t="s">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="H82" s="2" t="s">
         <v>16</v>
@@ -2918,7 +2898,7 @@
         <v>0</v>
       </c>
       <c r="K82" s="1">
-        <v>46212.764004629629</v>
+        <v>46212.763310185182</v>
       </c>
       <c r="L82">
         <v>0</v>
@@ -2932,10 +2912,10 @@
         <v>18</v>
       </c>
       <c r="E83">
-        <v>5677</v>
+        <v>5670</v>
       </c>
       <c r="F83" t="s">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="H83" s="2" t="s">
         <v>16</v>
@@ -2944,10 +2924,10 @@
         <v>10</v>
       </c>
       <c r="J83" s="2">
-        <v>7.2337962962962963E-3</v>
+        <v>1.8865740740740742E-2</v>
       </c>
       <c r="K83" s="1">
-        <v>46212.764699074076</v>
+        <v>46212.764004629629</v>
       </c>
       <c r="L83">
         <v>0</v>
@@ -2961,19 +2941,19 @@
         <v>18</v>
       </c>
       <c r="E84">
-        <v>5685</v>
+        <v>5677</v>
       </c>
       <c r="F84" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H84" s="2" t="s">
         <v>16</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J84" s="2">
-        <v>0</v>
+        <v>7.2337962962962963E-3</v>
       </c>
       <c r="K84" s="1">
         <v>46212.764699074076</v>
@@ -2990,22 +2970,22 @@
         <v>18</v>
       </c>
       <c r="E85">
-        <v>5719</v>
+        <v>5685</v>
       </c>
       <c r="F85" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H85" s="2" t="s">
         <v>16</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J85" s="2">
-        <v>9.5486111111111119E-3</v>
+        <v>0</v>
       </c>
       <c r="K85" s="1">
-        <v>46212.765393518515</v>
+        <v>46212.764699074076</v>
       </c>
       <c r="L85">
         <v>0</v>
@@ -3015,162 +2995,467 @@
       </c>
     </row>
     <row r="86" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H86" s="2"/>
-      <c r="I86" s="1"/>
-      <c r="J86" s="2"/>
-      <c r="K86" s="1"/>
+      <c r="D86" t="s">
+        <v>18</v>
+      </c>
+      <c r="E86">
+        <v>5719</v>
+      </c>
+      <c r="F86" t="s">
+        <v>92</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I86" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J86" s="2">
+        <v>9.5486111111111119E-3</v>
+      </c>
+      <c r="K86" s="1">
+        <v>46212.765393518515</v>
+      </c>
+      <c r="L86">
+        <v>0</v>
+      </c>
+      <c r="M86" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="87" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H87" s="2"/>
-      <c r="I87" s="1"/>
-      <c r="J87" s="2"/>
-      <c r="K87" s="1"/>
+      <c r="D87" t="s">
+        <v>18</v>
+      </c>
+      <c r="E87">
+        <v>5747</v>
+      </c>
+      <c r="F87" t="s">
+        <v>22</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I87" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J87" s="2">
+        <v>7.4131944444444445E-2</v>
+      </c>
+      <c r="K87" s="1">
+        <v>46218.585879629631</v>
+      </c>
+      <c r="L87">
+        <v>0</v>
+      </c>
+      <c r="M87" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="88" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H88" s="2"/>
       <c r="I88" s="1"/>
       <c r="J88" s="2"/>
       <c r="K88" s="1"/>
+      <c r="M88" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="89" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H89" s="2"/>
-      <c r="I89" s="1"/>
-      <c r="J89" s="2"/>
-      <c r="K89" s="1"/>
+      <c r="D89" t="s">
+        <v>18</v>
+      </c>
+      <c r="E89">
+        <v>5714</v>
+      </c>
+      <c r="F89" t="s">
+        <v>30</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I89" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J89" s="2">
+        <v>2.931712962962963E-2</v>
+      </c>
+      <c r="K89" s="1">
+        <v>46218.586574074077</v>
+      </c>
+      <c r="L89">
+        <v>0</v>
+      </c>
+      <c r="M89" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="90" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H90" s="2"/>
-      <c r="I90" s="1"/>
-      <c r="J90" s="2"/>
-      <c r="K90" s="1"/>
+      <c r="D90" t="s">
+        <v>18</v>
+      </c>
+      <c r="E90">
+        <v>5669</v>
+      </c>
+      <c r="F90" t="s">
+        <v>19</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I90" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J90" s="2">
+        <v>0</v>
+      </c>
+      <c r="K90" s="1">
+        <v>46218.587268518517</v>
+      </c>
+      <c r="L90">
+        <v>0</v>
+      </c>
+      <c r="M90" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="91" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H91" s="2"/>
-      <c r="I91" s="1"/>
-      <c r="J91" s="2"/>
-      <c r="K91" s="1"/>
+      <c r="D91" t="s">
+        <v>18</v>
+      </c>
+      <c r="E91">
+        <v>5675</v>
+      </c>
+      <c r="F91" t="s">
+        <v>32</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I91" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J91" s="2">
+        <v>2.5416666666666667E-2</v>
+      </c>
+      <c r="K91" s="1">
+        <v>46218.587268518517</v>
+      </c>
+      <c r="L91">
+        <v>0</v>
+      </c>
+      <c r="M91" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="92" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H92" s="2"/>
-      <c r="I92" s="1"/>
-      <c r="J92" s="2"/>
-      <c r="K92" s="1"/>
+      <c r="D92" t="s">
+        <v>18</v>
+      </c>
+      <c r="E92">
+        <v>5689</v>
+      </c>
+      <c r="F92" t="s">
+        <v>40</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I92" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J92" s="2">
+        <v>2.2650462962962963E-2</v>
+      </c>
+      <c r="K92" s="1">
+        <v>46218.587962962964</v>
+      </c>
+      <c r="L92">
+        <v>0</v>
+      </c>
+      <c r="M92" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="93" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H93" s="2"/>
-      <c r="I93" s="1"/>
-      <c r="J93" s="2"/>
-      <c r="K93" s="1"/>
+      <c r="D93" t="s">
+        <v>18</v>
+      </c>
+      <c r="E93">
+        <v>5682</v>
+      </c>
+      <c r="F93" t="s">
+        <v>46</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I93" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J93" s="2">
+        <v>2.2164351851851852E-2</v>
+      </c>
+      <c r="K93" s="1">
+        <v>46218.58865740741</v>
+      </c>
+      <c r="L93">
+        <v>0</v>
+      </c>
+      <c r="M93" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="94" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H94" s="2"/>
-      <c r="I94" s="1"/>
-      <c r="J94" s="2"/>
-      <c r="K94" s="1"/>
+      <c r="D94" t="s">
+        <v>18</v>
+      </c>
+      <c r="E94">
+        <v>5732</v>
+      </c>
+      <c r="F94" t="s">
+        <v>53</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I94" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J94" s="2">
+        <v>0</v>
+      </c>
+      <c r="K94" s="1">
+        <v>46218.58935185185</v>
+      </c>
+      <c r="L94">
+        <v>0</v>
+      </c>
+      <c r="M94" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="95" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H95" s="2"/>
-      <c r="I95" s="1"/>
-      <c r="J95" s="2"/>
-      <c r="K95" s="1"/>
+      <c r="D95" t="s">
+        <v>18</v>
+      </c>
+      <c r="E95">
+        <v>5702</v>
+      </c>
+      <c r="F95" t="s">
+        <v>57</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I95" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J95" s="2">
+        <v>6.5624999999999998E-3</v>
+      </c>
+      <c r="K95" s="1">
+        <v>46218.58935185185</v>
+      </c>
+      <c r="L95">
+        <v>0</v>
+      </c>
+      <c r="M95" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="96" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H96" s="2"/>
-      <c r="I96" s="1"/>
-      <c r="J96" s="2"/>
-      <c r="K96" s="1"/>
-    </row>
-    <row r="97" spans="8:11" x14ac:dyDescent="0.3">
+      <c r="D96" t="s">
+        <v>18</v>
+      </c>
+      <c r="E96">
+        <v>5701</v>
+      </c>
+      <c r="F96" t="s">
+        <v>69</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I96" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J96" s="2">
+        <v>2.1643518518518518E-3</v>
+      </c>
+      <c r="K96" s="1">
+        <v>46218.590046296296</v>
+      </c>
+      <c r="L96">
+        <v>0</v>
+      </c>
+      <c r="M96" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="97" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H97" s="2"/>
       <c r="I97" s="1"/>
       <c r="J97" s="2"/>
       <c r="K97" s="1"/>
-    </row>
-    <row r="98" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H98" s="2"/>
-      <c r="I98" s="1"/>
-      <c r="J98" s="2"/>
-      <c r="K98" s="1"/>
-    </row>
-    <row r="99" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H99" s="2"/>
-      <c r="I99" s="1"/>
-      <c r="J99" s="2"/>
-      <c r="K99" s="1"/>
-    </row>
-    <row r="100" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H100" s="2"/>
-      <c r="I100" s="1"/>
-      <c r="J100" s="2"/>
-      <c r="K100" s="1"/>
-    </row>
-    <row r="101" spans="8:11" x14ac:dyDescent="0.3">
+      <c r="M97" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="98" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D98" t="s">
+        <v>18</v>
+      </c>
+      <c r="E98">
+        <v>5708</v>
+      </c>
+      <c r="F98" t="s">
+        <v>83</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I98" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J98" s="2">
+        <v>0</v>
+      </c>
+      <c r="K98" s="1">
+        <v>46218.590740740743</v>
+      </c>
+      <c r="L98">
+        <v>0</v>
+      </c>
+      <c r="M98" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="99" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D99" t="s">
+        <v>18</v>
+      </c>
+      <c r="E99">
+        <v>5670</v>
+      </c>
+      <c r="F99" t="s">
+        <v>20</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I99" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J99" s="2">
+        <v>2.3321759259259261E-2</v>
+      </c>
+      <c r="K99" s="1">
+        <v>46218.590740740743</v>
+      </c>
+      <c r="L99">
+        <v>0</v>
+      </c>
+      <c r="M99" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="100" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D100" t="s">
+        <v>18</v>
+      </c>
+      <c r="E100">
+        <v>5719</v>
+      </c>
+      <c r="F100" t="s">
+        <v>92</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I100" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J100" s="2">
+        <v>0</v>
+      </c>
+      <c r="K100" s="1">
+        <v>46218.591435185182</v>
+      </c>
+      <c r="L100">
+        <v>0</v>
+      </c>
+      <c r="M100" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="101" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H101" s="2"/>
       <c r="I101" s="1"/>
       <c r="J101" s="2"/>
       <c r="K101" s="1"/>
     </row>
-    <row r="102" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="102" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H102" s="2"/>
       <c r="I102" s="1"/>
       <c r="J102" s="2"/>
       <c r="K102" s="1"/>
     </row>
-    <row r="103" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="103" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H103" s="2"/>
       <c r="I103" s="1"/>
       <c r="J103" s="2"/>
       <c r="K103" s="1"/>
     </row>
-    <row r="104" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="104" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H104" s="2"/>
       <c r="I104" s="1"/>
       <c r="J104" s="2"/>
       <c r="K104" s="1"/>
     </row>
-    <row r="105" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="105" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H105" s="2"/>
       <c r="I105" s="1"/>
       <c r="J105" s="2"/>
       <c r="K105" s="1"/>
     </row>
-    <row r="106" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="106" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H106" s="2"/>
       <c r="I106" s="1"/>
       <c r="J106" s="2"/>
       <c r="K106" s="1"/>
     </row>
-    <row r="107" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="107" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H107" s="2"/>
       <c r="I107" s="1"/>
       <c r="J107" s="2"/>
       <c r="K107" s="1"/>
     </row>
-    <row r="108" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="108" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H108" s="2"/>
       <c r="I108" s="1"/>
       <c r="J108" s="2"/>
       <c r="K108" s="1"/>
     </row>
-    <row r="109" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="109" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H109" s="2"/>
       <c r="I109" s="1"/>
       <c r="J109" s="2"/>
       <c r="K109" s="1"/>
     </row>
-    <row r="110" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="110" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H110" s="2"/>
       <c r="I110" s="1"/>
       <c r="J110" s="2"/>
       <c r="K110" s="1"/>
     </row>
-    <row r="111" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="111" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H111" s="2"/>
       <c r="I111" s="1"/>
       <c r="J111" s="2"/>
       <c r="K111" s="1"/>
     </row>
-    <row r="112" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="112" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H112" s="2"/>
       <c r="I112" s="1"/>
       <c r="J112" s="2"/>
@@ -7309,6 +7594,7 @@
     <row r="802" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H802" s="2"/>
       <c r="I802" s="1"/>
+      <c r="J802" s="2"/>
       <c r="K802" s="1"/>
     </row>
     <row r="803" spans="8:11" x14ac:dyDescent="0.3">
@@ -7584,6 +7870,7 @@
     <row r="848" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H848" s="2"/>
       <c r="I848" s="1"/>
+      <c r="J848" s="2"/>
       <c r="K848" s="1"/>
     </row>
     <row r="849" spans="8:11" x14ac:dyDescent="0.3">
@@ -10669,6 +10956,7 @@
     <row r="1367" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1367" s="2"/>
       <c r="I1367" s="1"/>
+      <c r="J1367" s="2"/>
       <c r="K1367" s="1"/>
     </row>
     <row r="1368" spans="8:11" x14ac:dyDescent="0.3">
@@ -13992,6 +14280,7 @@
     </row>
     <row r="1934" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1934" s="1"/>
+      <c r="J1934" s="2"/>
       <c r="K1934" s="1"/>
     </row>
     <row r="1935" spans="8:11" x14ac:dyDescent="0.3">
@@ -14002,14 +14291,17 @@
     <row r="1936" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1936" s="2"/>
       <c r="I1936" s="1"/>
+      <c r="K1936" s="1"/>
     </row>
     <row r="1937" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1937" s="2"/>
       <c r="I1937" s="1"/>
+      <c r="J1937" s="2"/>
       <c r="K1937" s="1"/>
     </row>
     <row r="1938" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1938" s="1"/>
+      <c r="J1938" s="2"/>
       <c r="K1938" s="1"/>
     </row>
     <row r="1939" spans="8:11" x14ac:dyDescent="0.3">
@@ -14035,6 +14327,7 @@
     <row r="1943" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1943" s="2"/>
       <c r="I1943" s="1"/>
+      <c r="J1943" s="2"/>
       <c r="K1943" s="1"/>
     </row>
     <row r="1944" spans="8:11" x14ac:dyDescent="0.3">
@@ -14044,9 +14337,11 @@
     </row>
     <row r="1945" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1945" s="1"/>
+      <c r="K1945" s="1"/>
     </row>
     <row r="1946" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1946" s="1"/>
+      <c r="J1946" s="2"/>
       <c r="K1946" s="1"/>
     </row>
     <row r="1947" spans="8:11" x14ac:dyDescent="0.3">
@@ -40984,6 +41279,7 @@
       <c r="K6920" s="1"/>
     </row>
     <row r="6921" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6921" s="2"/>
       <c r="K6921" s="1"/>
     </row>
     <row r="6922" spans="10:11" x14ac:dyDescent="0.3">
@@ -40991,6 +41287,7 @@
       <c r="K6922" s="1"/>
     </row>
     <row r="6923" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6923" s="2"/>
       <c r="K6923" s="1"/>
     </row>
     <row r="6924" spans="10:11" x14ac:dyDescent="0.3">
@@ -40998,6 +41295,7 @@
       <c r="K6924" s="1"/>
     </row>
     <row r="6925" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6925" s="2"/>
       <c r="K6925" s="1"/>
     </row>
     <row r="6926" spans="10:11" x14ac:dyDescent="0.3">
@@ -41013,6 +41311,7 @@
       <c r="K6928" s="1"/>
     </row>
     <row r="6929" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6929" s="2"/>
       <c r="K6929" s="1"/>
     </row>
     <row r="6930" spans="10:11" x14ac:dyDescent="0.3">
@@ -41022,6 +41321,7 @@
       <c r="K6931" s="1"/>
     </row>
     <row r="6932" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6932" s="2"/>
       <c r="K6932" s="1"/>
     </row>
     <row r="6933" spans="10:11" x14ac:dyDescent="0.3">
@@ -41029,9 +41329,15 @@
       <c r="K6933" s="1"/>
     </row>
     <row r="6934" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6934" s="2"/>
       <c r="K6934" s="1"/>
     </row>
+    <row r="6935" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6935" s="2"/>
+      <c r="K6935" s="1"/>
+    </row>
     <row r="6936" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6936" s="2"/>
       <c r="K6936" s="1"/>
     </row>
     <row r="6937" spans="10:11" x14ac:dyDescent="0.3">
@@ -41039,12 +41345,15 @@
       <c r="K6937" s="1"/>
     </row>
     <row r="6938" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6938" s="2"/>
       <c r="K6938" s="1"/>
     </row>
     <row r="6939" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6939" s="2"/>
       <c r="K6939" s="1"/>
     </row>
     <row r="6940" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6940" s="2"/>
       <c r="K6940" s="1"/>
     </row>
     <row r="6941" spans="10:11" x14ac:dyDescent="0.3">
@@ -41052,12 +41361,15 @@
       <c r="K6941" s="1"/>
     </row>
     <row r="6942" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6942" s="2"/>
       <c r="K6942" s="1"/>
     </row>
     <row r="6943" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6943" s="2"/>
       <c r="K6943" s="1"/>
     </row>
     <row r="6944" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6944" s="2"/>
       <c r="K6944" s="1"/>
     </row>
     <row r="6945" spans="10:11" x14ac:dyDescent="0.3">
@@ -41069,9 +41381,11 @@
       <c r="K6946" s="1"/>
     </row>
     <row r="6947" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6947" s="2"/>
       <c r="K6947" s="1"/>
     </row>
     <row r="6948" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6948" s="2"/>
       <c r="K6948" s="1"/>
     </row>
     <row r="6949" spans="10:11" x14ac:dyDescent="0.3">
@@ -41086,6 +41400,7 @@
       <c r="K6951" s="1"/>
     </row>
     <row r="6952" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6952" s="2"/>
       <c r="K6952" s="1"/>
     </row>
     <row r="6953" spans="10:11" x14ac:dyDescent="0.3">
@@ -41112,6 +41427,7 @@
       <c r="K6958" s="1"/>
     </row>
     <row r="6959" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6959" s="2"/>
       <c r="K6959" s="1"/>
     </row>
     <row r="6960" spans="10:11" x14ac:dyDescent="0.3">
@@ -41122,7 +41438,12 @@
       <c r="J6961" s="2"/>
       <c r="K6961" s="1"/>
     </row>
+    <row r="6962" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6962" s="2"/>
+      <c r="K6962" s="1"/>
+    </row>
     <row r="6963" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6963" s="2"/>
       <c r="K6963" s="1"/>
     </row>
     <row r="6964" spans="10:11" x14ac:dyDescent="0.3">
@@ -41130,6 +41451,7 @@
       <c r="K6964" s="1"/>
     </row>
     <row r="6965" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6965" s="2"/>
       <c r="K6965" s="1"/>
     </row>
     <row r="6966" spans="10:11" x14ac:dyDescent="0.3">
@@ -41141,6 +41463,7 @@
       <c r="K6967" s="1"/>
     </row>
     <row r="6968" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6968" s="2"/>
       <c r="K6968" s="1"/>
     </row>
     <row r="6969" spans="10:11" x14ac:dyDescent="0.3">
@@ -41148,6 +41471,7 @@
       <c r="K6969" s="1"/>
     </row>
     <row r="6970" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6970" s="2"/>
       <c r="K6970" s="1"/>
     </row>
     <row r="6971" spans="10:11" x14ac:dyDescent="0.3">
@@ -41162,13 +41486,19 @@
       <c r="K6973" s="1"/>
     </row>
     <row r="6974" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6974" s="2"/>
       <c r="K6974" s="1"/>
     </row>
     <row r="6975" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J6975" s="2"/>
       <c r="K6975" s="1"/>
     </row>
+    <row r="6976" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6976" s="2"/>
+      <c r="K6976" s="1"/>
+    </row>
     <row r="6977" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6977" s="2"/>
       <c r="K6977" s="1"/>
     </row>
     <row r="6978" spans="10:11" x14ac:dyDescent="0.3">
@@ -41179,15 +41509,18 @@
       <c r="K6979" s="1"/>
     </row>
     <row r="6980" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6980" s="2"/>
       <c r="K6980" s="1"/>
     </row>
     <row r="6981" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6981" s="2"/>
       <c r="K6981" s="1"/>
     </row>
     <row r="6982" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K6982" s="1"/>
     </row>
     <row r="6983" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6983" s="2"/>
       <c r="K6983" s="1"/>
     </row>
     <row r="6984" spans="10:11" x14ac:dyDescent="0.3">
@@ -41203,6 +41536,7 @@
       <c r="K6986" s="1"/>
     </row>
     <row r="6987" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6987" s="2"/>
       <c r="K6987" s="1"/>
     </row>
     <row r="6988" spans="10:11" x14ac:dyDescent="0.3">
@@ -41221,6 +41555,7 @@
       <c r="K6991" s="1"/>
     </row>
     <row r="6992" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6992" s="2"/>
       <c r="K6992" s="1"/>
     </row>
     <row r="6993" spans="10:11" x14ac:dyDescent="0.3">
@@ -41232,6 +41567,7 @@
       <c r="K6994" s="1"/>
     </row>
     <row r="6995" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6995" s="2"/>
       <c r="K6995" s="1"/>
     </row>
     <row r="6996" spans="10:11" x14ac:dyDescent="0.3">
@@ -41249,18 +41585,23 @@
       <c r="K6999" s="1"/>
     </row>
     <row r="7000" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7000" s="2"/>
       <c r="K7000" s="1"/>
     </row>
     <row r="7001" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7001" s="2"/>
       <c r="K7001" s="1"/>
     </row>
     <row r="7002" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7002" s="2"/>
       <c r="K7002" s="1"/>
     </row>
     <row r="7003" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7003" s="2"/>
       <c r="K7003" s="1"/>
     </row>
     <row r="7004" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7004" s="2"/>
       <c r="K7004" s="1"/>
     </row>
     <row r="7005" spans="10:11" x14ac:dyDescent="0.3">
@@ -41289,6 +41630,7 @@
       <c r="K7012" s="1"/>
     </row>
     <row r="7014" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7014" s="2"/>
       <c r="K7014" s="1"/>
     </row>
     <row r="7015" spans="10:11" x14ac:dyDescent="0.3">
@@ -41296,9 +41638,11 @@
       <c r="K7015" s="1"/>
     </row>
     <row r="7016" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7016" s="2"/>
       <c r="K7016" s="1"/>
     </row>
     <row r="7017" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7017" s="2"/>
       <c r="K7017" s="1"/>
     </row>
     <row r="7018" spans="10:11" x14ac:dyDescent="0.3">
@@ -41321,12 +41665,15 @@
       <c r="K7022" s="1"/>
     </row>
     <row r="7023" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7023" s="2"/>
       <c r="K7023" s="1"/>
     </row>
     <row r="7024" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7024" s="2"/>
       <c r="K7024" s="1"/>
     </row>
     <row r="7025" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7025" s="2"/>
       <c r="K7025" s="1"/>
     </row>
     <row r="7026" spans="10:11" x14ac:dyDescent="0.3">
@@ -41341,9 +41688,11 @@
       <c r="K7028" s="1"/>
     </row>
     <row r="7030" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7030" s="2"/>
       <c r="K7030" s="1"/>
     </row>
     <row r="7031" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7031" s="2"/>
       <c r="K7031" s="1"/>
     </row>
     <row r="7032" spans="10:11" x14ac:dyDescent="0.3">
@@ -41359,12 +41708,14 @@
       <c r="K7034" s="1"/>
     </row>
     <row r="7035" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7035" s="2"/>
       <c r="K7035" s="1"/>
     </row>
     <row r="7036" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7036" s="1"/>
     </row>
     <row r="7037" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7037" s="2"/>
       <c r="K7037" s="1"/>
     </row>
     <row r="7038" spans="10:11" x14ac:dyDescent="0.3">
@@ -41385,6 +41736,7 @@
       <c r="K7042" s="1"/>
     </row>
     <row r="7043" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7043" s="2"/>
       <c r="K7043" s="1"/>
     </row>
     <row r="7044" spans="10:11" x14ac:dyDescent="0.3">
@@ -41396,9 +41748,11 @@
       <c r="K7045" s="1"/>
     </row>
     <row r="7046" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7046" s="2"/>
       <c r="K7046" s="1"/>
     </row>
     <row r="7047" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7047" s="2"/>
       <c r="K7047" s="1"/>
     </row>
     <row r="7048" spans="10:11" x14ac:dyDescent="0.3">
@@ -41410,6 +41764,7 @@
       <c r="K7049" s="1"/>
     </row>
     <row r="7050" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7050" s="2"/>
       <c r="K7050" s="1"/>
     </row>
     <row r="7051" spans="10:11" x14ac:dyDescent="0.3">
@@ -41449,9 +41804,11 @@
       <c r="K7059" s="1"/>
     </row>
     <row r="7060" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7060" s="2"/>
       <c r="K7060" s="1"/>
     </row>
     <row r="7061" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7061" s="2"/>
       <c r="K7061" s="1"/>
     </row>
     <row r="7062" spans="10:11" x14ac:dyDescent="0.3">
@@ -41459,9 +41816,11 @@
       <c r="K7062" s="1"/>
     </row>
     <row r="7063" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7063" s="2"/>
       <c r="K7063" s="1"/>
     </row>
     <row r="7064" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7064" s="2"/>
       <c r="K7064" s="1"/>
     </row>
     <row r="7065" spans="10:11" x14ac:dyDescent="0.3">
@@ -41472,6 +41831,7 @@
       <c r="K7066" s="1"/>
     </row>
     <row r="7067" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7067" s="2"/>
       <c r="K7067" s="1"/>
     </row>
     <row r="7068" spans="10:11" x14ac:dyDescent="0.3">
@@ -41479,18 +41839,26 @@
       <c r="K7068" s="1"/>
     </row>
     <row r="7069" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7069" s="2"/>
       <c r="K7069" s="1"/>
     </row>
+    <row r="7070" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7070" s="2"/>
+      <c r="K7070" s="1"/>
+    </row>
     <row r="7071" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7071" s="2"/>
       <c r="K7071" s="1"/>
     </row>
     <row r="7072" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7072" s="2"/>
       <c r="K7072" s="1"/>
     </row>
     <row r="7073" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7073" s="1"/>
     </row>
     <row r="7074" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7074" s="2"/>
       <c r="K7074" s="1"/>
     </row>
     <row r="7075" spans="10:11" x14ac:dyDescent="0.3">
@@ -41498,6 +41866,7 @@
       <c r="K7075" s="1"/>
     </row>
     <row r="7076" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7076" s="2"/>
       <c r="K7076" s="1"/>
     </row>
     <row r="7077" spans="10:11" x14ac:dyDescent="0.3">
@@ -41508,6 +41877,7 @@
       <c r="K7078" s="1"/>
     </row>
     <row r="7079" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7079" s="2"/>
       <c r="K7079" s="1"/>
     </row>
     <row r="7080" spans="10:11" x14ac:dyDescent="0.3">
@@ -41534,15 +41904,19 @@
       <c r="K7085" s="1"/>
     </row>
     <row r="7086" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7086" s="2"/>
       <c r="K7086" s="1"/>
     </row>
     <row r="7087" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7087" s="2"/>
       <c r="K7087" s="1"/>
     </row>
     <row r="7088" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7088" s="2"/>
       <c r="K7088" s="1"/>
     </row>
     <row r="7089" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7089" s="2"/>
       <c r="K7089" s="1"/>
     </row>
     <row r="7090" spans="10:11" x14ac:dyDescent="0.3">
@@ -41564,6 +41938,7 @@
       <c r="K7094" s="1"/>
     </row>
     <row r="7095" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7095" s="2"/>
       <c r="K7095" s="1"/>
     </row>
     <row r="7096" spans="10:11" x14ac:dyDescent="0.3">
@@ -41571,9 +41946,11 @@
       <c r="K7096" s="1"/>
     </row>
     <row r="7097" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7097" s="2"/>
       <c r="K7097" s="1"/>
     </row>
     <row r="7098" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7098" s="2"/>
       <c r="K7098" s="1"/>
     </row>
     <row r="7099" spans="10:11" x14ac:dyDescent="0.3">
@@ -41581,6 +41958,7 @@
       <c r="K7099" s="1"/>
     </row>
     <row r="7100" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7100" s="2"/>
       <c r="K7100" s="1"/>
     </row>
     <row r="7101" spans="10:11" x14ac:dyDescent="0.3">
@@ -41592,6 +41970,7 @@
       <c r="K7102" s="1"/>
     </row>
     <row r="7103" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7103" s="2"/>
       <c r="K7103" s="1"/>
     </row>
     <row r="7104" spans="10:11" x14ac:dyDescent="0.3">
@@ -41606,6 +41985,10 @@
       <c r="J7106" s="2"/>
       <c r="K7106" s="1"/>
     </row>
+    <row r="7107" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7107" s="2"/>
+      <c r="K7107" s="1"/>
+    </row>
     <row r="7108" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J7108" s="2"/>
       <c r="K7108" s="1"/>
@@ -41615,6 +41998,7 @@
       <c r="K7109" s="1"/>
     </row>
     <row r="7110" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7110" s="2"/>
       <c r="K7110" s="1"/>
     </row>
     <row r="7111" spans="10:11" x14ac:dyDescent="0.3">
@@ -41626,6 +42010,7 @@
       <c r="K7112" s="1"/>
     </row>
     <row r="7113" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7113" s="2"/>
       <c r="K7113" s="1"/>
     </row>
     <row r="7114" spans="10:11" x14ac:dyDescent="0.3">
@@ -41636,10 +42021,15 @@
       <c r="J7115" s="2"/>
       <c r="K7115" s="1"/>
     </row>
+    <row r="7116" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7116" s="1"/>
+    </row>
     <row r="7117" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7117" s="2"/>
       <c r="K7117" s="1"/>
     </row>
     <row r="7118" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7118" s="2"/>
       <c r="K7118" s="1"/>
     </row>
     <row r="7119" spans="10:11" x14ac:dyDescent="0.3">
@@ -41647,6 +42037,7 @@
       <c r="K7119" s="1"/>
     </row>
     <row r="7120" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7120" s="2"/>
       <c r="K7120" s="1"/>
     </row>
     <row r="7121" spans="10:11" x14ac:dyDescent="0.3">
@@ -41661,6 +42052,7 @@
       <c r="K7123" s="1"/>
     </row>
     <row r="7124" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7124" s="2"/>
       <c r="K7124" s="1"/>
     </row>
     <row r="7125" spans="10:11" x14ac:dyDescent="0.3">
@@ -41683,6 +42075,7 @@
       <c r="K7129" s="1"/>
     </row>
     <row r="7130" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7130" s="2"/>
       <c r="K7130" s="1"/>
     </row>
     <row r="7131" spans="10:11" x14ac:dyDescent="0.3">
@@ -41702,25 +42095,37 @@
       <c r="K7134" s="1"/>
     </row>
     <row r="7135" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7135" s="2"/>
       <c r="K7135" s="1"/>
     </row>
     <row r="7136" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7136" s="2"/>
       <c r="K7136" s="1"/>
     </row>
     <row r="7137" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7137" s="2"/>
       <c r="K7137" s="1"/>
     </row>
     <row r="7138" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J7138" s="2"/>
       <c r="K7138" s="1"/>
     </row>
+    <row r="7139" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7139" s="2"/>
+      <c r="K7139" s="1"/>
+    </row>
     <row r="7140" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7140" s="2"/>
       <c r="K7140" s="1"/>
     </row>
     <row r="7141" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J7141" s="2"/>
       <c r="K7141" s="1"/>
     </row>
+    <row r="7142" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7142" s="2"/>
+      <c r="K7142" s="1"/>
+    </row>
     <row r="7143" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7143" s="1"/>
     </row>
@@ -41728,6 +42133,7 @@
       <c r="K7144" s="1"/>
     </row>
     <row r="7145" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7145" s="2"/>
       <c r="K7145" s="1"/>
     </row>
     <row r="7146" spans="10:11" x14ac:dyDescent="0.3">
@@ -41735,15 +42141,22 @@
       <c r="K7146" s="1"/>
     </row>
     <row r="7147" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7147" s="2"/>
       <c r="K7147" s="1"/>
     </row>
     <row r="7148" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7148" s="1"/>
     </row>
+    <row r="7149" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7149" s="2"/>
+      <c r="K7149" s="1"/>
+    </row>
     <row r="7150" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7150" s="2"/>
       <c r="K7150" s="1"/>
     </row>
     <row r="7151" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7151" s="2"/>
       <c r="K7151" s="1"/>
     </row>
     <row r="7152" spans="10:11" x14ac:dyDescent="0.3">
@@ -41757,6 +42170,7 @@
       <c r="K7154" s="1"/>
     </row>
     <row r="7155" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7155" s="2"/>
       <c r="K7155" s="1"/>
     </row>
     <row r="7156" spans="10:11" x14ac:dyDescent="0.3">
@@ -41775,9 +42189,11 @@
       <c r="K7159" s="1"/>
     </row>
     <row r="7160" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7160" s="2"/>
       <c r="K7160" s="1"/>
     </row>
     <row r="7161" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7161" s="2"/>
       <c r="K7161" s="1"/>
     </row>
     <row r="7162" spans="10:11" x14ac:dyDescent="0.3">
@@ -41785,9 +42201,11 @@
       <c r="K7162" s="1"/>
     </row>
     <row r="7163" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7163" s="2"/>
       <c r="K7163" s="1"/>
     </row>
     <row r="7164" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7164" s="2"/>
       <c r="K7164" s="1"/>
     </row>
     <row r="7165" spans="10:11" x14ac:dyDescent="0.3">
@@ -41795,6 +42213,7 @@
       <c r="K7165" s="1"/>
     </row>
     <row r="7166" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7166" s="2"/>
       <c r="K7166" s="1"/>
     </row>
     <row r="7167" spans="10:11" x14ac:dyDescent="0.3">
@@ -41811,10 +42230,14 @@
       <c r="K7170" s="1"/>
     </row>
     <row r="7171" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7171" s="2"/>
       <c r="K7171" s="1"/>
     </row>
     <row r="7172" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7172" s="1"/>
+    </row>
+    <row r="7173" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7173" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Pep-Move\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A7C760BF-1568-414B-B83F-1AD9511D6C64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{39A00D71-ADA1-4E7F-9EEF-1C80FBEC2E0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="3585" yWindow="3585" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="95">
   <si>
     <t>Company Name</t>
   </si>
@@ -87,6 +87,9 @@
   </si>
   <si>
     <t>Mark Complete</t>
+  </si>
+  <si>
+    <t>Alert Driving: Big Three</t>
   </si>
   <si>
     <t>Camera Event Management Orientation for Drivers</t>
@@ -694,7 +697,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="B1:K7400"/>
+  <dimension ref="A1:K7404"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -709,50 +712,50 @@
     <col min="11" max="11" width="8.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2">
         <v>5669</v>
       </c>
       <c r="D2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G2" t="s">
         <v>12</v>
@@ -770,7 +773,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="H3" s="2"/>
       <c r="I3" s="1"/>
       <c r="J3" s="2"/>
@@ -778,18 +781,18 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4">
         <v>5670</v>
       </c>
       <c r="D4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G4" t="s">
         <v>12</v>
@@ -807,7 +810,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="H5" s="2"/>
       <c r="I5" s="1"/>
       <c r="J5" s="2"/>
@@ -815,18 +818,18 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6">
         <v>5717</v>
       </c>
       <c r="D6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G6" t="s">
         <v>10</v>
@@ -844,18 +847,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7">
         <v>5747</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G7" t="s">
         <v>10</v>
@@ -873,18 +876,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C8">
         <v>5715</v>
       </c>
       <c r="D8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G8" t="s">
         <v>10</v>
@@ -902,18 +905,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C9">
         <v>5731</v>
       </c>
       <c r="D9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G9" t="s">
         <v>10</v>
@@ -931,18 +934,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C10">
         <v>5741</v>
       </c>
       <c r="D10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G10" t="s">
         <v>10</v>
@@ -960,18 +963,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C11">
         <v>5688</v>
       </c>
       <c r="D11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G11" t="s">
         <v>10</v>
@@ -989,18 +992,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12">
         <v>5678</v>
       </c>
       <c r="D12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G12" t="s">
         <v>10</v>
@@ -1018,18 +1021,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C13">
         <v>5676</v>
       </c>
       <c r="D13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G13" t="s">
         <v>10</v>
@@ -1047,18 +1050,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C14">
         <v>5686</v>
       </c>
       <c r="D14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G14" t="s">
         <v>13</v>
@@ -1076,18 +1079,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C15">
         <v>5714</v>
       </c>
       <c r="D15" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G15" t="s">
         <v>10</v>
@@ -1105,18 +1108,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C16">
         <v>5705</v>
       </c>
       <c r="D16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F16" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G16" t="s">
         <v>13</v>
@@ -1136,16 +1139,16 @@
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C17">
         <v>5669</v>
       </c>
       <c r="D17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F17" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G17" t="s">
         <v>10</v>
@@ -1165,16 +1168,16 @@
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C18">
         <v>5675</v>
       </c>
       <c r="D18" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G18" t="s">
         <v>10</v>
@@ -1194,16 +1197,16 @@
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C19">
         <v>5707</v>
       </c>
       <c r="D19" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G19" t="s">
         <v>10</v>
@@ -1223,16 +1226,16 @@
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C20">
         <v>5722</v>
       </c>
       <c r="D20" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G20" t="s">
         <v>10</v>
@@ -1252,16 +1255,16 @@
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C21">
         <v>5737</v>
       </c>
       <c r="D21" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G21" t="s">
         <v>10</v>
@@ -1281,16 +1284,16 @@
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C22">
         <v>5698</v>
       </c>
       <c r="D22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F22" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G22" t="s">
         <v>14</v>
@@ -1318,16 +1321,16 @@
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C24">
         <v>5713</v>
       </c>
       <c r="D24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F24" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G24" t="s">
         <v>12</v>
@@ -1355,16 +1358,16 @@
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C26">
         <v>5721</v>
       </c>
       <c r="D26" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F26" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G26" t="s">
         <v>10</v>
@@ -1384,16 +1387,16 @@
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C27">
         <v>5680</v>
       </c>
       <c r="D27" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F27" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G27" t="s">
         <v>12</v>
@@ -1421,16 +1424,16 @@
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C29">
         <v>5689</v>
       </c>
       <c r="D29" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F29" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G29" t="s">
         <v>10</v>
@@ -1450,16 +1453,16 @@
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C30">
         <v>5687</v>
       </c>
       <c r="D30" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F30" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G30" t="s">
         <v>10</v>
@@ -1479,16 +1482,16 @@
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C31">
         <v>5727</v>
       </c>
       <c r="D31" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F31" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G31" t="s">
         <v>10</v>
@@ -1508,16 +1511,16 @@
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C32">
         <v>5725</v>
       </c>
       <c r="D32" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F32" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G32" t="s">
         <v>10</v>
@@ -1537,16 +1540,16 @@
     </row>
     <row r="33" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C33">
         <v>5709</v>
       </c>
       <c r="D33" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F33" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G33" t="s">
         <v>13</v>
@@ -1566,16 +1569,16 @@
     </row>
     <row r="34" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C34">
         <v>5736</v>
       </c>
       <c r="D34" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F34" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G34" t="s">
         <v>10</v>
@@ -1595,16 +1598,16 @@
     </row>
     <row r="35" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C35">
         <v>5682</v>
       </c>
       <c r="D35" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F35" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G35" t="s">
         <v>10</v>
@@ -1624,16 +1627,16 @@
     </row>
     <row r="36" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C36">
         <v>5729</v>
       </c>
       <c r="D36" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F36" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G36" t="s">
         <v>10</v>
@@ -1653,16 +1656,16 @@
     </row>
     <row r="37" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C37">
         <v>5696</v>
       </c>
       <c r="D37" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F37" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G37" t="s">
         <v>13</v>
@@ -1682,16 +1685,16 @@
     </row>
     <row r="38" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C38">
         <v>5716</v>
       </c>
       <c r="D38" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F38" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G38" t="s">
         <v>10</v>
@@ -1711,16 +1714,16 @@
     </row>
     <row r="39" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C39">
         <v>5720</v>
       </c>
       <c r="D39" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F39" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G39" t="s">
         <v>10</v>
@@ -1740,16 +1743,16 @@
     </row>
     <row r="40" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C40">
         <v>5679</v>
       </c>
       <c r="D40" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F40" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G40" t="s">
         <v>14</v>
@@ -1777,16 +1780,16 @@
     </row>
     <row r="42" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C42">
         <v>5711</v>
       </c>
       <c r="D42" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F42" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G42" t="s">
         <v>10</v>
@@ -1806,16 +1809,16 @@
     </row>
     <row r="43" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C43">
         <v>5732</v>
       </c>
       <c r="D43" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F43" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G43" t="s">
         <v>10</v>
@@ -1835,16 +1838,16 @@
     </row>
     <row r="44" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C44">
         <v>5739</v>
       </c>
       <c r="D44" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F44" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G44" t="s">
         <v>12</v>
@@ -1872,16 +1875,16 @@
     </row>
     <row r="46" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C46">
         <v>5710</v>
       </c>
       <c r="D46" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F46" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G46" t="s">
         <v>10</v>
@@ -1901,16 +1904,16 @@
     </row>
     <row r="47" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C47">
         <v>5746</v>
       </c>
       <c r="D47" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F47" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G47" t="s">
         <v>13</v>
@@ -1930,16 +1933,16 @@
     </row>
     <row r="48" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C48">
         <v>5702</v>
       </c>
       <c r="D48" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F48" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G48" t="s">
         <v>10</v>
@@ -1959,16 +1962,16 @@
     </row>
     <row r="49" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C49">
         <v>5728</v>
       </c>
       <c r="D49" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F49" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G49" t="s">
         <v>13</v>
@@ -1988,16 +1991,16 @@
     </row>
     <row r="50" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C50">
         <v>5683</v>
       </c>
       <c r="D50" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F50" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G50" t="s">
         <v>13</v>
@@ -2017,16 +2020,16 @@
     </row>
     <row r="51" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C51">
         <v>5745</v>
       </c>
       <c r="D51" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F51" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G51" t="s">
         <v>10</v>
@@ -2046,16 +2049,16 @@
     </row>
     <row r="52" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C52">
         <v>5733</v>
       </c>
       <c r="D52" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F52" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G52" t="s">
         <v>13</v>
@@ -2075,16 +2078,16 @@
     </row>
     <row r="53" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C53">
         <v>5704</v>
       </c>
       <c r="D53" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F53" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G53" t="s">
         <v>10</v>
@@ -2104,16 +2107,16 @@
     </row>
     <row r="54" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C54">
         <v>5693</v>
       </c>
       <c r="D54" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F54" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G54" t="s">
         <v>10</v>
@@ -2133,16 +2136,16 @@
     </row>
     <row r="55" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C55">
         <v>5718</v>
       </c>
       <c r="D55" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F55" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G55" t="s">
         <v>10</v>
@@ -2162,16 +2165,16 @@
     </row>
     <row r="56" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C56">
         <v>5700</v>
       </c>
       <c r="D56" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F56" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G56" t="s">
         <v>13</v>
@@ -2191,16 +2194,16 @@
     </row>
     <row r="57" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C57">
         <v>5726</v>
       </c>
       <c r="D57" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F57" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G57" t="s">
         <v>10</v>
@@ -2220,16 +2223,16 @@
     </row>
     <row r="58" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C58">
         <v>5684</v>
       </c>
       <c r="D58" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F58" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G58" t="s">
         <v>13</v>
@@ -2249,16 +2252,16 @@
     </row>
     <row r="59" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C59">
         <v>5740</v>
       </c>
       <c r="D59" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F59" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G59" t="s">
         <v>10</v>
@@ -2278,16 +2281,16 @@
     </row>
     <row r="60" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C60">
         <v>5701</v>
       </c>
       <c r="D60" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F60" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G60" t="s">
         <v>10</v>
@@ -2307,16 +2310,16 @@
     </row>
     <row r="61" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C61">
         <v>5695</v>
       </c>
       <c r="D61" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F61" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G61" t="s">
         <v>10</v>
@@ -2336,16 +2339,16 @@
     </row>
     <row r="62" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C62">
         <v>5690</v>
       </c>
       <c r="D62" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F62" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G62" t="s">
         <v>10</v>
@@ -2365,16 +2368,16 @@
     </row>
     <row r="63" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C63">
         <v>5697</v>
       </c>
       <c r="D63" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F63" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G63" t="s">
         <v>13</v>
@@ -2394,16 +2397,16 @@
     </row>
     <row r="64" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B64" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C64">
         <v>5744</v>
       </c>
       <c r="D64" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F64" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G64" t="s">
         <v>14</v>
@@ -2431,16 +2434,16 @@
     </row>
     <row r="66" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B66" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C66">
         <v>5738</v>
       </c>
       <c r="D66" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F66" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G66" t="s">
         <v>12</v>
@@ -2468,16 +2471,16 @@
     </row>
     <row r="68" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B68" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C68">
         <v>5691</v>
       </c>
       <c r="D68" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F68" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G68" t="s">
         <v>13</v>
@@ -2497,16 +2500,16 @@
     </row>
     <row r="69" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C69">
         <v>5699</v>
       </c>
       <c r="D69" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F69" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G69" t="s">
         <v>13</v>
@@ -2526,16 +2529,16 @@
     </row>
     <row r="70" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B70" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C70">
         <v>5694</v>
       </c>
       <c r="D70" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F70" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G70" t="s">
         <v>13</v>
@@ -2555,16 +2558,16 @@
     </row>
     <row r="71" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B71" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C71">
         <v>5730</v>
       </c>
       <c r="D71" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F71" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G71" t="s">
         <v>13</v>
@@ -2584,16 +2587,16 @@
     </row>
     <row r="72" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B72" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C72">
         <v>5681</v>
       </c>
       <c r="D72" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F72" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G72" t="s">
         <v>13</v>
@@ -2613,16 +2616,16 @@
     </row>
     <row r="73" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B73" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C73">
         <v>5735</v>
       </c>
       <c r="D73" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F73" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G73" t="s">
         <v>13</v>
@@ -2642,16 +2645,16 @@
     </row>
     <row r="74" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C74">
         <v>5692</v>
       </c>
       <c r="D74" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F74" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G74" t="s">
         <v>13</v>
@@ -2671,16 +2674,16 @@
     </row>
     <row r="75" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B75" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C75">
         <v>5703</v>
       </c>
       <c r="D75" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F75" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G75" t="s">
         <v>10</v>
@@ -2700,16 +2703,16 @@
     </row>
     <row r="76" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B76" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C76">
         <v>5708</v>
       </c>
       <c r="D76" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F76" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G76" t="s">
         <v>10</v>
@@ -2729,16 +2732,16 @@
     </row>
     <row r="77" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B77" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C77">
         <v>5712</v>
       </c>
       <c r="D77" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F77" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G77" t="s">
         <v>10</v>
@@ -2758,16 +2761,16 @@
     </row>
     <row r="78" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B78" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C78">
         <v>5734</v>
       </c>
       <c r="D78" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F78" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G78" t="s">
         <v>13</v>
@@ -2787,16 +2790,16 @@
     </row>
     <row r="79" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B79" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C79">
         <v>5743</v>
       </c>
       <c r="D79" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F79" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G79" t="s">
         <v>10</v>
@@ -2816,16 +2819,16 @@
     </row>
     <row r="80" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B80" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C80">
         <v>5742</v>
       </c>
       <c r="D80" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F80" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G80" t="s">
         <v>13</v>
@@ -2845,16 +2848,16 @@
     </row>
     <row r="81" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B81" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C81">
         <v>5723</v>
       </c>
       <c r="D81" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F81" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G81" t="s">
         <v>10</v>
@@ -2874,16 +2877,16 @@
     </row>
     <row r="82" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C82">
         <v>5706</v>
       </c>
       <c r="D82" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F82" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G82" t="s">
         <v>13</v>
@@ -2903,16 +2906,16 @@
     </row>
     <row r="83" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B83" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C83">
         <v>5670</v>
       </c>
       <c r="D83" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F83" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G83" t="s">
         <v>10</v>
@@ -2932,16 +2935,16 @@
     </row>
     <row r="84" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B84" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C84">
         <v>5677</v>
       </c>
       <c r="D84" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F84" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G84" t="s">
         <v>10</v>
@@ -2961,16 +2964,16 @@
     </row>
     <row r="85" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B85" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C85">
         <v>5685</v>
       </c>
       <c r="D85" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F85" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G85" t="s">
         <v>10</v>
@@ -2990,16 +2993,16 @@
     </row>
     <row r="86" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B86" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C86">
         <v>5719</v>
       </c>
       <c r="D86" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F86" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G86" t="s">
         <v>10</v>
@@ -3019,16 +3022,16 @@
     </row>
     <row r="87" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B87" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C87">
         <v>5747</v>
       </c>
       <c r="D87" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F87" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G87" t="s">
         <v>10</v>
@@ -3048,16 +3051,16 @@
     </row>
     <row r="88" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B88" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C88">
         <v>5714</v>
       </c>
       <c r="D88" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F88" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G88" t="s">
         <v>10</v>
@@ -3077,16 +3080,16 @@
     </row>
     <row r="89" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B89" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C89">
         <v>5669</v>
       </c>
       <c r="D89" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F89" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G89" t="s">
         <v>12</v>
@@ -3114,16 +3117,16 @@
     </row>
     <row r="91" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B91" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C91">
         <v>5675</v>
       </c>
       <c r="D91" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F91" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G91" t="s">
         <v>10</v>
@@ -3143,16 +3146,16 @@
     </row>
     <row r="92" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B92" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C92">
         <v>5689</v>
       </c>
       <c r="D92" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F92" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G92" t="s">
         <v>10</v>
@@ -3172,16 +3175,16 @@
     </row>
     <row r="93" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B93" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C93">
         <v>5682</v>
       </c>
       <c r="D93" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F93" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G93" t="s">
         <v>10</v>
@@ -3201,16 +3204,16 @@
     </row>
     <row r="94" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B94" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C94">
         <v>5732</v>
       </c>
       <c r="D94" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F94" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G94" t="s">
         <v>13</v>
@@ -3230,16 +3233,16 @@
     </row>
     <row r="95" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B95" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C95">
         <v>5702</v>
       </c>
       <c r="D95" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F95" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G95" t="s">
         <v>10</v>
@@ -3259,16 +3262,16 @@
     </row>
     <row r="96" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B96" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C96">
         <v>5701</v>
       </c>
       <c r="D96" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F96" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G96" t="s">
         <v>10</v>
@@ -3288,16 +3291,16 @@
     </row>
     <row r="97" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B97" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C97">
         <v>5708</v>
       </c>
       <c r="D97" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F97" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G97" t="s">
         <v>10</v>
@@ -3317,16 +3320,16 @@
     </row>
     <row r="98" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B98" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C98">
         <v>5670</v>
       </c>
       <c r="D98" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F98" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G98" t="s">
         <v>10</v>
@@ -3346,16 +3349,16 @@
     </row>
     <row r="99" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B99" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C99">
         <v>5719</v>
       </c>
       <c r="D99" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F99" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G99" t="s">
         <v>14</v>
@@ -3383,16 +3386,16 @@
     </row>
     <row r="101" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B101" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C101">
         <v>6002</v>
       </c>
       <c r="D101" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F101" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G101" t="s">
         <v>10</v>
@@ -3411,546 +3414,2285 @@
       </c>
     </row>
     <row r="102" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H102" s="2"/>
-      <c r="I102" s="1"/>
-      <c r="J102" s="2"/>
-      <c r="K102" s="1"/>
+      <c r="B102" t="s">
+        <v>19</v>
+      </c>
+      <c r="C102">
+        <v>5717</v>
+      </c>
+      <c r="D102" t="s">
+        <v>22</v>
+      </c>
+      <c r="F102" t="s">
+        <v>16</v>
+      </c>
+      <c r="G102" t="s">
+        <v>10</v>
+      </c>
+      <c r="H102" s="2">
+        <v>6.6550925925925927E-3</v>
+      </c>
+      <c r="I102" s="1">
+        <v>46237.840277777781</v>
+      </c>
+      <c r="J102" s="2">
+        <v>0</v>
+      </c>
+      <c r="K102" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="103" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H103" s="2"/>
-      <c r="I103" s="1"/>
-      <c r="J103" s="2"/>
-      <c r="K103" s="1"/>
+      <c r="B103" t="s">
+        <v>19</v>
+      </c>
+      <c r="C103">
+        <v>5747</v>
+      </c>
+      <c r="D103" t="s">
+        <v>23</v>
+      </c>
+      <c r="F103" t="s">
+        <v>16</v>
+      </c>
+      <c r="G103" t="s">
+        <v>12</v>
+      </c>
+      <c r="H103" s="2">
+        <v>2.650462962962963E-3</v>
+      </c>
+      <c r="I103" s="1">
+        <v>46237.84097222222</v>
+      </c>
+      <c r="J103" s="2">
+        <v>0</v>
+      </c>
+      <c r="K103" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="104" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H104" s="2"/>
       <c r="I104" s="1"/>
       <c r="J104" s="2"/>
-      <c r="K104" s="1"/>
+      <c r="K104" s="1" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="105" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H105" s="2"/>
-      <c r="I105" s="1"/>
-      <c r="J105" s="2"/>
-      <c r="K105" s="1"/>
+      <c r="B105" t="s">
+        <v>19</v>
+      </c>
+      <c r="C105">
+        <v>5715</v>
+      </c>
+      <c r="D105" t="s">
+        <v>24</v>
+      </c>
+      <c r="F105" t="s">
+        <v>16</v>
+      </c>
+      <c r="G105" t="s">
+        <v>10</v>
+      </c>
+      <c r="H105" s="2">
+        <v>8.3564814814814821E-3</v>
+      </c>
+      <c r="I105" s="1">
+        <v>46237.841666666667</v>
+      </c>
+      <c r="J105" s="2">
+        <v>0</v>
+      </c>
+      <c r="K105" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="106" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H106" s="2"/>
-      <c r="I106" s="1"/>
-      <c r="J106" s="2"/>
-      <c r="K106" s="1"/>
+      <c r="B106" t="s">
+        <v>19</v>
+      </c>
+      <c r="C106">
+        <v>5731</v>
+      </c>
+      <c r="D106" t="s">
+        <v>25</v>
+      </c>
+      <c r="F106" t="s">
+        <v>16</v>
+      </c>
+      <c r="G106" t="s">
+        <v>13</v>
+      </c>
+      <c r="H106" s="2">
+        <v>0</v>
+      </c>
+      <c r="I106" s="1">
+        <v>46237.841666666667</v>
+      </c>
+      <c r="J106" s="2">
+        <v>0</v>
+      </c>
+      <c r="K106" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="107" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H107" s="2"/>
-      <c r="I107" s="1"/>
-      <c r="J107" s="2"/>
-      <c r="K107" s="1"/>
+      <c r="B107" t="s">
+        <v>19</v>
+      </c>
+      <c r="C107">
+        <v>5741</v>
+      </c>
+      <c r="D107" t="s">
+        <v>26</v>
+      </c>
+      <c r="F107" t="s">
+        <v>16</v>
+      </c>
+      <c r="G107" t="s">
+        <v>10</v>
+      </c>
+      <c r="H107" s="2">
+        <v>5.8333333333333336E-3</v>
+      </c>
+      <c r="I107" s="1">
+        <v>46237.842361111114</v>
+      </c>
+      <c r="J107" s="2">
+        <v>0</v>
+      </c>
+      <c r="K107" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="108" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H108" s="2"/>
-      <c r="I108" s="1"/>
-      <c r="J108" s="2"/>
-      <c r="K108" s="1"/>
+      <c r="B108" t="s">
+        <v>19</v>
+      </c>
+      <c r="C108">
+        <v>5688</v>
+      </c>
+      <c r="D108" t="s">
+        <v>27</v>
+      </c>
+      <c r="F108" t="s">
+        <v>16</v>
+      </c>
+      <c r="G108" t="s">
+        <v>13</v>
+      </c>
+      <c r="H108" s="2">
+        <v>0</v>
+      </c>
+      <c r="I108" s="1">
+        <v>46237.843055555553</v>
+      </c>
+      <c r="J108" s="2">
+        <v>0</v>
+      </c>
+      <c r="K108" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="109" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H109" s="2"/>
-      <c r="I109" s="1"/>
-      <c r="J109" s="2"/>
-      <c r="K109" s="1"/>
+      <c r="B109" t="s">
+        <v>19</v>
+      </c>
+      <c r="C109">
+        <v>5678</v>
+      </c>
+      <c r="D109" t="s">
+        <v>28</v>
+      </c>
+      <c r="F109" t="s">
+        <v>16</v>
+      </c>
+      <c r="G109" t="s">
+        <v>10</v>
+      </c>
+      <c r="H109" s="2">
+        <v>9.4560185185185181E-3</v>
+      </c>
+      <c r="I109" s="1">
+        <v>46237.843055555553</v>
+      </c>
+      <c r="J109" s="2">
+        <v>0</v>
+      </c>
+      <c r="K109" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="110" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H110" s="2"/>
-      <c r="I110" s="1"/>
-      <c r="J110" s="2"/>
-      <c r="K110" s="1"/>
+      <c r="B110" t="s">
+        <v>19</v>
+      </c>
+      <c r="C110">
+        <v>5676</v>
+      </c>
+      <c r="D110" t="s">
+        <v>29</v>
+      </c>
+      <c r="F110" t="s">
+        <v>16</v>
+      </c>
+      <c r="G110" t="s">
+        <v>10</v>
+      </c>
+      <c r="H110" s="2">
+        <v>5.4166666666666669E-3</v>
+      </c>
+      <c r="I110" s="1">
+        <v>46237.84375</v>
+      </c>
+      <c r="J110" s="2">
+        <v>0</v>
+      </c>
+      <c r="K110" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="111" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H111" s="2"/>
-      <c r="I111" s="1"/>
-      <c r="J111" s="2"/>
-      <c r="K111" s="1"/>
+      <c r="B111" t="s">
+        <v>19</v>
+      </c>
+      <c r="C111">
+        <v>5686</v>
+      </c>
+      <c r="D111" t="s">
+        <v>30</v>
+      </c>
+      <c r="F111" t="s">
+        <v>16</v>
+      </c>
+      <c r="G111" t="s">
+        <v>13</v>
+      </c>
+      <c r="H111" s="2">
+        <v>0</v>
+      </c>
+      <c r="I111" s="1">
+        <v>46237.844444444447</v>
+      </c>
+      <c r="J111" s="2">
+        <v>0</v>
+      </c>
+      <c r="K111" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="112" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H112" s="2"/>
-      <c r="I112" s="1"/>
-      <c r="J112" s="2"/>
-      <c r="K112" s="1"/>
-    </row>
-    <row r="113" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H113" s="2"/>
-      <c r="I113" s="1"/>
-      <c r="J113" s="2"/>
-      <c r="K113" s="1"/>
-    </row>
-    <row r="114" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H114" s="2"/>
-      <c r="I114" s="1"/>
-      <c r="J114" s="2"/>
-      <c r="K114" s="1"/>
-    </row>
-    <row r="115" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H115" s="2"/>
-      <c r="I115" s="1"/>
-      <c r="J115" s="2"/>
-      <c r="K115" s="1"/>
-    </row>
-    <row r="116" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H116" s="2"/>
-      <c r="I116" s="1"/>
-      <c r="J116" s="2"/>
-      <c r="K116" s="1"/>
-    </row>
-    <row r="117" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="B112" t="s">
+        <v>19</v>
+      </c>
+      <c r="C112">
+        <v>5714</v>
+      </c>
+      <c r="D112" t="s">
+        <v>31</v>
+      </c>
+      <c r="F112" t="s">
+        <v>16</v>
+      </c>
+      <c r="G112" t="s">
+        <v>10</v>
+      </c>
+      <c r="H112" s="2">
+        <v>5.8564814814814816E-3</v>
+      </c>
+      <c r="I112" s="1">
+        <v>46237.844444444447</v>
+      </c>
+      <c r="J112" s="2">
+        <v>0</v>
+      </c>
+      <c r="K112" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="113" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B113" t="s">
+        <v>19</v>
+      </c>
+      <c r="C113">
+        <v>5705</v>
+      </c>
+      <c r="D113" t="s">
+        <v>32</v>
+      </c>
+      <c r="F113" t="s">
+        <v>16</v>
+      </c>
+      <c r="G113" t="s">
+        <v>10</v>
+      </c>
+      <c r="H113" s="2">
+        <v>1.3055555555555556E-2</v>
+      </c>
+      <c r="I113" s="1">
+        <v>46237.845138888886</v>
+      </c>
+      <c r="J113" s="2">
+        <v>0</v>
+      </c>
+      <c r="K113" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="114" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B114" t="s">
+        <v>19</v>
+      </c>
+      <c r="C114">
+        <v>5669</v>
+      </c>
+      <c r="D114" t="s">
+        <v>20</v>
+      </c>
+      <c r="F114" t="s">
+        <v>16</v>
+      </c>
+      <c r="G114" t="s">
+        <v>13</v>
+      </c>
+      <c r="H114" s="2">
+        <v>0</v>
+      </c>
+      <c r="I114" s="1">
+        <v>46237.845833333333</v>
+      </c>
+      <c r="J114" s="2">
+        <v>0</v>
+      </c>
+      <c r="K114" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="115" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B115" t="s">
+        <v>19</v>
+      </c>
+      <c r="C115">
+        <v>5675</v>
+      </c>
+      <c r="D115" t="s">
+        <v>33</v>
+      </c>
+      <c r="F115" t="s">
+        <v>16</v>
+      </c>
+      <c r="G115" t="s">
+        <v>10</v>
+      </c>
+      <c r="H115" s="2">
+        <v>1.119212962962963E-2</v>
+      </c>
+      <c r="I115" s="1">
+        <v>46237.84652777778</v>
+      </c>
+      <c r="J115" s="2">
+        <v>0</v>
+      </c>
+      <c r="K115" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="116" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B116" t="s">
+        <v>19</v>
+      </c>
+      <c r="C116">
+        <v>5707</v>
+      </c>
+      <c r="D116" t="s">
+        <v>34</v>
+      </c>
+      <c r="F116" t="s">
+        <v>16</v>
+      </c>
+      <c r="G116" t="s">
+        <v>12</v>
+      </c>
+      <c r="H116" s="2">
+        <v>1.9675925925925924E-3</v>
+      </c>
+      <c r="I116" s="1">
+        <v>46237.84652777778</v>
+      </c>
+      <c r="J116" s="2">
+        <v>0</v>
+      </c>
+      <c r="K116" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="117" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H117" s="2"/>
       <c r="I117" s="1"/>
       <c r="J117" s="2"/>
-      <c r="K117" s="1"/>
-    </row>
-    <row r="118" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H118" s="2"/>
-      <c r="I118" s="1"/>
-      <c r="J118" s="2"/>
-      <c r="K118" s="1"/>
-    </row>
-    <row r="119" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="K117" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="118" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B118" t="s">
+        <v>19</v>
+      </c>
+      <c r="C118">
+        <v>5722</v>
+      </c>
+      <c r="D118" t="s">
+        <v>35</v>
+      </c>
+      <c r="F118" t="s">
+        <v>16</v>
+      </c>
+      <c r="G118" t="s">
+        <v>12</v>
+      </c>
+      <c r="H118" s="2">
+        <v>2.0833333333333335E-4</v>
+      </c>
+      <c r="I118" s="1">
+        <v>46237.847222222219</v>
+      </c>
+      <c r="J118" s="2">
+        <v>0</v>
+      </c>
+      <c r="K118" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="119" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H119" s="2"/>
       <c r="I119" s="1"/>
       <c r="J119" s="2"/>
-      <c r="K119" s="1"/>
-    </row>
-    <row r="120" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H120" s="2"/>
-      <c r="I120" s="1"/>
-      <c r="J120" s="2"/>
-      <c r="K120" s="1"/>
-    </row>
-    <row r="121" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H121" s="2"/>
-      <c r="I121" s="1"/>
-      <c r="J121" s="2"/>
-      <c r="K121" s="1"/>
-    </row>
-    <row r="122" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H122" s="2"/>
-      <c r="I122" s="1"/>
-      <c r="J122" s="2"/>
-      <c r="K122" s="1"/>
-    </row>
-    <row r="123" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H123" s="2"/>
-      <c r="I123" s="1"/>
-      <c r="J123" s="2"/>
-      <c r="K123" s="1"/>
-    </row>
-    <row r="124" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H124" s="2"/>
-      <c r="I124" s="1"/>
-      <c r="J124" s="2"/>
-      <c r="K124" s="1"/>
-    </row>
-    <row r="125" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H125" s="2"/>
-      <c r="I125" s="1"/>
-      <c r="J125" s="2"/>
-      <c r="K125" s="1"/>
-    </row>
-    <row r="126" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H126" s="2"/>
-      <c r="I126" s="1"/>
-      <c r="J126" s="2"/>
-      <c r="K126" s="1"/>
-    </row>
-    <row r="127" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H127" s="2"/>
-      <c r="I127" s="1"/>
-      <c r="J127" s="2"/>
-      <c r="K127" s="1"/>
-    </row>
-    <row r="128" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H128" s="2"/>
-      <c r="I128" s="1"/>
-      <c r="J128" s="2"/>
-      <c r="K128" s="1"/>
-    </row>
-    <row r="129" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H129" s="2"/>
-      <c r="I129" s="1"/>
-      <c r="J129" s="2"/>
-      <c r="K129" s="1"/>
-    </row>
-    <row r="130" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H130" s="2"/>
-      <c r="I130" s="1"/>
-      <c r="J130" s="2"/>
-      <c r="K130" s="1"/>
-    </row>
-    <row r="131" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H131" s="2"/>
-      <c r="I131" s="1"/>
-      <c r="J131" s="2"/>
-      <c r="K131" s="1"/>
-    </row>
-    <row r="132" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H132" s="2"/>
-      <c r="I132" s="1"/>
-      <c r="J132" s="2"/>
-      <c r="K132" s="1"/>
-    </row>
-    <row r="133" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H133" s="2"/>
-      <c r="I133" s="1"/>
-      <c r="J133" s="2"/>
-      <c r="K133" s="1"/>
-    </row>
-    <row r="134" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H134" s="2"/>
-      <c r="I134" s="1"/>
-      <c r="J134" s="2"/>
-      <c r="K134" s="1"/>
-    </row>
-    <row r="135" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H135" s="2"/>
-      <c r="I135" s="1"/>
-      <c r="J135" s="2"/>
-      <c r="K135" s="1"/>
-    </row>
-    <row r="136" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H136" s="2"/>
-      <c r="I136" s="1"/>
-      <c r="J136" s="2"/>
-      <c r="K136" s="1"/>
-    </row>
-    <row r="137" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H137" s="2"/>
-      <c r="I137" s="1"/>
-      <c r="J137" s="2"/>
-      <c r="K137" s="1"/>
-    </row>
-    <row r="138" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H138" s="2"/>
-      <c r="I138" s="1"/>
-      <c r="J138" s="2"/>
-      <c r="K138" s="1"/>
-    </row>
-    <row r="139" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="K119" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="120" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B120" t="s">
+        <v>19</v>
+      </c>
+      <c r="C120">
+        <v>5737</v>
+      </c>
+      <c r="D120" t="s">
+        <v>36</v>
+      </c>
+      <c r="F120" t="s">
+        <v>16</v>
+      </c>
+      <c r="G120" t="s">
+        <v>13</v>
+      </c>
+      <c r="H120" s="2">
+        <v>0</v>
+      </c>
+      <c r="I120" s="1">
+        <v>46237.847916666666</v>
+      </c>
+      <c r="J120" s="2">
+        <v>0</v>
+      </c>
+      <c r="K120" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="121" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B121" t="s">
+        <v>19</v>
+      </c>
+      <c r="C121">
+        <v>5698</v>
+      </c>
+      <c r="D121" t="s">
+        <v>37</v>
+      </c>
+      <c r="F121" t="s">
+        <v>16</v>
+      </c>
+      <c r="G121" t="s">
+        <v>13</v>
+      </c>
+      <c r="H121" s="2">
+        <v>0</v>
+      </c>
+      <c r="I121" s="1">
+        <v>46237.847916666666</v>
+      </c>
+      <c r="J121" s="2">
+        <v>0</v>
+      </c>
+      <c r="K121" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="122" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B122" t="s">
+        <v>19</v>
+      </c>
+      <c r="C122">
+        <v>5713</v>
+      </c>
+      <c r="D122" t="s">
+        <v>38</v>
+      </c>
+      <c r="F122" t="s">
+        <v>16</v>
+      </c>
+      <c r="G122" t="s">
+        <v>13</v>
+      </c>
+      <c r="H122" s="2">
+        <v>0</v>
+      </c>
+      <c r="I122" s="1">
+        <v>46237.848611111112</v>
+      </c>
+      <c r="J122" s="2">
+        <v>0</v>
+      </c>
+      <c r="K122" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="123" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B123" t="s">
+        <v>19</v>
+      </c>
+      <c r="C123">
+        <v>5721</v>
+      </c>
+      <c r="D123" t="s">
+        <v>39</v>
+      </c>
+      <c r="F123" t="s">
+        <v>16</v>
+      </c>
+      <c r="G123" t="s">
+        <v>13</v>
+      </c>
+      <c r="H123" s="2">
+        <v>0</v>
+      </c>
+      <c r="I123" s="1">
+        <v>46237.849305555559</v>
+      </c>
+      <c r="J123" s="2">
+        <v>0</v>
+      </c>
+      <c r="K123" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="124" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B124" t="s">
+        <v>19</v>
+      </c>
+      <c r="C124">
+        <v>5680</v>
+      </c>
+      <c r="D124" t="s">
+        <v>40</v>
+      </c>
+      <c r="F124" t="s">
+        <v>16</v>
+      </c>
+      <c r="G124" t="s">
+        <v>13</v>
+      </c>
+      <c r="H124" s="2">
+        <v>0</v>
+      </c>
+      <c r="I124" s="1">
+        <v>46237.849305555559</v>
+      </c>
+      <c r="J124" s="2">
+        <v>0</v>
+      </c>
+      <c r="K124" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="125" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B125" t="s">
+        <v>19</v>
+      </c>
+      <c r="C125">
+        <v>5689</v>
+      </c>
+      <c r="D125" t="s">
+        <v>41</v>
+      </c>
+      <c r="F125" t="s">
+        <v>16</v>
+      </c>
+      <c r="G125" t="s">
+        <v>10</v>
+      </c>
+      <c r="H125" s="2">
+        <v>6.828703703703704E-3</v>
+      </c>
+      <c r="I125" s="1">
+        <v>46237.85</v>
+      </c>
+      <c r="J125" s="2">
+        <v>0</v>
+      </c>
+      <c r="K125" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="126" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B126" t="s">
+        <v>19</v>
+      </c>
+      <c r="C126">
+        <v>5687</v>
+      </c>
+      <c r="D126" t="s">
+        <v>42</v>
+      </c>
+      <c r="F126" t="s">
+        <v>16</v>
+      </c>
+      <c r="G126" t="s">
+        <v>13</v>
+      </c>
+      <c r="H126" s="2">
+        <v>0</v>
+      </c>
+      <c r="I126" s="1">
+        <v>46237.85</v>
+      </c>
+      <c r="J126" s="2">
+        <v>0</v>
+      </c>
+      <c r="K126" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="127" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B127" t="s">
+        <v>19</v>
+      </c>
+      <c r="C127">
+        <v>5727</v>
+      </c>
+      <c r="D127" t="s">
+        <v>43</v>
+      </c>
+      <c r="F127" t="s">
+        <v>16</v>
+      </c>
+      <c r="G127" t="s">
+        <v>10</v>
+      </c>
+      <c r="H127" s="2">
+        <v>7.4189814814814813E-3</v>
+      </c>
+      <c r="I127" s="1">
+        <v>46237.850694444445</v>
+      </c>
+      <c r="J127" s="2">
+        <v>0</v>
+      </c>
+      <c r="K127" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="128" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B128" t="s">
+        <v>19</v>
+      </c>
+      <c r="C128">
+        <v>5725</v>
+      </c>
+      <c r="D128" t="s">
+        <v>44</v>
+      </c>
+      <c r="F128" t="s">
+        <v>16</v>
+      </c>
+      <c r="G128" t="s">
+        <v>10</v>
+      </c>
+      <c r="H128" s="2">
+        <v>5.5439814814814813E-3</v>
+      </c>
+      <c r="I128" s="1">
+        <v>46237.851388888892</v>
+      </c>
+      <c r="J128" s="2">
+        <v>0</v>
+      </c>
+      <c r="K128" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="129" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B129" t="s">
+        <v>19</v>
+      </c>
+      <c r="C129">
+        <v>5709</v>
+      </c>
+      <c r="D129" t="s">
+        <v>45</v>
+      </c>
+      <c r="F129" t="s">
+        <v>16</v>
+      </c>
+      <c r="G129" t="s">
+        <v>13</v>
+      </c>
+      <c r="H129" s="2">
+        <v>0</v>
+      </c>
+      <c r="I129" s="1">
+        <v>46237.852083333331</v>
+      </c>
+      <c r="J129" s="2">
+        <v>0</v>
+      </c>
+      <c r="K129" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="130" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B130" t="s">
+        <v>19</v>
+      </c>
+      <c r="C130">
+        <v>5736</v>
+      </c>
+      <c r="D130" t="s">
+        <v>46</v>
+      </c>
+      <c r="F130" t="s">
+        <v>16</v>
+      </c>
+      <c r="G130" t="s">
+        <v>10</v>
+      </c>
+      <c r="H130" s="2">
+        <v>5.8333333333333336E-3</v>
+      </c>
+      <c r="I130" s="1">
+        <v>46237.852083333331</v>
+      </c>
+      <c r="J130" s="2">
+        <v>0</v>
+      </c>
+      <c r="K130" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="131" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B131" t="s">
+        <v>19</v>
+      </c>
+      <c r="C131">
+        <v>5682</v>
+      </c>
+      <c r="D131" t="s">
+        <v>47</v>
+      </c>
+      <c r="F131" t="s">
+        <v>16</v>
+      </c>
+      <c r="G131" t="s">
+        <v>13</v>
+      </c>
+      <c r="H131" s="2">
+        <v>0</v>
+      </c>
+      <c r="I131" s="1">
+        <v>46237.852777777778</v>
+      </c>
+      <c r="J131" s="2">
+        <v>0</v>
+      </c>
+      <c r="K131" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="132" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B132" t="s">
+        <v>19</v>
+      </c>
+      <c r="C132">
+        <v>5729</v>
+      </c>
+      <c r="D132" t="s">
+        <v>48</v>
+      </c>
+      <c r="F132" t="s">
+        <v>16</v>
+      </c>
+      <c r="G132" t="s">
+        <v>10</v>
+      </c>
+      <c r="H132" s="2">
+        <v>1.4988425925925926E-2</v>
+      </c>
+      <c r="I132" s="1">
+        <v>46237.853472222225</v>
+      </c>
+      <c r="J132" s="2">
+        <v>0</v>
+      </c>
+      <c r="K132" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="133" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B133" t="s">
+        <v>19</v>
+      </c>
+      <c r="C133">
+        <v>5696</v>
+      </c>
+      <c r="D133" t="s">
+        <v>49</v>
+      </c>
+      <c r="F133" t="s">
+        <v>16</v>
+      </c>
+      <c r="G133" t="s">
+        <v>13</v>
+      </c>
+      <c r="H133" s="2">
+        <v>0</v>
+      </c>
+      <c r="I133" s="1">
+        <v>46237.853472222225</v>
+      </c>
+      <c r="J133" s="2">
+        <v>0</v>
+      </c>
+      <c r="K133" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="134" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B134" t="s">
+        <v>19</v>
+      </c>
+      <c r="C134">
+        <v>5716</v>
+      </c>
+      <c r="D134" t="s">
+        <v>50</v>
+      </c>
+      <c r="F134" t="s">
+        <v>16</v>
+      </c>
+      <c r="G134" t="s">
+        <v>10</v>
+      </c>
+      <c r="H134" s="2">
+        <v>8.9004629629629625E-3</v>
+      </c>
+      <c r="I134" s="1">
+        <v>46237.854166666664</v>
+      </c>
+      <c r="J134" s="2">
+        <v>0</v>
+      </c>
+      <c r="K134" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="135" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B135" t="s">
+        <v>19</v>
+      </c>
+      <c r="C135">
+        <v>5720</v>
+      </c>
+      <c r="D135" t="s">
+        <v>51</v>
+      </c>
+      <c r="F135" t="s">
+        <v>16</v>
+      </c>
+      <c r="G135" t="s">
+        <v>13</v>
+      </c>
+      <c r="H135" s="2">
+        <v>0</v>
+      </c>
+      <c r="I135" s="1">
+        <v>46237.854861111111</v>
+      </c>
+      <c r="J135" s="2">
+        <v>0</v>
+      </c>
+      <c r="K135" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="136" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B136" t="s">
+        <v>19</v>
+      </c>
+      <c r="C136">
+        <v>5679</v>
+      </c>
+      <c r="D136" t="s">
+        <v>52</v>
+      </c>
+      <c r="F136" t="s">
+        <v>16</v>
+      </c>
+      <c r="G136" t="s">
+        <v>13</v>
+      </c>
+      <c r="H136" s="2">
+        <v>0</v>
+      </c>
+      <c r="I136" s="1">
+        <v>46237.854861111111</v>
+      </c>
+      <c r="J136" s="2">
+        <v>0</v>
+      </c>
+      <c r="K136" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="137" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B137" t="s">
+        <v>19</v>
+      </c>
+      <c r="C137">
+        <v>5711</v>
+      </c>
+      <c r="D137" t="s">
+        <v>53</v>
+      </c>
+      <c r="F137" t="s">
+        <v>16</v>
+      </c>
+      <c r="G137" t="s">
+        <v>10</v>
+      </c>
+      <c r="H137" s="2">
+        <v>6.2268518518518515E-3</v>
+      </c>
+      <c r="I137" s="1">
+        <v>46237.855555555558</v>
+      </c>
+      <c r="J137" s="2">
+        <v>0</v>
+      </c>
+      <c r="K137" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="138" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B138" t="s">
+        <v>19</v>
+      </c>
+      <c r="C138">
+        <v>5732</v>
+      </c>
+      <c r="D138" t="s">
+        <v>54</v>
+      </c>
+      <c r="F138" t="s">
+        <v>16</v>
+      </c>
+      <c r="G138" t="s">
+        <v>12</v>
+      </c>
+      <c r="H138" s="2">
+        <v>1.0416666666666667E-4</v>
+      </c>
+      <c r="I138" s="1">
+        <v>46237.856249999997</v>
+      </c>
+      <c r="J138" s="2">
+        <v>0</v>
+      </c>
+      <c r="K138" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="139" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H139" s="2"/>
       <c r="I139" s="1"/>
       <c r="J139" s="2"/>
-      <c r="K139" s="1"/>
-    </row>
-    <row r="140" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H140" s="2"/>
-      <c r="I140" s="1"/>
-      <c r="J140" s="2"/>
-      <c r="K140" s="1"/>
-    </row>
-    <row r="141" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H141" s="2"/>
-      <c r="I141" s="1"/>
-      <c r="J141" s="2"/>
-      <c r="K141" s="1"/>
-    </row>
-    <row r="142" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H142" s="2"/>
-      <c r="I142" s="1"/>
-      <c r="J142" s="2"/>
-      <c r="K142" s="1"/>
-    </row>
-    <row r="143" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H143" s="2"/>
-      <c r="I143" s="1"/>
-      <c r="J143" s="2"/>
-      <c r="K143" s="1"/>
-    </row>
-    <row r="144" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H144" s="2"/>
-      <c r="I144" s="1"/>
-      <c r="J144" s="2"/>
-      <c r="K144" s="1"/>
-    </row>
-    <row r="145" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H145" s="2"/>
-      <c r="I145" s="1"/>
-      <c r="J145" s="2"/>
-      <c r="K145" s="1"/>
-    </row>
-    <row r="146" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H146" s="2"/>
-      <c r="I146" s="1"/>
-      <c r="J146" s="2"/>
-      <c r="K146" s="1"/>
-    </row>
-    <row r="147" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H147" s="2"/>
-      <c r="I147" s="1"/>
-      <c r="J147" s="2"/>
-      <c r="K147" s="1"/>
-    </row>
-    <row r="148" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H148" s="2"/>
-      <c r="I148" s="1"/>
-      <c r="J148" s="2"/>
-      <c r="K148" s="1"/>
-    </row>
-    <row r="149" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H149" s="2"/>
-      <c r="I149" s="1"/>
-      <c r="J149" s="2"/>
-      <c r="K149" s="1"/>
-    </row>
-    <row r="150" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H150" s="2"/>
-      <c r="I150" s="1"/>
-      <c r="J150" s="2"/>
-      <c r="K150" s="1"/>
-    </row>
-    <row r="151" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H151" s="2"/>
-      <c r="I151" s="1"/>
-      <c r="J151" s="2"/>
-      <c r="K151" s="1"/>
-    </row>
-    <row r="152" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H152" s="2"/>
-      <c r="I152" s="1"/>
-      <c r="J152" s="2"/>
-      <c r="K152" s="1"/>
-    </row>
-    <row r="153" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H153" s="2"/>
-      <c r="I153" s="1"/>
-      <c r="J153" s="2"/>
-      <c r="K153" s="1"/>
-    </row>
-    <row r="154" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H154" s="2"/>
-      <c r="I154" s="1"/>
-      <c r="J154" s="2"/>
-      <c r="K154" s="1"/>
-    </row>
-    <row r="155" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H155" s="2"/>
-      <c r="I155" s="1"/>
-      <c r="J155" s="2"/>
-      <c r="K155" s="1"/>
-    </row>
-    <row r="156" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H156" s="2"/>
-      <c r="I156" s="1"/>
-      <c r="J156" s="2"/>
-      <c r="K156" s="1"/>
-    </row>
-    <row r="157" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="K139" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="140" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B140" t="s">
+        <v>19</v>
+      </c>
+      <c r="C140">
+        <v>5739</v>
+      </c>
+      <c r="D140" t="s">
+        <v>55</v>
+      </c>
+      <c r="F140" t="s">
+        <v>16</v>
+      </c>
+      <c r="G140" t="s">
+        <v>13</v>
+      </c>
+      <c r="H140" s="2">
+        <v>0</v>
+      </c>
+      <c r="I140" s="1">
+        <v>46237.856944444444</v>
+      </c>
+      <c r="J140" s="2">
+        <v>0</v>
+      </c>
+      <c r="K140" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="141" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B141" t="s">
+        <v>19</v>
+      </c>
+      <c r="C141">
+        <v>5710</v>
+      </c>
+      <c r="D141" t="s">
+        <v>56</v>
+      </c>
+      <c r="F141" t="s">
+        <v>16</v>
+      </c>
+      <c r="G141" t="s">
+        <v>10</v>
+      </c>
+      <c r="H141" s="2">
+        <v>6.4351851851851853E-3</v>
+      </c>
+      <c r="I141" s="1">
+        <v>46237.857638888891</v>
+      </c>
+      <c r="J141" s="2">
+        <v>0</v>
+      </c>
+      <c r="K141" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="142" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B142" t="s">
+        <v>19</v>
+      </c>
+      <c r="C142">
+        <v>5746</v>
+      </c>
+      <c r="D142" t="s">
+        <v>57</v>
+      </c>
+      <c r="F142" t="s">
+        <v>16</v>
+      </c>
+      <c r="G142" t="s">
+        <v>13</v>
+      </c>
+      <c r="H142" s="2">
+        <v>0</v>
+      </c>
+      <c r="I142" s="1">
+        <v>46237.857638888891</v>
+      </c>
+      <c r="J142" s="2">
+        <v>0</v>
+      </c>
+      <c r="K142" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="143" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B143" t="s">
+        <v>19</v>
+      </c>
+      <c r="C143">
+        <v>5702</v>
+      </c>
+      <c r="D143" t="s">
+        <v>58</v>
+      </c>
+      <c r="F143" t="s">
+        <v>16</v>
+      </c>
+      <c r="G143" t="s">
+        <v>10</v>
+      </c>
+      <c r="H143" s="2">
+        <v>5.9953703703703705E-3</v>
+      </c>
+      <c r="I143" s="1">
+        <v>46237.85833333333</v>
+      </c>
+      <c r="J143" s="2">
+        <v>0</v>
+      </c>
+      <c r="K143" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="144" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B144" t="s">
+        <v>19</v>
+      </c>
+      <c r="C144">
+        <v>5728</v>
+      </c>
+      <c r="D144" t="s">
+        <v>59</v>
+      </c>
+      <c r="F144" t="s">
+        <v>16</v>
+      </c>
+      <c r="G144" t="s">
+        <v>13</v>
+      </c>
+      <c r="H144" s="2">
+        <v>0</v>
+      </c>
+      <c r="I144" s="1">
+        <v>46237.859027777777</v>
+      </c>
+      <c r="J144" s="2">
+        <v>0</v>
+      </c>
+      <c r="K144" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="145" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B145" t="s">
+        <v>19</v>
+      </c>
+      <c r="C145">
+        <v>5683</v>
+      </c>
+      <c r="D145" t="s">
+        <v>60</v>
+      </c>
+      <c r="F145" t="s">
+        <v>16</v>
+      </c>
+      <c r="G145" t="s">
+        <v>13</v>
+      </c>
+      <c r="H145" s="2">
+        <v>0</v>
+      </c>
+      <c r="I145" s="1">
+        <v>46237.859722222223</v>
+      </c>
+      <c r="J145" s="2">
+        <v>0</v>
+      </c>
+      <c r="K145" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="146" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B146" t="s">
+        <v>19</v>
+      </c>
+      <c r="C146">
+        <v>5745</v>
+      </c>
+      <c r="D146" t="s">
+        <v>61</v>
+      </c>
+      <c r="F146" t="s">
+        <v>16</v>
+      </c>
+      <c r="G146" t="s">
+        <v>13</v>
+      </c>
+      <c r="H146" s="2">
+        <v>0</v>
+      </c>
+      <c r="I146" s="1">
+        <v>46237.835532407407</v>
+      </c>
+      <c r="J146" s="2">
+        <v>0</v>
+      </c>
+      <c r="K146" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="147" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B147" t="s">
+        <v>19</v>
+      </c>
+      <c r="C147">
+        <v>5733</v>
+      </c>
+      <c r="D147" t="s">
+        <v>62</v>
+      </c>
+      <c r="F147" t="s">
+        <v>16</v>
+      </c>
+      <c r="G147" t="s">
+        <v>13</v>
+      </c>
+      <c r="H147" s="2">
+        <v>0</v>
+      </c>
+      <c r="I147" s="1">
+        <v>46237.835532407407</v>
+      </c>
+      <c r="J147" s="2">
+        <v>0</v>
+      </c>
+      <c r="K147" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="148" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B148" t="s">
+        <v>19</v>
+      </c>
+      <c r="C148">
+        <v>5704</v>
+      </c>
+      <c r="D148" t="s">
+        <v>63</v>
+      </c>
+      <c r="F148" t="s">
+        <v>16</v>
+      </c>
+      <c r="G148" t="s">
+        <v>13</v>
+      </c>
+      <c r="H148" s="2">
+        <v>0</v>
+      </c>
+      <c r="I148" s="1">
+        <v>46237.836226851854</v>
+      </c>
+      <c r="J148" s="2">
+        <v>0</v>
+      </c>
+      <c r="K148" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="149" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B149" t="s">
+        <v>19</v>
+      </c>
+      <c r="C149">
+        <v>5693</v>
+      </c>
+      <c r="D149" t="s">
+        <v>64</v>
+      </c>
+      <c r="F149" t="s">
+        <v>16</v>
+      </c>
+      <c r="G149" t="s">
+        <v>10</v>
+      </c>
+      <c r="H149" s="2">
+        <v>6.2500000000000003E-3</v>
+      </c>
+      <c r="I149" s="1">
+        <v>46237.836921296293</v>
+      </c>
+      <c r="J149" s="2">
+        <v>0</v>
+      </c>
+      <c r="K149" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="150" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B150" t="s">
+        <v>19</v>
+      </c>
+      <c r="C150">
+        <v>5718</v>
+      </c>
+      <c r="D150" t="s">
+        <v>65</v>
+      </c>
+      <c r="F150" t="s">
+        <v>16</v>
+      </c>
+      <c r="G150" t="s">
+        <v>13</v>
+      </c>
+      <c r="H150" s="2">
+        <v>0</v>
+      </c>
+      <c r="I150" s="1">
+        <v>46237.836921296293</v>
+      </c>
+      <c r="J150" s="2">
+        <v>0</v>
+      </c>
+      <c r="K150" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="151" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B151" t="s">
+        <v>19</v>
+      </c>
+      <c r="C151">
+        <v>5700</v>
+      </c>
+      <c r="D151" t="s">
+        <v>66</v>
+      </c>
+      <c r="F151" t="s">
+        <v>16</v>
+      </c>
+      <c r="G151" t="s">
+        <v>13</v>
+      </c>
+      <c r="H151" s="2">
+        <v>0</v>
+      </c>
+      <c r="I151" s="1">
+        <v>46237.83761574074</v>
+      </c>
+      <c r="J151" s="2">
+        <v>0</v>
+      </c>
+      <c r="K151" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="152" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B152" t="s">
+        <v>19</v>
+      </c>
+      <c r="C152">
+        <v>5726</v>
+      </c>
+      <c r="D152" t="s">
+        <v>67</v>
+      </c>
+      <c r="F152" t="s">
+        <v>16</v>
+      </c>
+      <c r="G152" t="s">
+        <v>13</v>
+      </c>
+      <c r="H152" s="2">
+        <v>0</v>
+      </c>
+      <c r="I152" s="1">
+        <v>46237.838310185187</v>
+      </c>
+      <c r="J152" s="2">
+        <v>0</v>
+      </c>
+      <c r="K152" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="153" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B153" t="s">
+        <v>19</v>
+      </c>
+      <c r="C153">
+        <v>5684</v>
+      </c>
+      <c r="D153" t="s">
+        <v>68</v>
+      </c>
+      <c r="F153" t="s">
+        <v>16</v>
+      </c>
+      <c r="G153" t="s">
+        <v>13</v>
+      </c>
+      <c r="H153" s="2">
+        <v>0</v>
+      </c>
+      <c r="I153" s="1">
+        <v>46237.838310185187</v>
+      </c>
+      <c r="J153" s="2">
+        <v>0</v>
+      </c>
+      <c r="K153" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="154" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B154" t="s">
+        <v>19</v>
+      </c>
+      <c r="C154">
+        <v>5740</v>
+      </c>
+      <c r="D154" t="s">
+        <v>69</v>
+      </c>
+      <c r="F154" t="s">
+        <v>16</v>
+      </c>
+      <c r="G154" t="s">
+        <v>13</v>
+      </c>
+      <c r="H154" s="2">
+        <v>0</v>
+      </c>
+      <c r="I154" s="1">
+        <v>46237.839004629626</v>
+      </c>
+      <c r="J154" s="2">
+        <v>0</v>
+      </c>
+      <c r="K154" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="155" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B155" t="s">
+        <v>19</v>
+      </c>
+      <c r="C155">
+        <v>5701</v>
+      </c>
+      <c r="D155" t="s">
+        <v>70</v>
+      </c>
+      <c r="F155" t="s">
+        <v>16</v>
+      </c>
+      <c r="G155" t="s">
+        <v>13</v>
+      </c>
+      <c r="H155" s="2">
+        <v>0</v>
+      </c>
+      <c r="I155" s="1">
+        <v>46237.839699074073</v>
+      </c>
+      <c r="J155" s="2">
+        <v>0</v>
+      </c>
+      <c r="K155" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="156" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B156" t="s">
+        <v>19</v>
+      </c>
+      <c r="C156">
+        <v>5695</v>
+      </c>
+      <c r="D156" t="s">
+        <v>71</v>
+      </c>
+      <c r="F156" t="s">
+        <v>16</v>
+      </c>
+      <c r="G156" t="s">
+        <v>12</v>
+      </c>
+      <c r="H156" s="2">
+        <v>6.134259259259259E-4</v>
+      </c>
+      <c r="I156" s="1">
+        <v>46237.839699074073</v>
+      </c>
+      <c r="J156" s="2">
+        <v>0</v>
+      </c>
+      <c r="K156" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="157" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H157" s="2"/>
       <c r="I157" s="1"/>
       <c r="J157" s="2"/>
-      <c r="K157" s="1"/>
-    </row>
-    <row r="158" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H158" s="2"/>
-      <c r="I158" s="1"/>
-      <c r="J158" s="2"/>
-      <c r="K158" s="1"/>
-    </row>
-    <row r="159" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H159" s="2"/>
-      <c r="I159" s="1"/>
-      <c r="J159" s="2"/>
-      <c r="K159" s="1"/>
-    </row>
-    <row r="160" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H160" s="2"/>
-      <c r="I160" s="1"/>
-      <c r="J160" s="2"/>
-      <c r="K160" s="1"/>
-    </row>
-    <row r="161" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H161" s="2"/>
-      <c r="I161" s="1"/>
-      <c r="J161" s="2"/>
-      <c r="K161" s="1"/>
-    </row>
-    <row r="162" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H162" s="2"/>
-      <c r="I162" s="1"/>
-      <c r="J162" s="2"/>
-      <c r="K162" s="1"/>
-    </row>
-    <row r="163" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H163" s="2"/>
-      <c r="I163" s="1"/>
-      <c r="J163" s="2"/>
-      <c r="K163" s="1"/>
-    </row>
-    <row r="164" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H164" s="2"/>
-      <c r="I164" s="1"/>
-      <c r="J164" s="2"/>
-      <c r="K164" s="1"/>
-    </row>
-    <row r="165" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H165" s="2"/>
-      <c r="I165" s="1"/>
-      <c r="J165" s="2"/>
-      <c r="K165" s="1"/>
-    </row>
-    <row r="166" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H166" s="2"/>
-      <c r="I166" s="1"/>
-      <c r="J166" s="2"/>
-      <c r="K166" s="1"/>
-    </row>
-    <row r="167" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H167" s="2"/>
-      <c r="I167" s="1"/>
-      <c r="J167" s="2"/>
-      <c r="K167" s="1"/>
-    </row>
-    <row r="168" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H168" s="2"/>
-      <c r="I168" s="1"/>
-      <c r="J168" s="2"/>
-      <c r="K168" s="1"/>
-    </row>
-    <row r="169" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H169" s="2"/>
-      <c r="I169" s="1"/>
-      <c r="J169" s="2"/>
-      <c r="K169" s="1"/>
-    </row>
-    <row r="170" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H170" s="2"/>
-      <c r="I170" s="1"/>
-      <c r="J170" s="2"/>
-      <c r="K170" s="1"/>
-    </row>
-    <row r="171" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H171" s="2"/>
-      <c r="I171" s="1"/>
-      <c r="J171" s="2"/>
-      <c r="K171" s="1"/>
-    </row>
-    <row r="172" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H172" s="2"/>
-      <c r="I172" s="1"/>
-      <c r="J172" s="2"/>
-      <c r="K172" s="1"/>
-    </row>
-    <row r="173" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H173" s="2"/>
-      <c r="I173" s="1"/>
-      <c r="J173" s="2"/>
-      <c r="K173" s="1"/>
-    </row>
-    <row r="174" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H174" s="2"/>
-      <c r="I174" s="1"/>
-      <c r="J174" s="2"/>
-      <c r="K174" s="1"/>
-    </row>
-    <row r="175" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H175" s="2"/>
-      <c r="I175" s="1"/>
-      <c r="J175" s="2"/>
-      <c r="K175" s="1"/>
-    </row>
-    <row r="176" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H176" s="2"/>
-      <c r="I176" s="1"/>
-      <c r="J176" s="2"/>
-      <c r="K176" s="1"/>
-    </row>
-    <row r="177" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H177" s="2"/>
-      <c r="I177" s="1"/>
-      <c r="J177" s="2"/>
-      <c r="K177" s="1"/>
-    </row>
-    <row r="178" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H178" s="2"/>
-      <c r="I178" s="1"/>
-      <c r="J178" s="2"/>
-      <c r="K178" s="1"/>
-    </row>
-    <row r="179" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="K157" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="158" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B158" t="s">
+        <v>19</v>
+      </c>
+      <c r="C158">
+        <v>5690</v>
+      </c>
+      <c r="D158" t="s">
+        <v>72</v>
+      </c>
+      <c r="F158" t="s">
+        <v>16</v>
+      </c>
+      <c r="G158" t="s">
+        <v>13</v>
+      </c>
+      <c r="H158" s="2">
+        <v>0</v>
+      </c>
+      <c r="I158" s="1">
+        <v>46237.84039351852</v>
+      </c>
+      <c r="J158" s="2">
+        <v>0</v>
+      </c>
+      <c r="K158" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="159" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B159" t="s">
+        <v>19</v>
+      </c>
+      <c r="C159">
+        <v>5697</v>
+      </c>
+      <c r="D159" t="s">
+        <v>73</v>
+      </c>
+      <c r="F159" t="s">
+        <v>16</v>
+      </c>
+      <c r="G159" t="s">
+        <v>13</v>
+      </c>
+      <c r="H159" s="2">
+        <v>0</v>
+      </c>
+      <c r="I159" s="1">
+        <v>46237.841087962966</v>
+      </c>
+      <c r="J159" s="2">
+        <v>0</v>
+      </c>
+      <c r="K159" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="160" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B160" t="s">
+        <v>19</v>
+      </c>
+      <c r="C160">
+        <v>5744</v>
+      </c>
+      <c r="D160" t="s">
+        <v>74</v>
+      </c>
+      <c r="F160" t="s">
+        <v>16</v>
+      </c>
+      <c r="G160" t="s">
+        <v>10</v>
+      </c>
+      <c r="H160" s="2">
+        <v>7.2685185185185188E-3</v>
+      </c>
+      <c r="I160" s="1">
+        <v>46237.841782407406</v>
+      </c>
+      <c r="J160" s="2">
+        <v>0</v>
+      </c>
+      <c r="K160" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="161" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B161" t="s">
+        <v>19</v>
+      </c>
+      <c r="C161">
+        <v>5738</v>
+      </c>
+      <c r="D161" t="s">
+        <v>75</v>
+      </c>
+      <c r="F161" t="s">
+        <v>16</v>
+      </c>
+      <c r="G161" t="s">
+        <v>13</v>
+      </c>
+      <c r="H161" s="2">
+        <v>0</v>
+      </c>
+      <c r="I161" s="1">
+        <v>46237.841782407406</v>
+      </c>
+      <c r="J161" s="2">
+        <v>0</v>
+      </c>
+      <c r="K161" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="162" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B162" t="s">
+        <v>19</v>
+      </c>
+      <c r="C162">
+        <v>5691</v>
+      </c>
+      <c r="D162" t="s">
+        <v>76</v>
+      </c>
+      <c r="F162" t="s">
+        <v>16</v>
+      </c>
+      <c r="G162" t="s">
+        <v>13</v>
+      </c>
+      <c r="H162" s="2">
+        <v>0</v>
+      </c>
+      <c r="I162" s="1">
+        <v>46237.842476851853</v>
+      </c>
+      <c r="J162" s="2">
+        <v>0</v>
+      </c>
+      <c r="K162" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="163" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B163" t="s">
+        <v>19</v>
+      </c>
+      <c r="C163">
+        <v>5699</v>
+      </c>
+      <c r="D163" t="s">
+        <v>77</v>
+      </c>
+      <c r="F163" t="s">
+        <v>16</v>
+      </c>
+      <c r="G163" t="s">
+        <v>13</v>
+      </c>
+      <c r="H163" s="2">
+        <v>0</v>
+      </c>
+      <c r="I163" s="1">
+        <v>46237.843171296299</v>
+      </c>
+      <c r="J163" s="2">
+        <v>0</v>
+      </c>
+      <c r="K163" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="164" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B164" t="s">
+        <v>19</v>
+      </c>
+      <c r="C164">
+        <v>5694</v>
+      </c>
+      <c r="D164" t="s">
+        <v>78</v>
+      </c>
+      <c r="F164" t="s">
+        <v>16</v>
+      </c>
+      <c r="G164" t="s">
+        <v>13</v>
+      </c>
+      <c r="H164" s="2">
+        <v>0</v>
+      </c>
+      <c r="I164" s="1">
+        <v>46237.843171296299</v>
+      </c>
+      <c r="J164" s="2">
+        <v>0</v>
+      </c>
+      <c r="K164" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="165" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B165" t="s">
+        <v>19</v>
+      </c>
+      <c r="C165">
+        <v>5730</v>
+      </c>
+      <c r="D165" t="s">
+        <v>79</v>
+      </c>
+      <c r="F165" t="s">
+        <v>16</v>
+      </c>
+      <c r="G165" t="s">
+        <v>13</v>
+      </c>
+      <c r="H165" s="2">
+        <v>0</v>
+      </c>
+      <c r="I165" s="1">
+        <v>46237.843865740739</v>
+      </c>
+      <c r="J165" s="2">
+        <v>0</v>
+      </c>
+      <c r="K165" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="166" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B166" t="s">
+        <v>19</v>
+      </c>
+      <c r="C166">
+        <v>5681</v>
+      </c>
+      <c r="D166" t="s">
+        <v>80</v>
+      </c>
+      <c r="F166" t="s">
+        <v>16</v>
+      </c>
+      <c r="G166" t="s">
+        <v>13</v>
+      </c>
+      <c r="H166" s="2">
+        <v>0</v>
+      </c>
+      <c r="I166" s="1">
+        <v>46237.844560185185</v>
+      </c>
+      <c r="J166" s="2">
+        <v>0</v>
+      </c>
+      <c r="K166" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="167" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B167" t="s">
+        <v>19</v>
+      </c>
+      <c r="C167">
+        <v>5735</v>
+      </c>
+      <c r="D167" t="s">
+        <v>81</v>
+      </c>
+      <c r="F167" t="s">
+        <v>16</v>
+      </c>
+      <c r="G167" t="s">
+        <v>13</v>
+      </c>
+      <c r="H167" s="2">
+        <v>0</v>
+      </c>
+      <c r="I167" s="1">
+        <v>46237.844560185185</v>
+      </c>
+      <c r="J167" s="2">
+        <v>0</v>
+      </c>
+      <c r="K167" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="168" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B168" t="s">
+        <v>19</v>
+      </c>
+      <c r="C168">
+        <v>5692</v>
+      </c>
+      <c r="D168" t="s">
+        <v>82</v>
+      </c>
+      <c r="F168" t="s">
+        <v>16</v>
+      </c>
+      <c r="G168" t="s">
+        <v>13</v>
+      </c>
+      <c r="H168" s="2">
+        <v>0</v>
+      </c>
+      <c r="I168" s="1">
+        <v>46237.845254629632</v>
+      </c>
+      <c r="J168" s="2">
+        <v>0</v>
+      </c>
+      <c r="K168" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="169" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B169" t="s">
+        <v>19</v>
+      </c>
+      <c r="C169">
+        <v>5703</v>
+      </c>
+      <c r="D169" t="s">
+        <v>83</v>
+      </c>
+      <c r="F169" t="s">
+        <v>16</v>
+      </c>
+      <c r="G169" t="s">
+        <v>13</v>
+      </c>
+      <c r="H169" s="2">
+        <v>0</v>
+      </c>
+      <c r="I169" s="1">
+        <v>46237.845254629632</v>
+      </c>
+      <c r="J169" s="2">
+        <v>0</v>
+      </c>
+      <c r="K169" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="170" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B170" t="s">
+        <v>19</v>
+      </c>
+      <c r="C170">
+        <v>5708</v>
+      </c>
+      <c r="D170" t="s">
+        <v>84</v>
+      </c>
+      <c r="F170" t="s">
+        <v>16</v>
+      </c>
+      <c r="G170" t="s">
+        <v>10</v>
+      </c>
+      <c r="H170" s="2">
+        <v>1.3460648148148149E-2</v>
+      </c>
+      <c r="I170" s="1">
+        <v>46237.845949074072</v>
+      </c>
+      <c r="J170" s="2">
+        <v>0</v>
+      </c>
+      <c r="K170" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="171" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B171" t="s">
+        <v>19</v>
+      </c>
+      <c r="C171">
+        <v>5712</v>
+      </c>
+      <c r="D171" t="s">
+        <v>85</v>
+      </c>
+      <c r="F171" t="s">
+        <v>16</v>
+      </c>
+      <c r="G171" t="s">
+        <v>13</v>
+      </c>
+      <c r="H171" s="2">
+        <v>0</v>
+      </c>
+      <c r="I171" s="1">
+        <v>46237.846643518518</v>
+      </c>
+      <c r="J171" s="2">
+        <v>0</v>
+      </c>
+      <c r="K171" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="172" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B172" t="s">
+        <v>19</v>
+      </c>
+      <c r="C172">
+        <v>6002</v>
+      </c>
+      <c r="D172" t="s">
+        <v>94</v>
+      </c>
+      <c r="F172" t="s">
+        <v>16</v>
+      </c>
+      <c r="G172" t="s">
+        <v>10</v>
+      </c>
+      <c r="H172" s="2">
+        <v>5.8564814814814816E-3</v>
+      </c>
+      <c r="I172" s="1">
+        <v>46237.846643518518</v>
+      </c>
+      <c r="J172" s="2">
+        <v>0</v>
+      </c>
+      <c r="K172" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="173" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B173" t="s">
+        <v>19</v>
+      </c>
+      <c r="C173">
+        <v>5734</v>
+      </c>
+      <c r="D173" t="s">
+        <v>86</v>
+      </c>
+      <c r="F173" t="s">
+        <v>16</v>
+      </c>
+      <c r="G173" t="s">
+        <v>13</v>
+      </c>
+      <c r="H173" s="2">
+        <v>0</v>
+      </c>
+      <c r="I173" s="1">
+        <v>46237.847337962965</v>
+      </c>
+      <c r="J173" s="2">
+        <v>0</v>
+      </c>
+      <c r="K173" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="174" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B174" t="s">
+        <v>19</v>
+      </c>
+      <c r="C174">
+        <v>5743</v>
+      </c>
+      <c r="D174" t="s">
+        <v>87</v>
+      </c>
+      <c r="F174" t="s">
+        <v>16</v>
+      </c>
+      <c r="G174" t="s">
+        <v>13</v>
+      </c>
+      <c r="H174" s="2">
+        <v>0</v>
+      </c>
+      <c r="I174" s="1">
+        <v>46237.848032407404</v>
+      </c>
+      <c r="J174" s="2">
+        <v>0</v>
+      </c>
+      <c r="K174" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="175" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B175" t="s">
+        <v>19</v>
+      </c>
+      <c r="C175">
+        <v>5742</v>
+      </c>
+      <c r="D175" t="s">
+        <v>88</v>
+      </c>
+      <c r="F175" t="s">
+        <v>16</v>
+      </c>
+      <c r="G175" t="s">
+        <v>13</v>
+      </c>
+      <c r="H175" s="2">
+        <v>0</v>
+      </c>
+      <c r="I175" s="1">
+        <v>46237.848726851851</v>
+      </c>
+      <c r="J175" s="2">
+        <v>0</v>
+      </c>
+      <c r="K175" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="176" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B176" t="s">
+        <v>19</v>
+      </c>
+      <c r="C176">
+        <v>5723</v>
+      </c>
+      <c r="D176" t="s">
+        <v>89</v>
+      </c>
+      <c r="F176" t="s">
+        <v>16</v>
+      </c>
+      <c r="G176" t="s">
+        <v>13</v>
+      </c>
+      <c r="H176" s="2">
+        <v>0</v>
+      </c>
+      <c r="I176" s="1">
+        <v>46237.848726851851</v>
+      </c>
+      <c r="J176" s="2">
+        <v>0</v>
+      </c>
+      <c r="K176" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="177" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B177" t="s">
+        <v>19</v>
+      </c>
+      <c r="C177">
+        <v>5706</v>
+      </c>
+      <c r="D177" t="s">
+        <v>90</v>
+      </c>
+      <c r="F177" t="s">
+        <v>16</v>
+      </c>
+      <c r="G177" t="s">
+        <v>13</v>
+      </c>
+      <c r="H177" s="2">
+        <v>0</v>
+      </c>
+      <c r="I177" s="1">
+        <v>46237.849421296298</v>
+      </c>
+      <c r="J177" s="2">
+        <v>0</v>
+      </c>
+      <c r="K177" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="178" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B178" t="s">
+        <v>19</v>
+      </c>
+      <c r="C178">
+        <v>5670</v>
+      </c>
+      <c r="D178" t="s">
+        <v>21</v>
+      </c>
+      <c r="F178" t="s">
+        <v>16</v>
+      </c>
+      <c r="G178" t="s">
+        <v>14</v>
+      </c>
+      <c r="H178" s="2">
+        <v>0</v>
+      </c>
+      <c r="I178" s="1">
+        <v>46237.850115740737</v>
+      </c>
+      <c r="J178" s="2">
+        <v>0</v>
+      </c>
+      <c r="K178" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="179" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H179" s="2"/>
       <c r="I179" s="1"/>
       <c r="J179" s="2"/>
-      <c r="K179" s="1"/>
-    </row>
-    <row r="180" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H180" s="2"/>
-      <c r="I180" s="1"/>
-      <c r="J180" s="2"/>
-      <c r="K180" s="1"/>
-    </row>
-    <row r="181" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H181" s="2"/>
-      <c r="I181" s="1"/>
-      <c r="J181" s="2"/>
-      <c r="K181" s="1"/>
-    </row>
-    <row r="182" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H182" s="2"/>
-      <c r="I182" s="1"/>
-      <c r="J182" s="2"/>
-      <c r="K182" s="1"/>
-    </row>
-    <row r="183" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="K179" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="180" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B180" t="s">
+        <v>19</v>
+      </c>
+      <c r="C180">
+        <v>5677</v>
+      </c>
+      <c r="D180" t="s">
+        <v>91</v>
+      </c>
+      <c r="F180" t="s">
+        <v>16</v>
+      </c>
+      <c r="G180" t="s">
+        <v>10</v>
+      </c>
+      <c r="H180" s="2">
+        <v>6.8055555555555551E-3</v>
+      </c>
+      <c r="I180" s="1">
+        <v>46237.850115740737</v>
+      </c>
+      <c r="J180" s="2">
+        <v>0</v>
+      </c>
+      <c r="K180" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="181" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B181" t="s">
+        <v>19</v>
+      </c>
+      <c r="C181">
+        <v>5685</v>
+      </c>
+      <c r="D181" t="s">
+        <v>92</v>
+      </c>
+      <c r="F181" t="s">
+        <v>16</v>
+      </c>
+      <c r="G181" t="s">
+        <v>13</v>
+      </c>
+      <c r="H181" s="2">
+        <v>0</v>
+      </c>
+      <c r="I181" s="1">
+        <v>46237.850810185184</v>
+      </c>
+      <c r="J181" s="2">
+        <v>0</v>
+      </c>
+      <c r="K181" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="182" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B182" t="s">
+        <v>19</v>
+      </c>
+      <c r="C182">
+        <v>5719</v>
+      </c>
+      <c r="D182" t="s">
+        <v>93</v>
+      </c>
+      <c r="F182" t="s">
+        <v>16</v>
+      </c>
+      <c r="G182" t="s">
+        <v>12</v>
+      </c>
+      <c r="H182" s="2">
+        <v>1.1226851851851851E-3</v>
+      </c>
+      <c r="I182" s="1">
+        <v>46237.850810185184</v>
+      </c>
+      <c r="J182" s="2">
+        <v>0</v>
+      </c>
+      <c r="K182" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="183" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H183" s="2"/>
       <c r="I183" s="1"/>
       <c r="J183" s="2"/>
-      <c r="K183" s="1"/>
-    </row>
-    <row r="184" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="K183" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="184" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H184" s="2"/>
       <c r="I184" s="1"/>
       <c r="J184" s="2"/>
       <c r="K184" s="1"/>
     </row>
-    <row r="185" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="185" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H185" s="2"/>
       <c r="I185" s="1"/>
       <c r="J185" s="2"/>
       <c r="K185" s="1"/>
     </row>
-    <row r="186" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="186" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H186" s="2"/>
       <c r="I186" s="1"/>
       <c r="J186" s="2"/>
       <c r="K186" s="1"/>
     </row>
-    <row r="187" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="187" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H187" s="2"/>
       <c r="I187" s="1"/>
       <c r="J187" s="2"/>
       <c r="K187" s="1"/>
     </row>
-    <row r="188" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="188" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H188" s="2"/>
       <c r="I188" s="1"/>
       <c r="J188" s="2"/>
       <c r="K188" s="1"/>
     </row>
-    <row r="189" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="189" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H189" s="2"/>
       <c r="I189" s="1"/>
       <c r="J189" s="2"/>
       <c r="K189" s="1"/>
     </row>
-    <row r="190" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="190" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H190" s="2"/>
       <c r="I190" s="1"/>
       <c r="J190" s="2"/>
       <c r="K190" s="1"/>
     </row>
-    <row r="191" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="191" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H191" s="2"/>
       <c r="I191" s="1"/>
       <c r="J191" s="2"/>
       <c r="K191" s="1"/>
     </row>
-    <row r="192" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="192" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H192" s="2"/>
       <c r="I192" s="1"/>
       <c r="J192" s="2"/>
@@ -14438,9 +16180,11 @@
       <c r="K1944" s="1"/>
     </row>
     <row r="1945" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1945" s="2"/>
       <c r="I1945" s="1"/>
     </row>
     <row r="1946" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1946" s="2"/>
       <c r="I1946" s="1"/>
       <c r="K1946" s="1"/>
     </row>
@@ -14506,6 +16250,7 @@
       <c r="K1958" s="1"/>
     </row>
     <row r="1959" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1959" s="2"/>
       <c r="I1959" s="1"/>
       <c r="K1959" s="1"/>
     </row>
@@ -14548,6 +16293,7 @@
       <c r="K1966" s="1"/>
     </row>
     <row r="1967" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1967" s="2"/>
       <c r="I1967" s="1"/>
     </row>
     <row r="1968" spans="8:11" x14ac:dyDescent="0.25">
@@ -14561,6 +16307,7 @@
       <c r="I1969" s="1"/>
     </row>
     <row r="1970" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1970" s="2"/>
       <c r="I1970" s="1"/>
       <c r="K1970" s="1"/>
     </row>
@@ -14631,6 +16378,7 @@
       <c r="K1982" s="1"/>
     </row>
     <row r="1983" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1983" s="2"/>
       <c r="I1983" s="1"/>
       <c r="K1983" s="1"/>
     </row>
@@ -14660,6 +16408,7 @@
       <c r="K1988" s="1"/>
     </row>
     <row r="1989" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1989" s="2"/>
       <c r="I1989" s="1"/>
       <c r="K1989" s="1"/>
     </row>
@@ -14681,6 +16430,7 @@
       <c r="K1992" s="1"/>
     </row>
     <row r="1993" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1993" s="2"/>
       <c r="I1993" s="1"/>
     </row>
     <row r="1994" spans="8:11" x14ac:dyDescent="0.25">
@@ -14759,6 +16509,7 @@
       <c r="K2007" s="1"/>
     </row>
     <row r="2008" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H2008" s="2"/>
       <c r="I2008" s="1"/>
       <c r="K2008" s="1"/>
     </row>
@@ -44940,6 +46691,7 @@
       <c r="K7155" s="1"/>
     </row>
     <row r="7156" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7156" s="2"/>
       <c r="I7156" s="1"/>
       <c r="J7156" s="2"/>
       <c r="K7156" s="1"/>
@@ -44954,11 +46706,13 @@
       <c r="K7158" s="1"/>
     </row>
     <row r="7159" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7159" s="2"/>
       <c r="I7159" s="1"/>
       <c r="J7159" s="2"/>
       <c r="K7159" s="1"/>
     </row>
     <row r="7160" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7160" s="2"/>
       <c r="I7160" s="1"/>
       <c r="K7160" s="1"/>
     </row>
@@ -44969,10 +46723,13 @@
       <c r="K7161" s="1"/>
     </row>
     <row r="7162" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7162" s="2"/>
+      <c r="I7162" s="1"/>
       <c r="J7162" s="2"/>
       <c r="K7162" s="1"/>
     </row>
     <row r="7163" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7163" s="2"/>
       <c r="I7163" s="1"/>
       <c r="K7163" s="1"/>
     </row>
@@ -44990,14 +46747,17 @@
       <c r="K7166" s="1"/>
     </row>
     <row r="7167" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7167" s="2"/>
       <c r="I7167" s="1"/>
       <c r="K7167" s="1"/>
     </row>
     <row r="7168" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7168" s="2"/>
       <c r="I7168" s="1"/>
       <c r="K7168" s="1"/>
     </row>
     <row r="7169" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7169" s="2"/>
       <c r="I7169" s="1"/>
       <c r="K7169" s="1"/>
     </row>
@@ -45008,14 +46768,17 @@
       <c r="K7170" s="1"/>
     </row>
     <row r="7171" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7171" s="2"/>
       <c r="I7171" s="1"/>
       <c r="K7171" s="1"/>
     </row>
     <row r="7172" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7172" s="2"/>
       <c r="I7172" s="1"/>
       <c r="K7172" s="1"/>
     </row>
     <row r="7173" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7173" s="2"/>
       <c r="I7173" s="1"/>
       <c r="K7173" s="1"/>
     </row>
@@ -45042,6 +46805,7 @@
       <c r="K7178" s="1"/>
     </row>
     <row r="7179" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7179" s="2"/>
       <c r="I7179" s="1"/>
       <c r="K7179" s="1"/>
     </row>
@@ -45050,6 +46814,7 @@
       <c r="K7180" s="1"/>
     </row>
     <row r="7181" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7181" s="2"/>
       <c r="I7181" s="1"/>
       <c r="K7181" s="1"/>
     </row>
@@ -45062,22 +46827,27 @@
       <c r="K7183" s="1"/>
     </row>
     <row r="7184" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7184" s="2"/>
       <c r="I7184" s="1"/>
       <c r="K7184" s="1"/>
     </row>
     <row r="7185" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7185" s="2"/>
       <c r="I7185" s="1"/>
       <c r="K7185" s="1"/>
     </row>
     <row r="7186" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7186" s="2"/>
       <c r="I7186" s="1"/>
       <c r="K7186" s="1"/>
     </row>
     <row r="7187" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7187" s="2"/>
       <c r="I7187" s="1"/>
       <c r="K7187" s="1"/>
     </row>
     <row r="7188" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7188" s="2"/>
       <c r="I7188" s="1"/>
       <c r="K7188" s="1"/>
     </row>
@@ -45096,6 +46866,7 @@
       <c r="K7191" s="1"/>
     </row>
     <row r="7192" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7192" s="2"/>
       <c r="I7192" s="1"/>
       <c r="K7192" s="1"/>
     </row>
@@ -45106,10 +46877,12 @@
       <c r="K7193" s="1"/>
     </row>
     <row r="7194" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7194" s="2"/>
       <c r="I7194" s="1"/>
       <c r="K7194" s="1"/>
     </row>
     <row r="7195" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7195" s="2"/>
       <c r="I7195" s="1"/>
       <c r="K7195" s="1"/>
     </row>
@@ -45118,10 +46891,12 @@
       <c r="K7196" s="1"/>
     </row>
     <row r="7197" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7197" s="2"/>
       <c r="I7197" s="1"/>
       <c r="K7197" s="1"/>
     </row>
     <row r="7198" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7198" s="2"/>
       <c r="I7198" s="1"/>
       <c r="K7198" s="1"/>
     </row>
@@ -45135,82 +46910,97 @@
       <c r="J7200" s="2"/>
       <c r="K7200" s="1"/>
     </row>
-    <row r="7201" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7201" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7201" s="2"/>
       <c r="I7201" s="1"/>
     </row>
-    <row r="7202" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7202" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7202" s="2"/>
       <c r="I7202" s="1"/>
       <c r="K7202" s="1"/>
     </row>
-    <row r="7203" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7203" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7203" s="2"/>
       <c r="I7203" s="1"/>
       <c r="K7203" s="1"/>
     </row>
-    <row r="7204" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7204" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7204" s="2"/>
       <c r="I7204" s="1"/>
       <c r="K7204" s="1"/>
     </row>
-    <row r="7205" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7205" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7205" s="2"/>
       <c r="I7205" s="1"/>
       <c r="K7205" s="1"/>
     </row>
-    <row r="7206" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7206" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7206" s="1"/>
       <c r="K7206" s="1"/>
     </row>
-    <row r="7207" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7207" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7207" s="2"/>
       <c r="I7207" s="1"/>
       <c r="K7207" s="1"/>
     </row>
-    <row r="7208" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7208" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7208" s="1"/>
       <c r="K7208" s="1"/>
     </row>
-    <row r="7209" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7209" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7209" s="2"/>
       <c r="I7209" s="1"/>
       <c r="K7209" s="1"/>
     </row>
-    <row r="7210" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7210" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7210" s="1"/>
       <c r="K7210" s="1"/>
     </row>
-    <row r="7211" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7211" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7211" s="2"/>
       <c r="I7211" s="1"/>
       <c r="K7211" s="1"/>
     </row>
-    <row r="7212" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7212" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7212" s="2"/>
       <c r="I7212" s="1"/>
       <c r="K7212" s="1"/>
     </row>
-    <row r="7213" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7213" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7213" s="2"/>
       <c r="I7213" s="1"/>
       <c r="K7213" s="1"/>
     </row>
-    <row r="7214" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7214" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7214" s="1"/>
       <c r="K7214" s="1"/>
     </row>
-    <row r="7215" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7215" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7215" s="1"/>
       <c r="K7215" s="1"/>
     </row>
-    <row r="7216" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7216" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7216" s="2"/>
       <c r="I7216" s="1"/>
       <c r="K7216" s="1"/>
     </row>
     <row r="7217" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7217" s="2"/>
       <c r="I7217" s="1"/>
       <c r="K7217" s="1"/>
     </row>
     <row r="7218" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7218" s="2"/>
       <c r="I7218" s="1"/>
       <c r="K7218" s="1"/>
     </row>
     <row r="7219" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7219" s="2"/>
       <c r="I7219" s="1"/>
       <c r="K7219" s="1"/>
     </row>
     <row r="7220" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7220" s="2"/>
       <c r="I7220" s="1"/>
       <c r="K7220" s="1"/>
     </row>
@@ -45224,6 +47014,7 @@
       <c r="K7222" s="1"/>
     </row>
     <row r="7223" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7223" s="2"/>
       <c r="I7223" s="1"/>
       <c r="J7223" s="2"/>
       <c r="K7223" s="1"/>
@@ -45234,6 +47025,7 @@
       <c r="K7224" s="1"/>
     </row>
     <row r="7225" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="I7225" s="1"/>
       <c r="J7225" s="2"/>
       <c r="K7225" s="1"/>
     </row>
@@ -45241,6 +47033,7 @@
       <c r="I7226" s="1"/>
     </row>
     <row r="7227" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7227" s="2"/>
       <c r="I7227" s="1"/>
       <c r="K7227" s="1"/>
     </row>
@@ -45249,86 +47042,99 @@
       <c r="K7228" s="1"/>
     </row>
     <row r="7229" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7229" s="2"/>
       <c r="I7229" s="1"/>
       <c r="K7229" s="1"/>
     </row>
     <row r="7230" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7230" s="2"/>
       <c r="I7230" s="1"/>
       <c r="K7230" s="1"/>
     </row>
     <row r="7231" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7231" s="2"/>
       <c r="I7231" s="1"/>
       <c r="K7231" s="1"/>
     </row>
     <row r="7232" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7232" s="2"/>
       <c r="I7232" s="1"/>
       <c r="K7232" s="1"/>
     </row>
-    <row r="7233" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7233" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7233" s="2"/>
       <c r="I7233" s="1"/>
       <c r="K7233" s="1"/>
     </row>
-    <row r="7234" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7234" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7234" s="1"/>
       <c r="K7234" s="1"/>
     </row>
-    <row r="7235" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7235" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7235" s="2"/>
       <c r="I7235" s="1"/>
       <c r="K7235" s="1"/>
     </row>
-    <row r="7236" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7236" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7236" s="1"/>
       <c r="K7236" s="1"/>
     </row>
-    <row r="7237" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7237" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7237" s="1"/>
       <c r="K7237" s="1"/>
     </row>
-    <row r="7238" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7238" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7238" s="2"/>
       <c r="I7238" s="1"/>
       <c r="K7238" s="1"/>
     </row>
-    <row r="7239" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7239" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7239" s="2"/>
       <c r="I7239" s="1"/>
       <c r="K7239" s="1"/>
     </row>
-    <row r="7240" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7240" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7240" s="1"/>
       <c r="K7240" s="1"/>
     </row>
-    <row r="7241" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7241" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7241" s="1"/>
       <c r="K7241" s="1"/>
     </row>
-    <row r="7242" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7242" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7242" s="1"/>
       <c r="K7242" s="1"/>
     </row>
-    <row r="7243" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7243" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7243" s="2"/>
       <c r="I7243" s="1"/>
       <c r="K7243" s="1"/>
     </row>
-    <row r="7244" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7244" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7244" s="2"/>
       <c r="I7244" s="1"/>
       <c r="K7244" s="1"/>
     </row>
-    <row r="7245" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7245" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7245" s="2"/>
       <c r="I7245" s="1"/>
       <c r="K7245" s="1"/>
     </row>
-    <row r="7246" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7246" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7246" s="1"/>
       <c r="K7246" s="1"/>
     </row>
-    <row r="7247" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7247" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7247" s="1"/>
       <c r="K7247" s="1"/>
     </row>
-    <row r="7248" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7248" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7248" s="2"/>
       <c r="I7248" s="1"/>
       <c r="K7248" s="1"/>
     </row>
     <row r="7249" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7249" s="2"/>
       <c r="I7249" s="1"/>
       <c r="K7249" s="1"/>
     </row>
@@ -45345,26 +47151,32 @@
       <c r="K7252" s="1"/>
     </row>
     <row r="7253" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7253" s="2"/>
       <c r="I7253" s="1"/>
       <c r="K7253" s="1"/>
     </row>
     <row r="7254" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7254" s="2"/>
       <c r="I7254" s="1"/>
       <c r="K7254" s="1"/>
     </row>
     <row r="7255" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7255" s="2"/>
       <c r="I7255" s="1"/>
       <c r="K7255" s="1"/>
     </row>
     <row r="7256" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7256" s="2"/>
       <c r="I7256" s="1"/>
       <c r="K7256" s="1"/>
     </row>
     <row r="7257" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7257" s="2"/>
       <c r="I7257" s="1"/>
       <c r="K7257" s="1"/>
     </row>
     <row r="7258" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7258" s="2"/>
       <c r="I7258" s="1"/>
       <c r="K7258" s="1"/>
     </row>
@@ -45395,6 +47207,7 @@
       <c r="I7264" s="1"/>
     </row>
     <row r="7265" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7265" s="2"/>
       <c r="I7265" s="1"/>
       <c r="J7265" s="2"/>
       <c r="K7265" s="1"/>
@@ -45404,10 +47217,12 @@
       <c r="K7266" s="1"/>
     </row>
     <row r="7267" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7267" s="2"/>
       <c r="I7267" s="1"/>
       <c r="K7267" s="1"/>
     </row>
     <row r="7268" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7268" s="2"/>
       <c r="I7268" s="1"/>
       <c r="K7268" s="1"/>
     </row>
@@ -45420,14 +47235,17 @@
       <c r="K7270" s="1"/>
     </row>
     <row r="7271" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7271" s="2"/>
       <c r="I7271" s="1"/>
       <c r="K7271" s="1"/>
     </row>
     <row r="7272" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7272" s="2"/>
       <c r="I7272" s="1"/>
       <c r="K7272" s="1"/>
     </row>
     <row r="7273" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7273" s="2"/>
       <c r="I7273" s="1"/>
       <c r="K7273" s="1"/>
     </row>
@@ -45436,14 +47254,17 @@
       <c r="K7274" s="1"/>
     </row>
     <row r="7275" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7275" s="2"/>
       <c r="I7275" s="1"/>
       <c r="K7275" s="1"/>
     </row>
     <row r="7276" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7276" s="2"/>
       <c r="I7276" s="1"/>
       <c r="K7276" s="1"/>
     </row>
     <row r="7277" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7277" s="2"/>
       <c r="I7277" s="1"/>
       <c r="K7277" s="1"/>
     </row>
@@ -45462,26 +47283,32 @@
       <c r="K7280" s="1"/>
     </row>
     <row r="7281" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7281" s="2"/>
       <c r="I7281" s="1"/>
       <c r="K7281" s="1"/>
     </row>
     <row r="7282" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7282" s="2"/>
       <c r="I7282" s="1"/>
       <c r="K7282" s="1"/>
     </row>
     <row r="7283" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7283" s="2"/>
       <c r="I7283" s="1"/>
       <c r="K7283" s="1"/>
     </row>
     <row r="7284" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7284" s="2"/>
       <c r="I7284" s="1"/>
       <c r="K7284" s="1"/>
     </row>
     <row r="7285" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7285" s="2"/>
       <c r="I7285" s="1"/>
       <c r="K7285" s="1"/>
     </row>
     <row r="7286" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7286" s="2"/>
       <c r="I7286" s="1"/>
       <c r="K7286" s="1"/>
     </row>
@@ -45500,6 +47327,7 @@
       <c r="K7289" s="1"/>
     </row>
     <row r="7290" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7290" s="2"/>
       <c r="I7290" s="1"/>
       <c r="K7290" s="1"/>
     </row>
@@ -45508,10 +47336,12 @@
       <c r="K7291" s="1"/>
     </row>
     <row r="7292" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7292" s="2"/>
       <c r="I7292" s="1"/>
       <c r="K7292" s="1"/>
     </row>
     <row r="7293" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7293" s="2"/>
       <c r="I7293" s="1"/>
       <c r="K7293" s="1"/>
     </row>
@@ -45520,6 +47350,7 @@
       <c r="K7294" s="1"/>
     </row>
     <row r="7295" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7295" s="2"/>
       <c r="I7295" s="1"/>
       <c r="K7295" s="1"/>
     </row>
@@ -45532,10 +47363,12 @@
       <c r="K7297" s="1"/>
     </row>
     <row r="7298" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7298" s="2"/>
       <c r="I7298" s="1"/>
       <c r="K7298" s="1"/>
     </row>
     <row r="7299" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7299" s="2"/>
       <c r="I7299" s="1"/>
       <c r="K7299" s="1"/>
     </row>
@@ -45544,6 +47377,7 @@
       <c r="K7300" s="1"/>
     </row>
     <row r="7301" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7301" s="2"/>
       <c r="I7301" s="1"/>
       <c r="K7301" s="1"/>
     </row>
@@ -45552,14 +47386,17 @@
       <c r="K7302" s="1"/>
     </row>
     <row r="7303" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7303" s="2"/>
       <c r="I7303" s="1"/>
       <c r="K7303" s="1"/>
     </row>
     <row r="7304" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7304" s="2"/>
       <c r="I7304" s="1"/>
       <c r="K7304" s="1"/>
     </row>
     <row r="7305" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7305" s="2"/>
       <c r="I7305" s="1"/>
       <c r="K7305" s="1"/>
     </row>
@@ -45568,14 +47405,17 @@
       <c r="K7306" s="1"/>
     </row>
     <row r="7307" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7307" s="2"/>
       <c r="I7307" s="1"/>
       <c r="K7307" s="1"/>
     </row>
     <row r="7308" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7308" s="2"/>
       <c r="I7308" s="1"/>
       <c r="K7308" s="1"/>
     </row>
     <row r="7309" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7309" s="2"/>
       <c r="I7309" s="1"/>
       <c r="K7309" s="1"/>
     </row>
@@ -45592,76 +47432,85 @@
       <c r="I7312" s="1"/>
       <c r="K7312" s="1"/>
     </row>
-    <row r="7313" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7313" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7313" s="1"/>
       <c r="J7313" s="2"/>
       <c r="K7313" s="1"/>
     </row>
-    <row r="7314" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7314" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7314" s="2"/>
       <c r="I7314" s="1"/>
       <c r="K7314" s="1"/>
     </row>
-    <row r="7315" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7315" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7315" s="1"/>
       <c r="K7315" s="1"/>
     </row>
-    <row r="7316" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7316" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7316" s="1"/>
       <c r="K7316" s="1"/>
     </row>
-    <row r="7317" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7317" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7317" s="2"/>
       <c r="I7317" s="1"/>
       <c r="K7317" s="1"/>
     </row>
-    <row r="7318" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7318" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7318" s="2"/>
       <c r="I7318" s="1"/>
       <c r="K7318" s="1"/>
     </row>
-    <row r="7319" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7319" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7319" s="1"/>
       <c r="K7319" s="1"/>
     </row>
-    <row r="7320" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7320" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7320" s="1"/>
       <c r="K7320" s="1"/>
     </row>
-    <row r="7321" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7321" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7321" s="1"/>
       <c r="K7321" s="1"/>
     </row>
-    <row r="7322" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7322" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7322" s="1"/>
       <c r="K7322" s="1"/>
     </row>
-    <row r="7323" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7323" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7323" s="2"/>
       <c r="I7323" s="1"/>
       <c r="K7323" s="1"/>
     </row>
-    <row r="7324" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7324" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7324" s="2"/>
       <c r="I7324" s="1"/>
       <c r="K7324" s="1"/>
     </row>
-    <row r="7325" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7325" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7325" s="2"/>
       <c r="I7325" s="1"/>
       <c r="K7325" s="1"/>
     </row>
-    <row r="7326" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7326" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7326" s="1"/>
       <c r="K7326" s="1"/>
     </row>
-    <row r="7327" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7327" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7327" s="1"/>
       <c r="K7327" s="1"/>
     </row>
-    <row r="7328" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7328" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7328" s="2"/>
       <c r="I7328" s="1"/>
       <c r="K7328" s="1"/>
     </row>
     <row r="7329" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7329" s="2"/>
       <c r="I7329" s="1"/>
       <c r="K7329" s="1"/>
     </row>
     <row r="7330" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7330" s="2"/>
       <c r="I7330" s="1"/>
       <c r="K7330" s="1"/>
     </row>
@@ -45675,31 +47524,38 @@
       <c r="K7332" s="1"/>
     </row>
     <row r="7333" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7333" s="2"/>
       <c r="I7333" s="1"/>
       <c r="J7333" s="2"/>
       <c r="K7333" s="1"/>
     </row>
     <row r="7334" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7334" s="2"/>
       <c r="I7334" s="1"/>
       <c r="K7334" s="1"/>
     </row>
     <row r="7335" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7335" s="2"/>
       <c r="I7335" s="1"/>
       <c r="K7335" s="1"/>
     </row>
     <row r="7336" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7336" s="2"/>
       <c r="I7336" s="1"/>
       <c r="K7336" s="1"/>
     </row>
     <row r="7337" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7337" s="2"/>
       <c r="I7337" s="1"/>
       <c r="K7337" s="1"/>
     </row>
     <row r="7338" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7338" s="2"/>
       <c r="I7338" s="1"/>
       <c r="K7338" s="1"/>
     </row>
     <row r="7339" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7339" s="2"/>
       <c r="I7339" s="1"/>
       <c r="K7339" s="1"/>
     </row>
@@ -45712,10 +47568,12 @@
       <c r="K7341" s="1"/>
     </row>
     <row r="7342" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7342" s="2"/>
       <c r="I7342" s="1"/>
       <c r="K7342" s="1"/>
     </row>
     <row r="7343" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7343" s="2"/>
       <c r="I7343" s="1"/>
       <c r="K7343" s="1"/>
     </row>
@@ -45724,10 +47582,12 @@
       <c r="K7344" s="1"/>
     </row>
     <row r="7345" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7345" s="2"/>
       <c r="I7345" s="1"/>
       <c r="K7345" s="1"/>
     </row>
     <row r="7346" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7346" s="2"/>
       <c r="I7346" s="1"/>
       <c r="K7346" s="1"/>
     </row>
@@ -45736,6 +47596,7 @@
       <c r="K7347" s="1"/>
     </row>
     <row r="7348" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7348" s="2"/>
       <c r="I7348" s="1"/>
       <c r="K7348" s="1"/>
     </row>
@@ -45750,10 +47611,12 @@
       <c r="K7350" s="1"/>
     </row>
     <row r="7351" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7351" s="2"/>
       <c r="I7351" s="1"/>
       <c r="K7351" s="1"/>
     </row>
     <row r="7352" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7352" s="2"/>
       <c r="I7352" s="1"/>
       <c r="K7352" s="1"/>
     </row>
@@ -45762,10 +47625,12 @@
       <c r="K7353" s="1"/>
     </row>
     <row r="7354" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7354" s="2"/>
       <c r="I7354" s="1"/>
       <c r="K7354" s="1"/>
     </row>
     <row r="7355" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7355" s="2"/>
       <c r="I7355" s="1"/>
       <c r="K7355" s="1"/>
     </row>
@@ -45779,6 +47644,7 @@
       <c r="K7357" s="1"/>
     </row>
     <row r="7358" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7358" s="2"/>
       <c r="I7358" s="1"/>
       <c r="J7358" s="2"/>
       <c r="K7358" s="1"/>
@@ -45794,14 +47660,17 @@
       <c r="K7360" s="1"/>
     </row>
     <row r="7361" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7361" s="2"/>
       <c r="I7361" s="1"/>
       <c r="K7361" s="1"/>
     </row>
     <row r="7362" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7362" s="2"/>
       <c r="I7362" s="1"/>
       <c r="K7362" s="1"/>
     </row>
     <row r="7363" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7363" s="2"/>
       <c r="I7363" s="1"/>
       <c r="K7363" s="1"/>
     </row>
@@ -45819,14 +47688,17 @@
       <c r="I7366" s="1"/>
     </row>
     <row r="7367" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7367" s="2"/>
       <c r="I7367" s="1"/>
       <c r="K7367" s="1"/>
     </row>
     <row r="7368" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7368" s="2"/>
       <c r="I7368" s="1"/>
       <c r="K7368" s="1"/>
     </row>
     <row r="7369" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7369" s="2"/>
       <c r="I7369" s="1"/>
       <c r="K7369" s="1"/>
     </row>
@@ -45839,10 +47711,12 @@
       <c r="K7371" s="1"/>
     </row>
     <row r="7372" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7372" s="2"/>
       <c r="I7372" s="1"/>
       <c r="K7372" s="1"/>
     </row>
     <row r="7373" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7373" s="2"/>
       <c r="I7373" s="1"/>
       <c r="K7373" s="1"/>
     </row>
@@ -45851,14 +47725,17 @@
       <c r="K7374" s="1"/>
     </row>
     <row r="7375" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7375" s="2"/>
       <c r="I7375" s="1"/>
       <c r="K7375" s="1"/>
     </row>
     <row r="7376" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7376" s="2"/>
       <c r="I7376" s="1"/>
       <c r="K7376" s="1"/>
     </row>
     <row r="7377" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7377" s="2"/>
       <c r="I7377" s="1"/>
       <c r="K7377" s="1"/>
     </row>
@@ -45867,10 +47744,12 @@
       <c r="K7378" s="1"/>
     </row>
     <row r="7379" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7379" s="2"/>
       <c r="I7379" s="1"/>
       <c r="K7379" s="1"/>
     </row>
     <row r="7380" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7380" s="2"/>
       <c r="I7380" s="1"/>
       <c r="K7380" s="1"/>
     </row>
@@ -45879,14 +47758,17 @@
       <c r="K7381" s="1"/>
     </row>
     <row r="7382" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7382" s="2"/>
       <c r="I7382" s="1"/>
       <c r="K7382" s="1"/>
     </row>
     <row r="7383" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7383" s="2"/>
       <c r="I7383" s="1"/>
       <c r="K7383" s="1"/>
     </row>
     <row r="7384" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7384" s="2"/>
       <c r="I7384" s="1"/>
       <c r="K7384" s="1"/>
     </row>
@@ -45908,6 +47790,7 @@
       <c r="K7388" s="1"/>
     </row>
     <row r="7389" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7389" s="2"/>
       <c r="I7389" s="1"/>
       <c r="J7389" s="2"/>
       <c r="K7389" s="1"/>
@@ -45916,39 +47799,65 @@
       <c r="I7390" s="1"/>
     </row>
     <row r="7391" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7391" s="2"/>
       <c r="I7391" s="1"/>
       <c r="K7391" s="1"/>
     </row>
     <row r="7392" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7392" s="2"/>
       <c r="I7392" s="1"/>
       <c r="K7392" s="1"/>
     </row>
-    <row r="7393" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7393" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7393" s="2"/>
       <c r="I7393" s="1"/>
       <c r="K7393" s="1"/>
     </row>
-    <row r="7394" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7394" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="I7394" s="1"/>
       <c r="K7394" s="1"/>
     </row>
-    <row r="7395" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7395" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7395" s="2"/>
       <c r="I7395" s="1"/>
       <c r="K7395" s="1"/>
     </row>
-    <row r="7396" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7396" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7396" s="2"/>
       <c r="I7396" s="1"/>
       <c r="K7396" s="1"/>
     </row>
-    <row r="7397" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7397" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7397" s="2"/>
       <c r="I7397" s="1"/>
     </row>
-    <row r="7398" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7398" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="I7398" s="1"/>
       <c r="K7398" s="1"/>
     </row>
-    <row r="7399" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7399" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7399" s="2"/>
+      <c r="I7399" s="1"/>
       <c r="K7399" s="1"/>
     </row>
-    <row r="7400" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7400" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="I7400" s="1"/>
       <c r="K7400" s="1"/>
+    </row>
+    <row r="7401" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7401" s="2"/>
+      <c r="I7401" s="1"/>
+    </row>
+    <row r="7402" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7402" s="2"/>
+      <c r="I7402" s="1"/>
+    </row>
+    <row r="7403" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="I7403" s="1"/>
+    </row>
+    <row r="7404" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7404" s="2"/>
+      <c r="I7404" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Pep-Move\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{39A00D71-ADA1-4E7F-9EEF-1C80FBEC2E0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E22BAA67-7188-498F-9C65-BA1AC1BAB223}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3585" yWindow="3585" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="863" uniqueCount="95">
   <si>
     <t>Company Name</t>
   </si>
@@ -697,7 +697,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="A1:K7404"/>
+  <dimension ref="A1:K7403"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -773,7 +773,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H3" s="2"/>
       <c r="I3" s="1"/>
       <c r="J3" s="2"/>
@@ -905,7 +905,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>19</v>
       </c>
@@ -1021,7 +1021,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>19</v>
       </c>
@@ -1356,7 +1356,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>19</v>
       </c>
@@ -1509,7 +1509,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>19</v>
       </c>
@@ -1778,7 +1778,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>19</v>
       </c>
@@ -2105,7 +2105,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="54" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
         <v>19</v>
       </c>
@@ -2643,7 +2643,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
         <v>19</v>
       </c>
@@ -2875,7 +2875,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="82" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
         <v>19</v>
       </c>
@@ -3092,10 +3092,10 @@
         <v>18</v>
       </c>
       <c r="G89" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H89" s="2">
-        <v>1.1458333333333333E-2</v>
+        <v>2.326388888888889E-2</v>
       </c>
       <c r="I89" s="1">
         <v>46218.587268518517</v>
@@ -3108,11 +3108,32 @@
       </c>
     </row>
     <row r="90" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H90" s="2"/>
-      <c r="I90" s="1"/>
-      <c r="J90" s="2"/>
+      <c r="B90" t="s">
+        <v>19</v>
+      </c>
+      <c r="C90">
+        <v>5675</v>
+      </c>
+      <c r="D90" t="s">
+        <v>33</v>
+      </c>
+      <c r="F90" t="s">
+        <v>18</v>
+      </c>
+      <c r="G90" t="s">
+        <v>10</v>
+      </c>
+      <c r="H90" s="2">
+        <v>2.5416666666666667E-2</v>
+      </c>
+      <c r="I90" s="1">
+        <v>46218.587268518517</v>
+      </c>
+      <c r="J90" s="2">
+        <v>0</v>
+      </c>
       <c r="K90" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="91" spans="2:11" x14ac:dyDescent="0.25">
@@ -3120,10 +3141,10 @@
         <v>19</v>
       </c>
       <c r="C91">
-        <v>5675</v>
+        <v>5689</v>
       </c>
       <c r="D91" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="F91" t="s">
         <v>18</v>
@@ -3132,10 +3153,10 @@
         <v>10</v>
       </c>
       <c r="H91" s="2">
-        <v>2.5416666666666667E-2</v>
+        <v>2.2650462962962963E-2</v>
       </c>
       <c r="I91" s="1">
-        <v>46218.587268518517</v>
+        <v>46218.587962962964</v>
       </c>
       <c r="J91" s="2">
         <v>0</v>
@@ -3144,15 +3165,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="92" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B92" t="s">
         <v>19</v>
       </c>
       <c r="C92">
-        <v>5689</v>
+        <v>5682</v>
       </c>
       <c r="D92" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="F92" t="s">
         <v>18</v>
@@ -3161,10 +3182,10 @@
         <v>10</v>
       </c>
       <c r="H92" s="2">
-        <v>2.2650462962962963E-2</v>
+        <v>2.2164351851851852E-2</v>
       </c>
       <c r="I92" s="1">
-        <v>46218.587962962964</v>
+        <v>46218.58865740741</v>
       </c>
       <c r="J92" s="2">
         <v>0</v>
@@ -3178,25 +3199,25 @@
         <v>19</v>
       </c>
       <c r="C93">
-        <v>5682</v>
+        <v>5732</v>
       </c>
       <c r="D93" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="F93" t="s">
         <v>18</v>
       </c>
       <c r="G93" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H93" s="2">
-        <v>2.2164351851851852E-2</v>
+        <v>0</v>
       </c>
       <c r="I93" s="1">
-        <v>46218.58865740741</v>
+        <v>46218.58935185185</v>
       </c>
       <c r="J93" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K93" s="1" t="s">
         <v>11</v>
@@ -3207,25 +3228,25 @@
         <v>19</v>
       </c>
       <c r="C94">
-        <v>5732</v>
+        <v>5702</v>
       </c>
       <c r="D94" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F94" t="s">
         <v>18</v>
       </c>
       <c r="G94" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H94" s="2">
-        <v>0</v>
+        <v>6.5624999999999998E-3</v>
       </c>
       <c r="I94" s="1">
         <v>46218.58935185185</v>
       </c>
       <c r="J94" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K94" s="1" t="s">
         <v>11</v>
@@ -3236,10 +3257,10 @@
         <v>19</v>
       </c>
       <c r="C95">
-        <v>5702</v>
+        <v>5701</v>
       </c>
       <c r="D95" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="F95" t="s">
         <v>18</v>
@@ -3248,13 +3269,13 @@
         <v>10</v>
       </c>
       <c r="H95" s="2">
-        <v>6.5624999999999998E-3</v>
+        <v>4.5416666666666668E-2</v>
       </c>
       <c r="I95" s="1">
-        <v>46218.58935185185</v>
+        <v>46218.590046296296</v>
       </c>
       <c r="J95" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K95" s="1" t="s">
         <v>11</v>
@@ -3265,10 +3286,10 @@
         <v>19</v>
       </c>
       <c r="C96">
-        <v>5701</v>
+        <v>5708</v>
       </c>
       <c r="D96" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="F96" t="s">
         <v>18</v>
@@ -3277,13 +3298,13 @@
         <v>10</v>
       </c>
       <c r="H96" s="2">
-        <v>4.5416666666666668E-2</v>
+        <v>2.9444444444444443E-2</v>
       </c>
       <c r="I96" s="1">
-        <v>46218.590046296296</v>
+        <v>46218.590740740743</v>
       </c>
       <c r="J96" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K96" s="1" t="s">
         <v>11</v>
@@ -3294,10 +3315,10 @@
         <v>19</v>
       </c>
       <c r="C97">
-        <v>5708</v>
+        <v>5670</v>
       </c>
       <c r="D97" t="s">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="F97" t="s">
         <v>18</v>
@@ -3306,13 +3327,13 @@
         <v>10</v>
       </c>
       <c r="H97" s="2">
-        <v>2.9444444444444443E-2</v>
+        <v>2.3321759259259261E-2</v>
       </c>
       <c r="I97" s="1">
         <v>46218.590740740743</v>
       </c>
       <c r="J97" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K97" s="1" t="s">
         <v>11</v>
@@ -3323,65 +3344,65 @@
         <v>19</v>
       </c>
       <c r="C98">
-        <v>5670</v>
+        <v>5719</v>
       </c>
       <c r="D98" t="s">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="F98" t="s">
         <v>18</v>
       </c>
       <c r="G98" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H98" s="2">
-        <v>2.3321759259259261E-2</v>
+        <v>0</v>
       </c>
       <c r="I98" s="1">
-        <v>46218.590740740743</v>
+        <v>46218.591435185182</v>
       </c>
       <c r="J98" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K98" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="99" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B99" t="s">
+      <c r="H99" s="2"/>
+      <c r="I99" s="1"/>
+      <c r="J99" s="2"/>
+      <c r="K99" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="100" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B100" t="s">
         <v>19</v>
       </c>
-      <c r="C99">
-        <v>5719</v>
-      </c>
-      <c r="D99" t="s">
-        <v>93</v>
-      </c>
-      <c r="F99" t="s">
+      <c r="C100">
+        <v>6002</v>
+      </c>
+      <c r="D100" t="s">
+        <v>94</v>
+      </c>
+      <c r="F100" t="s">
         <v>18</v>
       </c>
-      <c r="G99" t="s">
-        <v>14</v>
-      </c>
-      <c r="H99" s="2">
+      <c r="G100" t="s">
+        <v>10</v>
+      </c>
+      <c r="H100" s="2">
+        <v>2.5405092592592594E-2</v>
+      </c>
+      <c r="I100" s="1">
+        <v>46224.668287037035</v>
+      </c>
+      <c r="J100" s="2">
         <v>0</v>
       </c>
-      <c r="I99" s="1">
-        <v>46218.591435185182</v>
-      </c>
-      <c r="J99" s="2">
-        <v>1</v>
-      </c>
-      <c r="K99" s="1" t="s">
+      <c r="K100" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="100" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H100" s="2"/>
-      <c r="I100" s="1"/>
-      <c r="J100" s="2"/>
-      <c r="K100" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="101" spans="2:11" x14ac:dyDescent="0.25">
@@ -3389,22 +3410,22 @@
         <v>19</v>
       </c>
       <c r="C101">
-        <v>6002</v>
+        <v>5717</v>
       </c>
       <c r="D101" t="s">
-        <v>94</v>
+        <v>22</v>
       </c>
       <c r="F101" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G101" t="s">
         <v>10</v>
       </c>
       <c r="H101" s="2">
-        <v>2.5405092592592594E-2</v>
+        <v>6.6550925925925927E-3</v>
       </c>
       <c r="I101" s="1">
-        <v>46224.668287037035</v>
+        <v>46237.840277777781</v>
       </c>
       <c r="J101" s="2">
         <v>0</v>
@@ -3418,10 +3439,10 @@
         <v>19</v>
       </c>
       <c r="C102">
-        <v>5717</v>
+        <v>5747</v>
       </c>
       <c r="D102" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F102" t="s">
         <v>16</v>
@@ -3430,13 +3451,13 @@
         <v>10</v>
       </c>
       <c r="H102" s="2">
-        <v>6.6550925925925927E-3</v>
+        <v>5.7534722222222223E-2</v>
       </c>
       <c r="I102" s="1">
-        <v>46237.840277777781</v>
+        <v>46237.84097222222</v>
       </c>
       <c r="J102" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K102" s="1" t="s">
         <v>11</v>
@@ -3447,22 +3468,22 @@
         <v>19</v>
       </c>
       <c r="C103">
-        <v>5747</v>
+        <v>5715</v>
       </c>
       <c r="D103" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F103" t="s">
         <v>16</v>
       </c>
       <c r="G103" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H103" s="2">
-        <v>2.650462962962963E-3</v>
+        <v>8.3564814814814821E-3</v>
       </c>
       <c r="I103" s="1">
-        <v>46237.84097222222</v>
+        <v>46237.841666666667</v>
       </c>
       <c r="J103" s="2">
         <v>0</v>
@@ -3472,11 +3493,32 @@
       </c>
     </row>
     <row r="104" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H104" s="2"/>
-      <c r="I104" s="1"/>
-      <c r="J104" s="2"/>
+      <c r="B104" t="s">
+        <v>19</v>
+      </c>
+      <c r="C104">
+        <v>5731</v>
+      </c>
+      <c r="D104" t="s">
+        <v>25</v>
+      </c>
+      <c r="F104" t="s">
+        <v>16</v>
+      </c>
+      <c r="G104" t="s">
+        <v>13</v>
+      </c>
+      <c r="H104" s="2">
+        <v>0</v>
+      </c>
+      <c r="I104" s="1">
+        <v>46237.841666666667</v>
+      </c>
+      <c r="J104" s="2">
+        <v>3</v>
+      </c>
       <c r="K104" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="105" spans="2:11" x14ac:dyDescent="0.25">
@@ -3484,10 +3526,10 @@
         <v>19</v>
       </c>
       <c r="C105">
-        <v>5715</v>
+        <v>5741</v>
       </c>
       <c r="D105" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F105" t="s">
         <v>16</v>
@@ -3496,10 +3538,10 @@
         <v>10</v>
       </c>
       <c r="H105" s="2">
-        <v>8.3564814814814821E-3</v>
+        <v>5.8333333333333336E-3</v>
       </c>
       <c r="I105" s="1">
-        <v>46237.841666666667</v>
+        <v>46237.842361111114</v>
       </c>
       <c r="J105" s="2">
         <v>0</v>
@@ -3513,25 +3555,25 @@
         <v>19</v>
       </c>
       <c r="C106">
-        <v>5731</v>
+        <v>5688</v>
       </c>
       <c r="D106" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F106" t="s">
         <v>16</v>
       </c>
       <c r="G106" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H106" s="2">
-        <v>0</v>
+        <v>7.8472222222222224E-3</v>
       </c>
       <c r="I106" s="1">
-        <v>46237.841666666667</v>
+        <v>46237.843055555553</v>
       </c>
       <c r="J106" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K106" s="1" t="s">
         <v>11</v>
@@ -3542,10 +3584,10 @@
         <v>19</v>
       </c>
       <c r="C107">
-        <v>5741</v>
+        <v>5678</v>
       </c>
       <c r="D107" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F107" t="s">
         <v>16</v>
@@ -3554,10 +3596,10 @@
         <v>10</v>
       </c>
       <c r="H107" s="2">
-        <v>5.8333333333333336E-3</v>
+        <v>9.4560185185185181E-3</v>
       </c>
       <c r="I107" s="1">
-        <v>46237.842361111114</v>
+        <v>46237.843055555553</v>
       </c>
       <c r="J107" s="2">
         <v>0</v>
@@ -3571,22 +3613,22 @@
         <v>19</v>
       </c>
       <c r="C108">
-        <v>5688</v>
+        <v>5676</v>
       </c>
       <c r="D108" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F108" t="s">
         <v>16</v>
       </c>
       <c r="G108" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H108" s="2">
-        <v>0</v>
+        <v>5.4166666666666669E-3</v>
       </c>
       <c r="I108" s="1">
-        <v>46237.843055555553</v>
+        <v>46237.84375</v>
       </c>
       <c r="J108" s="2">
         <v>0</v>
@@ -3600,25 +3642,25 @@
         <v>19</v>
       </c>
       <c r="C109">
-        <v>5678</v>
+        <v>5686</v>
       </c>
       <c r="D109" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F109" t="s">
         <v>16</v>
       </c>
       <c r="G109" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H109" s="2">
-        <v>9.4560185185185181E-3</v>
+        <v>0</v>
       </c>
       <c r="I109" s="1">
-        <v>46237.843055555553</v>
+        <v>46237.844444444447</v>
       </c>
       <c r="J109" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K109" s="1" t="s">
         <v>11</v>
@@ -3629,10 +3671,10 @@
         <v>19</v>
       </c>
       <c r="C110">
-        <v>5676</v>
+        <v>5714</v>
       </c>
       <c r="D110" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F110" t="s">
         <v>16</v>
@@ -3641,10 +3683,10 @@
         <v>10</v>
       </c>
       <c r="H110" s="2">
-        <v>5.4166666666666669E-3</v>
+        <v>5.8564814814814816E-3</v>
       </c>
       <c r="I110" s="1">
-        <v>46237.84375</v>
+        <v>46237.844444444447</v>
       </c>
       <c r="J110" s="2">
         <v>0</v>
@@ -3658,22 +3700,22 @@
         <v>19</v>
       </c>
       <c r="C111">
-        <v>5686</v>
+        <v>5705</v>
       </c>
       <c r="D111" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F111" t="s">
         <v>16</v>
       </c>
       <c r="G111" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H111" s="2">
-        <v>0</v>
+        <v>1.3055555555555556E-2</v>
       </c>
       <c r="I111" s="1">
-        <v>46237.844444444447</v>
+        <v>46237.845138888886</v>
       </c>
       <c r="J111" s="2">
         <v>0</v>
@@ -3682,15 +3724,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="112" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B112" t="s">
         <v>19</v>
       </c>
       <c r="C112">
-        <v>5714</v>
+        <v>5669</v>
       </c>
       <c r="D112" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="F112" t="s">
         <v>16</v>
@@ -3699,13 +3741,13 @@
         <v>10</v>
       </c>
       <c r="H112" s="2">
-        <v>5.8564814814814816E-3</v>
+        <v>7.037037037037037E-3</v>
       </c>
       <c r="I112" s="1">
-        <v>46237.844444444447</v>
+        <v>46237.845833333333</v>
       </c>
       <c r="J112" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K112" s="1" t="s">
         <v>11</v>
@@ -3716,10 +3758,10 @@
         <v>19</v>
       </c>
       <c r="C113">
-        <v>5705</v>
+        <v>5675</v>
       </c>
       <c r="D113" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F113" t="s">
         <v>16</v>
@@ -3728,10 +3770,10 @@
         <v>10</v>
       </c>
       <c r="H113" s="2">
-        <v>1.3055555555555556E-2</v>
+        <v>1.119212962962963E-2</v>
       </c>
       <c r="I113" s="1">
-        <v>46237.845138888886</v>
+        <v>46237.84652777778</v>
       </c>
       <c r="J113" s="2">
         <v>0</v>
@@ -3745,39 +3787,39 @@
         <v>19</v>
       </c>
       <c r="C114">
-        <v>5669</v>
+        <v>5707</v>
       </c>
       <c r="D114" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="F114" t="s">
         <v>16</v>
       </c>
       <c r="G114" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H114" s="2">
-        <v>0</v>
+        <v>6.7013888888888887E-3</v>
       </c>
       <c r="I114" s="1">
-        <v>46237.845833333333</v>
+        <v>46237.84652777778</v>
       </c>
       <c r="J114" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K114" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="115" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B115" t="s">
         <v>19</v>
       </c>
       <c r="C115">
-        <v>5675</v>
+        <v>5722</v>
       </c>
       <c r="D115" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F115" t="s">
         <v>16</v>
@@ -3786,13 +3828,13 @@
         <v>10</v>
       </c>
       <c r="H115" s="2">
-        <v>1.119212962962963E-2</v>
+        <v>7.1875000000000003E-3</v>
       </c>
       <c r="I115" s="1">
-        <v>46237.84652777778</v>
+        <v>46237.847222222219</v>
       </c>
       <c r="J115" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K115" s="1" t="s">
         <v>11</v>
@@ -3803,36 +3845,57 @@
         <v>19</v>
       </c>
       <c r="C116">
-        <v>5707</v>
+        <v>5737</v>
       </c>
       <c r="D116" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F116" t="s">
         <v>16</v>
       </c>
       <c r="G116" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H116" s="2">
-        <v>1.9675925925925924E-3</v>
+        <v>0</v>
       </c>
       <c r="I116" s="1">
-        <v>46237.84652777778</v>
+        <v>46237.847916666666</v>
       </c>
       <c r="J116" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K116" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="117" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H117" s="2"/>
-      <c r="I117" s="1"/>
-      <c r="J117" s="2"/>
+      <c r="B117" t="s">
+        <v>19</v>
+      </c>
+      <c r="C117">
+        <v>5698</v>
+      </c>
+      <c r="D117" t="s">
+        <v>37</v>
+      </c>
+      <c r="F117" t="s">
+        <v>16</v>
+      </c>
+      <c r="G117" t="s">
+        <v>13</v>
+      </c>
+      <c r="H117" s="2">
+        <v>0</v>
+      </c>
+      <c r="I117" s="1">
+        <v>46237.847916666666</v>
+      </c>
+      <c r="J117" s="2">
+        <v>3</v>
+      </c>
       <c r="K117" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="118" spans="2:11" x14ac:dyDescent="0.25">
@@ -3840,36 +3903,57 @@
         <v>19</v>
       </c>
       <c r="C118">
-        <v>5722</v>
+        <v>5713</v>
       </c>
       <c r="D118" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F118" t="s">
         <v>16</v>
       </c>
       <c r="G118" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H118" s="2">
-        <v>2.0833333333333335E-4</v>
+        <v>1.1435185185185185E-2</v>
       </c>
       <c r="I118" s="1">
-        <v>46237.847222222219</v>
+        <v>46237.848611111112</v>
       </c>
       <c r="J118" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K118" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="119" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H119" s="2"/>
-      <c r="I119" s="1"/>
-      <c r="J119" s="2"/>
+      <c r="B119" t="s">
+        <v>19</v>
+      </c>
+      <c r="C119">
+        <v>5721</v>
+      </c>
+      <c r="D119" t="s">
+        <v>39</v>
+      </c>
+      <c r="F119" t="s">
+        <v>16</v>
+      </c>
+      <c r="G119" t="s">
+        <v>13</v>
+      </c>
+      <c r="H119" s="2">
+        <v>0</v>
+      </c>
+      <c r="I119" s="1">
+        <v>46237.849305555559</v>
+      </c>
+      <c r="J119" s="2">
+        <v>3</v>
+      </c>
       <c r="K119" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="120" spans="2:11" x14ac:dyDescent="0.25">
@@ -3877,10 +3961,10 @@
         <v>19</v>
       </c>
       <c r="C120">
-        <v>5737</v>
+        <v>5680</v>
       </c>
       <c r="D120" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F120" t="s">
         <v>16</v>
@@ -3892,10 +3976,10 @@
         <v>0</v>
       </c>
       <c r="I120" s="1">
-        <v>46237.847916666666</v>
+        <v>46237.849305555559</v>
       </c>
       <c r="J120" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K120" s="1" t="s">
         <v>11</v>
@@ -3906,22 +3990,22 @@
         <v>19</v>
       </c>
       <c r="C121">
-        <v>5698</v>
+        <v>5689</v>
       </c>
       <c r="D121" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F121" t="s">
         <v>16</v>
       </c>
       <c r="G121" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H121" s="2">
-        <v>0</v>
+        <v>6.828703703703704E-3</v>
       </c>
       <c r="I121" s="1">
-        <v>46237.847916666666</v>
+        <v>46237.85</v>
       </c>
       <c r="J121" s="2">
         <v>0</v>
@@ -3935,25 +4019,25 @@
         <v>19</v>
       </c>
       <c r="C122">
-        <v>5713</v>
+        <v>5687</v>
       </c>
       <c r="D122" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F122" t="s">
         <v>16</v>
       </c>
       <c r="G122" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H122" s="2">
-        <v>0</v>
+        <v>8.5300925925925926E-3</v>
       </c>
       <c r="I122" s="1">
-        <v>46237.848611111112</v>
+        <v>46237.85</v>
       </c>
       <c r="J122" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K122" s="1" t="s">
         <v>11</v>
@@ -3964,22 +4048,22 @@
         <v>19</v>
       </c>
       <c r="C123">
-        <v>5721</v>
+        <v>5727</v>
       </c>
       <c r="D123" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F123" t="s">
         <v>16</v>
       </c>
       <c r="G123" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H123" s="2">
-        <v>0</v>
+        <v>7.4189814814814813E-3</v>
       </c>
       <c r="I123" s="1">
-        <v>46237.849305555559</v>
+        <v>46237.850694444445</v>
       </c>
       <c r="J123" s="2">
         <v>0</v>
@@ -3993,22 +4077,22 @@
         <v>19</v>
       </c>
       <c r="C124">
-        <v>5680</v>
+        <v>5725</v>
       </c>
       <c r="D124" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F124" t="s">
         <v>16</v>
       </c>
       <c r="G124" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H124" s="2">
-        <v>0</v>
+        <v>5.5439814814814813E-3</v>
       </c>
       <c r="I124" s="1">
-        <v>46237.849305555559</v>
+        <v>46237.851388888892</v>
       </c>
       <c r="J124" s="2">
         <v>0</v>
@@ -4022,25 +4106,25 @@
         <v>19</v>
       </c>
       <c r="C125">
-        <v>5689</v>
+        <v>5709</v>
       </c>
       <c r="D125" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F125" t="s">
         <v>16</v>
       </c>
       <c r="G125" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H125" s="2">
-        <v>6.828703703703704E-3</v>
+        <v>0</v>
       </c>
       <c r="I125" s="1">
-        <v>46237.85</v>
+        <v>46237.852083333331</v>
       </c>
       <c r="J125" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K125" s="1" t="s">
         <v>11</v>
@@ -4051,22 +4135,22 @@
         <v>19</v>
       </c>
       <c r="C126">
-        <v>5687</v>
+        <v>5736</v>
       </c>
       <c r="D126" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F126" t="s">
         <v>16</v>
       </c>
       <c r="G126" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H126" s="2">
-        <v>0</v>
+        <v>5.8333333333333336E-3</v>
       </c>
       <c r="I126" s="1">
-        <v>46237.85</v>
+        <v>46237.852083333331</v>
       </c>
       <c r="J126" s="2">
         <v>0</v>
@@ -4075,15 +4159,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="127" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B127" t="s">
         <v>19</v>
       </c>
       <c r="C127">
-        <v>5727</v>
+        <v>5682</v>
       </c>
       <c r="D127" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="F127" t="s">
         <v>16</v>
@@ -4092,13 +4176,13 @@
         <v>10</v>
       </c>
       <c r="H127" s="2">
-        <v>7.4189814814814813E-3</v>
+        <v>5.5787037037037038E-3</v>
       </c>
       <c r="I127" s="1">
-        <v>46237.850694444445</v>
+        <v>46237.852777777778</v>
       </c>
       <c r="J127" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K127" s="1" t="s">
         <v>11</v>
@@ -4109,10 +4193,10 @@
         <v>19</v>
       </c>
       <c r="C128">
-        <v>5725</v>
+        <v>5729</v>
       </c>
       <c r="D128" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F128" t="s">
         <v>16</v>
@@ -4121,10 +4205,10 @@
         <v>10</v>
       </c>
       <c r="H128" s="2">
-        <v>5.5439814814814813E-3</v>
+        <v>1.4988425925925926E-2</v>
       </c>
       <c r="I128" s="1">
-        <v>46237.851388888892</v>
+        <v>46237.853472222225</v>
       </c>
       <c r="J128" s="2">
         <v>0</v>
@@ -4138,10 +4222,10 @@
         <v>19</v>
       </c>
       <c r="C129">
-        <v>5709</v>
+        <v>5696</v>
       </c>
       <c r="D129" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F129" t="s">
         <v>16</v>
@@ -4153,10 +4237,10 @@
         <v>0</v>
       </c>
       <c r="I129" s="1">
-        <v>46237.852083333331</v>
+        <v>46237.853472222225</v>
       </c>
       <c r="J129" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K129" s="1" t="s">
         <v>11</v>
@@ -4167,10 +4251,10 @@
         <v>19</v>
       </c>
       <c r="C130">
-        <v>5736</v>
+        <v>5716</v>
       </c>
       <c r="D130" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F130" t="s">
         <v>16</v>
@@ -4179,10 +4263,10 @@
         <v>10</v>
       </c>
       <c r="H130" s="2">
-        <v>5.8333333333333336E-3</v>
+        <v>8.9004629629629625E-3</v>
       </c>
       <c r="I130" s="1">
-        <v>46237.852083333331</v>
+        <v>46237.854166666664</v>
       </c>
       <c r="J130" s="2">
         <v>0</v>
@@ -4196,25 +4280,25 @@
         <v>19</v>
       </c>
       <c r="C131">
-        <v>5682</v>
+        <v>5720</v>
       </c>
       <c r="D131" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F131" t="s">
         <v>16</v>
       </c>
       <c r="G131" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H131" s="2">
-        <v>0</v>
+        <v>1.4513888888888889E-2</v>
       </c>
       <c r="I131" s="1">
-        <v>46237.852777777778</v>
+        <v>46237.854861111111</v>
       </c>
       <c r="J131" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K131" s="1" t="s">
         <v>11</v>
@@ -4225,57 +4309,36 @@
         <v>19</v>
       </c>
       <c r="C132">
-        <v>5729</v>
+        <v>5679</v>
       </c>
       <c r="D132" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F132" t="s">
         <v>16</v>
       </c>
       <c r="G132" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H132" s="2">
-        <v>1.4988425925925926E-2</v>
+        <v>6.018518518518519E-4</v>
       </c>
       <c r="I132" s="1">
-        <v>46237.853472222225</v>
+        <v>46237.854861111111</v>
       </c>
       <c r="J132" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K132" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="133" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B133" t="s">
-        <v>19</v>
-      </c>
-      <c r="C133">
-        <v>5696</v>
-      </c>
-      <c r="D133" t="s">
-        <v>49</v>
-      </c>
-      <c r="F133" t="s">
-        <v>16</v>
-      </c>
-      <c r="G133" t="s">
-        <v>13</v>
-      </c>
-      <c r="H133" s="2">
-        <v>0</v>
-      </c>
-      <c r="I133" s="1">
-        <v>46237.853472222225</v>
-      </c>
-      <c r="J133" s="2">
-        <v>0</v>
-      </c>
+      <c r="H133" s="2"/>
+      <c r="I133" s="1"/>
+      <c r="J133" s="2"/>
       <c r="K133" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="134" spans="2:11" x14ac:dyDescent="0.25">
@@ -4283,10 +4346,10 @@
         <v>19</v>
       </c>
       <c r="C134">
-        <v>5716</v>
+        <v>5711</v>
       </c>
       <c r="D134" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F134" t="s">
         <v>16</v>
@@ -4295,10 +4358,10 @@
         <v>10</v>
       </c>
       <c r="H134" s="2">
-        <v>8.9004629629629625E-3</v>
+        <v>6.2268518518518515E-3</v>
       </c>
       <c r="I134" s="1">
-        <v>46237.854166666664</v>
+        <v>46237.855555555558</v>
       </c>
       <c r="J134" s="2">
         <v>0</v>
@@ -4312,25 +4375,25 @@
         <v>19</v>
       </c>
       <c r="C135">
-        <v>5720</v>
+        <v>5732</v>
       </c>
       <c r="D135" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F135" t="s">
         <v>16</v>
       </c>
       <c r="G135" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H135" s="2">
-        <v>0</v>
+        <v>6.2152777777777779E-3</v>
       </c>
       <c r="I135" s="1">
-        <v>46237.854861111111</v>
+        <v>46237.856249999997</v>
       </c>
       <c r="J135" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K135" s="1" t="s">
         <v>11</v>
@@ -4341,10 +4404,10 @@
         <v>19</v>
       </c>
       <c r="C136">
-        <v>5679</v>
+        <v>5739</v>
       </c>
       <c r="D136" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F136" t="s">
         <v>16</v>
@@ -4356,10 +4419,10 @@
         <v>0</v>
       </c>
       <c r="I136" s="1">
-        <v>46237.854861111111</v>
+        <v>46237.856944444444</v>
       </c>
       <c r="J136" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K136" s="1" t="s">
         <v>11</v>
@@ -4370,10 +4433,10 @@
         <v>19</v>
       </c>
       <c r="C137">
-        <v>5711</v>
+        <v>5710</v>
       </c>
       <c r="D137" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F137" t="s">
         <v>16</v>
@@ -4382,10 +4445,10 @@
         <v>10</v>
       </c>
       <c r="H137" s="2">
-        <v>6.2268518518518515E-3</v>
+        <v>6.4351851851851853E-3</v>
       </c>
       <c r="I137" s="1">
-        <v>46237.855555555558</v>
+        <v>46237.857638888891</v>
       </c>
       <c r="J137" s="2">
         <v>0</v>
@@ -4399,36 +4462,57 @@
         <v>19</v>
       </c>
       <c r="C138">
-        <v>5732</v>
+        <v>5746</v>
       </c>
       <c r="D138" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F138" t="s">
         <v>16</v>
       </c>
       <c r="G138" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H138" s="2">
-        <v>1.0416666666666667E-4</v>
+        <v>0</v>
       </c>
       <c r="I138" s="1">
-        <v>46237.856249999997</v>
+        <v>46237.857638888891</v>
       </c>
       <c r="J138" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K138" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="139" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H139" s="2"/>
-      <c r="I139" s="1"/>
-      <c r="J139" s="2"/>
+      <c r="B139" t="s">
+        <v>19</v>
+      </c>
+      <c r="C139">
+        <v>5702</v>
+      </c>
+      <c r="D139" t="s">
+        <v>58</v>
+      </c>
+      <c r="F139" t="s">
+        <v>16</v>
+      </c>
+      <c r="G139" t="s">
+        <v>10</v>
+      </c>
+      <c r="H139" s="2">
+        <v>5.9953703703703705E-3</v>
+      </c>
+      <c r="I139" s="1">
+        <v>46237.85833333333</v>
+      </c>
+      <c r="J139" s="2">
+        <v>0</v>
+      </c>
       <c r="K139" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="140" spans="2:11" x14ac:dyDescent="0.25">
@@ -4436,10 +4520,10 @@
         <v>19</v>
       </c>
       <c r="C140">
-        <v>5739</v>
+        <v>5728</v>
       </c>
       <c r="D140" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F140" t="s">
         <v>16</v>
@@ -4451,10 +4535,10 @@
         <v>0</v>
       </c>
       <c r="I140" s="1">
-        <v>46237.856944444444</v>
+        <v>46237.859027777777</v>
       </c>
       <c r="J140" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K140" s="1" t="s">
         <v>11</v>
@@ -4465,25 +4549,25 @@
         <v>19</v>
       </c>
       <c r="C141">
-        <v>5710</v>
+        <v>5683</v>
       </c>
       <c r="D141" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F141" t="s">
         <v>16</v>
       </c>
       <c r="G141" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H141" s="2">
-        <v>6.4351851851851853E-3</v>
+        <v>0</v>
       </c>
       <c r="I141" s="1">
-        <v>46237.857638888891</v>
+        <v>46237.859722222223</v>
       </c>
       <c r="J141" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K141" s="1" t="s">
         <v>11</v>
@@ -4494,10 +4578,10 @@
         <v>19</v>
       </c>
       <c r="C142">
-        <v>5746</v>
+        <v>5745</v>
       </c>
       <c r="D142" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F142" t="s">
         <v>16</v>
@@ -4509,10 +4593,10 @@
         <v>0</v>
       </c>
       <c r="I142" s="1">
-        <v>46237.857638888891</v>
+        <v>46237.835532407407</v>
       </c>
       <c r="J142" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K142" s="1" t="s">
         <v>11</v>
@@ -4523,25 +4607,25 @@
         <v>19</v>
       </c>
       <c r="C143">
-        <v>5702</v>
+        <v>5733</v>
       </c>
       <c r="D143" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="F143" t="s">
         <v>16</v>
       </c>
       <c r="G143" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H143" s="2">
-        <v>5.9953703703703705E-3</v>
+        <v>0</v>
       </c>
       <c r="I143" s="1">
-        <v>46237.85833333333</v>
+        <v>46237.835532407407</v>
       </c>
       <c r="J143" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K143" s="1" t="s">
         <v>11</v>
@@ -4552,10 +4636,10 @@
         <v>19</v>
       </c>
       <c r="C144">
-        <v>5728</v>
+        <v>5704</v>
       </c>
       <c r="D144" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F144" t="s">
         <v>16</v>
@@ -4567,10 +4651,10 @@
         <v>0</v>
       </c>
       <c r="I144" s="1">
-        <v>46237.859027777777</v>
+        <v>46237.836226851854</v>
       </c>
       <c r="J144" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K144" s="1" t="s">
         <v>11</v>
@@ -4581,22 +4665,22 @@
         <v>19</v>
       </c>
       <c r="C145">
-        <v>5683</v>
+        <v>5693</v>
       </c>
       <c r="D145" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F145" t="s">
         <v>16</v>
       </c>
       <c r="G145" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H145" s="2">
-        <v>0</v>
+        <v>6.2500000000000003E-3</v>
       </c>
       <c r="I145" s="1">
-        <v>46237.859722222223</v>
+        <v>46237.836921296293</v>
       </c>
       <c r="J145" s="2">
         <v>0</v>
@@ -4610,25 +4694,25 @@
         <v>19</v>
       </c>
       <c r="C146">
-        <v>5745</v>
+        <v>5718</v>
       </c>
       <c r="D146" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F146" t="s">
         <v>16</v>
       </c>
       <c r="G146" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H146" s="2">
-        <v>0</v>
+        <v>7.1875000000000003E-3</v>
       </c>
       <c r="I146" s="1">
-        <v>46237.835532407407</v>
+        <v>46237.836921296293</v>
       </c>
       <c r="J146" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K146" s="1" t="s">
         <v>11</v>
@@ -4639,10 +4723,10 @@
         <v>19</v>
       </c>
       <c r="C147">
-        <v>5733</v>
+        <v>5700</v>
       </c>
       <c r="D147" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F147" t="s">
         <v>16</v>
@@ -4654,10 +4738,10 @@
         <v>0</v>
       </c>
       <c r="I147" s="1">
-        <v>46237.835532407407</v>
+        <v>46237.83761574074</v>
       </c>
       <c r="J147" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K147" s="1" t="s">
         <v>11</v>
@@ -4668,25 +4752,25 @@
         <v>19</v>
       </c>
       <c r="C148">
-        <v>5704</v>
+        <v>5726</v>
       </c>
       <c r="D148" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F148" t="s">
         <v>16</v>
       </c>
       <c r="G148" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H148" s="2">
-        <v>0</v>
+        <v>1.3425925925925926E-2</v>
       </c>
       <c r="I148" s="1">
-        <v>46237.836226851854</v>
+        <v>46237.838310185187</v>
       </c>
       <c r="J148" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K148" s="1" t="s">
         <v>11</v>
@@ -4697,25 +4781,25 @@
         <v>19</v>
       </c>
       <c r="C149">
-        <v>5693</v>
+        <v>5684</v>
       </c>
       <c r="D149" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F149" t="s">
         <v>16</v>
       </c>
       <c r="G149" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H149" s="2">
-        <v>6.2500000000000003E-3</v>
+        <v>0</v>
       </c>
       <c r="I149" s="1">
-        <v>46237.836921296293</v>
+        <v>46237.838310185187</v>
       </c>
       <c r="J149" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K149" s="1" t="s">
         <v>11</v>
@@ -4726,22 +4810,22 @@
         <v>19</v>
       </c>
       <c r="C150">
-        <v>5718</v>
+        <v>5740</v>
       </c>
       <c r="D150" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="F150" t="s">
         <v>16</v>
       </c>
       <c r="G150" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H150" s="2">
-        <v>0</v>
+        <v>1.1064814814814816E-2</v>
       </c>
       <c r="I150" s="1">
-        <v>46237.836921296293</v>
+        <v>46237.839004629626</v>
       </c>
       <c r="J150" s="2">
         <v>0</v>
@@ -4755,25 +4839,25 @@
         <v>19</v>
       </c>
       <c r="C151">
-        <v>5700</v>
+        <v>5701</v>
       </c>
       <c r="D151" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F151" t="s">
         <v>16</v>
       </c>
       <c r="G151" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H151" s="2">
-        <v>0</v>
+        <v>0.10394675925925925</v>
       </c>
       <c r="I151" s="1">
-        <v>46237.83761574074</v>
+        <v>46237.839699074073</v>
       </c>
       <c r="J151" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K151" s="1" t="s">
         <v>11</v>
@@ -4784,57 +4868,36 @@
         <v>19</v>
       </c>
       <c r="C152">
-        <v>5726</v>
+        <v>5695</v>
       </c>
       <c r="D152" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="F152" t="s">
         <v>16</v>
       </c>
       <c r="G152" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H152" s="2">
-        <v>0</v>
+        <v>6.134259259259259E-4</v>
       </c>
       <c r="I152" s="1">
-        <v>46237.838310185187</v>
+        <v>46237.839699074073</v>
       </c>
       <c r="J152" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K152" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="153" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B153" t="s">
-        <v>19</v>
-      </c>
-      <c r="C153">
-        <v>5684</v>
-      </c>
-      <c r="D153" t="s">
-        <v>68</v>
-      </c>
-      <c r="F153" t="s">
-        <v>16</v>
-      </c>
-      <c r="G153" t="s">
-        <v>13</v>
-      </c>
-      <c r="H153" s="2">
-        <v>0</v>
-      </c>
-      <c r="I153" s="1">
-        <v>46237.838310185187</v>
-      </c>
-      <c r="J153" s="2">
-        <v>0</v>
-      </c>
+      <c r="H153" s="2"/>
+      <c r="I153" s="1"/>
+      <c r="J153" s="2"/>
       <c r="K153" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="154" spans="2:11" x14ac:dyDescent="0.25">
@@ -4842,10 +4905,10 @@
         <v>19</v>
       </c>
       <c r="C154">
-        <v>5740</v>
+        <v>5690</v>
       </c>
       <c r="D154" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F154" t="s">
         <v>16</v>
@@ -4857,10 +4920,10 @@
         <v>0</v>
       </c>
       <c r="I154" s="1">
-        <v>46237.839004629626</v>
+        <v>46237.84039351852</v>
       </c>
       <c r="J154" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K154" s="1" t="s">
         <v>11</v>
@@ -4871,10 +4934,10 @@
         <v>19</v>
       </c>
       <c r="C155">
-        <v>5701</v>
+        <v>5697</v>
       </c>
       <c r="D155" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F155" t="s">
         <v>16</v>
@@ -4886,10 +4949,10 @@
         <v>0</v>
       </c>
       <c r="I155" s="1">
-        <v>46237.839699074073</v>
+        <v>46237.841087962966</v>
       </c>
       <c r="J155" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K155" s="1" t="s">
         <v>11</v>
@@ -4900,22 +4963,22 @@
         <v>19</v>
       </c>
       <c r="C156">
-        <v>5695</v>
+        <v>5744</v>
       </c>
       <c r="D156" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F156" t="s">
         <v>16</v>
       </c>
       <c r="G156" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H156" s="2">
-        <v>6.134259259259259E-4</v>
+        <v>7.2685185185185188E-3</v>
       </c>
       <c r="I156" s="1">
-        <v>46237.839699074073</v>
+        <v>46237.841782407406</v>
       </c>
       <c r="J156" s="2">
         <v>0</v>
@@ -4925,11 +4988,32 @@
       </c>
     </row>
     <row r="157" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H157" s="2"/>
-      <c r="I157" s="1"/>
-      <c r="J157" s="2"/>
+      <c r="B157" t="s">
+        <v>19</v>
+      </c>
+      <c r="C157">
+        <v>5738</v>
+      </c>
+      <c r="D157" t="s">
+        <v>75</v>
+      </c>
+      <c r="F157" t="s">
+        <v>16</v>
+      </c>
+      <c r="G157" t="s">
+        <v>13</v>
+      </c>
+      <c r="H157" s="2">
+        <v>0</v>
+      </c>
+      <c r="I157" s="1">
+        <v>46237.841782407406</v>
+      </c>
+      <c r="J157" s="2">
+        <v>3</v>
+      </c>
       <c r="K157" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="158" spans="2:11" x14ac:dyDescent="0.25">
@@ -4937,10 +5021,10 @@
         <v>19</v>
       </c>
       <c r="C158">
-        <v>5690</v>
+        <v>5691</v>
       </c>
       <c r="D158" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F158" t="s">
         <v>16</v>
@@ -4952,10 +5036,10 @@
         <v>0</v>
       </c>
       <c r="I158" s="1">
-        <v>46237.84039351852</v>
+        <v>46237.842476851853</v>
       </c>
       <c r="J158" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K158" s="1" t="s">
         <v>11</v>
@@ -4966,10 +5050,10 @@
         <v>19</v>
       </c>
       <c r="C159">
-        <v>5697</v>
+        <v>5699</v>
       </c>
       <c r="D159" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F159" t="s">
         <v>16</v>
@@ -4981,10 +5065,10 @@
         <v>0</v>
       </c>
       <c r="I159" s="1">
-        <v>46237.841087962966</v>
+        <v>46237.843171296299</v>
       </c>
       <c r="J159" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K159" s="1" t="s">
         <v>11</v>
@@ -4995,25 +5079,25 @@
         <v>19</v>
       </c>
       <c r="C160">
-        <v>5744</v>
+        <v>5694</v>
       </c>
       <c r="D160" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F160" t="s">
         <v>16</v>
       </c>
       <c r="G160" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H160" s="2">
-        <v>7.2685185185185188E-3</v>
+        <v>0</v>
       </c>
       <c r="I160" s="1">
-        <v>46237.841782407406</v>
+        <v>46237.843171296299</v>
       </c>
       <c r="J160" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K160" s="1" t="s">
         <v>11</v>
@@ -5024,10 +5108,10 @@
         <v>19</v>
       </c>
       <c r="C161">
-        <v>5738</v>
+        <v>5730</v>
       </c>
       <c r="D161" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F161" t="s">
         <v>16</v>
@@ -5039,10 +5123,10 @@
         <v>0</v>
       </c>
       <c r="I161" s="1">
-        <v>46237.841782407406</v>
+        <v>46237.843865740739</v>
       </c>
       <c r="J161" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K161" s="1" t="s">
         <v>11</v>
@@ -5053,10 +5137,10 @@
         <v>19</v>
       </c>
       <c r="C162">
-        <v>5691</v>
+        <v>5681</v>
       </c>
       <c r="D162" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F162" t="s">
         <v>16</v>
@@ -5068,10 +5152,10 @@
         <v>0</v>
       </c>
       <c r="I162" s="1">
-        <v>46237.842476851853</v>
+        <v>46237.844560185185</v>
       </c>
       <c r="J162" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K162" s="1" t="s">
         <v>11</v>
@@ -5082,10 +5166,10 @@
         <v>19</v>
       </c>
       <c r="C163">
-        <v>5699</v>
+        <v>5735</v>
       </c>
       <c r="D163" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F163" t="s">
         <v>16</v>
@@ -5097,10 +5181,10 @@
         <v>0</v>
       </c>
       <c r="I163" s="1">
-        <v>46237.843171296299</v>
+        <v>46237.844560185185</v>
       </c>
       <c r="J163" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K163" s="1" t="s">
         <v>11</v>
@@ -5111,10 +5195,10 @@
         <v>19</v>
       </c>
       <c r="C164">
-        <v>5694</v>
+        <v>5692</v>
       </c>
       <c r="D164" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F164" t="s">
         <v>16</v>
@@ -5126,10 +5210,10 @@
         <v>0</v>
       </c>
       <c r="I164" s="1">
-        <v>46237.843171296299</v>
+        <v>46237.845254629632</v>
       </c>
       <c r="J164" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K164" s="1" t="s">
         <v>11</v>
@@ -5140,25 +5224,25 @@
         <v>19</v>
       </c>
       <c r="C165">
-        <v>5730</v>
+        <v>5703</v>
       </c>
       <c r="D165" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F165" t="s">
         <v>16</v>
       </c>
       <c r="G165" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H165" s="2">
-        <v>0</v>
+        <v>8.6458333333333335E-3</v>
       </c>
       <c r="I165" s="1">
-        <v>46237.843865740739</v>
+        <v>46237.845254629632</v>
       </c>
       <c r="J165" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K165" s="1" t="s">
         <v>11</v>
@@ -5169,22 +5253,22 @@
         <v>19</v>
       </c>
       <c r="C166">
-        <v>5681</v>
+        <v>5708</v>
       </c>
       <c r="D166" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F166" t="s">
         <v>16</v>
       </c>
       <c r="G166" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H166" s="2">
-        <v>0</v>
+        <v>1.3460648148148149E-2</v>
       </c>
       <c r="I166" s="1">
-        <v>46237.844560185185</v>
+        <v>46237.845949074072</v>
       </c>
       <c r="J166" s="2">
         <v>0</v>
@@ -5198,25 +5282,25 @@
         <v>19</v>
       </c>
       <c r="C167">
-        <v>5735</v>
+        <v>5712</v>
       </c>
       <c r="D167" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F167" t="s">
         <v>16</v>
       </c>
       <c r="G167" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H167" s="2">
-        <v>0</v>
+        <v>7.1412037037037034E-3</v>
       </c>
       <c r="I167" s="1">
-        <v>46237.844560185185</v>
+        <v>46237.846643518518</v>
       </c>
       <c r="J167" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K167" s="1" t="s">
         <v>11</v>
@@ -5227,22 +5311,22 @@
         <v>19</v>
       </c>
       <c r="C168">
-        <v>5692</v>
+        <v>6002</v>
       </c>
       <c r="D168" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="F168" t="s">
         <v>16</v>
       </c>
       <c r="G168" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H168" s="2">
-        <v>0</v>
+        <v>5.8564814814814816E-3</v>
       </c>
       <c r="I168" s="1">
-        <v>46237.845254629632</v>
+        <v>46237.846643518518</v>
       </c>
       <c r="J168" s="2">
         <v>0</v>
@@ -5256,10 +5340,10 @@
         <v>19</v>
       </c>
       <c r="C169">
-        <v>5703</v>
+        <v>5734</v>
       </c>
       <c r="D169" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F169" t="s">
         <v>16</v>
@@ -5271,10 +5355,10 @@
         <v>0</v>
       </c>
       <c r="I169" s="1">
-        <v>46237.845254629632</v>
+        <v>46237.847337962965</v>
       </c>
       <c r="J169" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K169" s="1" t="s">
         <v>11</v>
@@ -5285,25 +5369,25 @@
         <v>19</v>
       </c>
       <c r="C170">
-        <v>5708</v>
+        <v>5743</v>
       </c>
       <c r="D170" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F170" t="s">
         <v>16</v>
       </c>
       <c r="G170" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H170" s="2">
-        <v>1.3460648148148149E-2</v>
+        <v>0</v>
       </c>
       <c r="I170" s="1">
-        <v>46237.845949074072</v>
+        <v>46237.848032407404</v>
       </c>
       <c r="J170" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K170" s="1" t="s">
         <v>11</v>
@@ -5314,10 +5398,10 @@
         <v>19</v>
       </c>
       <c r="C171">
-        <v>5712</v>
+        <v>5742</v>
       </c>
       <c r="D171" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F171" t="s">
         <v>16</v>
@@ -5329,10 +5413,10 @@
         <v>0</v>
       </c>
       <c r="I171" s="1">
-        <v>46237.846643518518</v>
+        <v>46237.848726851851</v>
       </c>
       <c r="J171" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K171" s="1" t="s">
         <v>11</v>
@@ -5343,10 +5427,10 @@
         <v>19</v>
       </c>
       <c r="C172">
-        <v>6002</v>
+        <v>5723</v>
       </c>
       <c r="D172" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="F172" t="s">
         <v>16</v>
@@ -5355,13 +5439,13 @@
         <v>10</v>
       </c>
       <c r="H172" s="2">
-        <v>5.8564814814814816E-3</v>
+        <v>1.5219907407407408E-2</v>
       </c>
       <c r="I172" s="1">
-        <v>46237.846643518518</v>
+        <v>46237.848726851851</v>
       </c>
       <c r="J172" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K172" s="1" t="s">
         <v>11</v>
@@ -5372,10 +5456,10 @@
         <v>19</v>
       </c>
       <c r="C173">
-        <v>5734</v>
+        <v>5706</v>
       </c>
       <c r="D173" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="F173" t="s">
         <v>16</v>
@@ -5387,39 +5471,39 @@
         <v>0</v>
       </c>
       <c r="I173" s="1">
-        <v>46237.847337962965</v>
+        <v>46237.849421296298</v>
       </c>
       <c r="J173" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K173" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="174" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B174" t="s">
         <v>19</v>
       </c>
       <c r="C174">
-        <v>5743</v>
+        <v>5670</v>
       </c>
       <c r="D174" t="s">
-        <v>87</v>
+        <v>21</v>
       </c>
       <c r="F174" t="s">
         <v>16</v>
       </c>
       <c r="G174" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H174" s="2">
-        <v>0</v>
+        <v>6.7129629629629631E-3</v>
       </c>
       <c r="I174" s="1">
-        <v>46237.848032407404</v>
+        <v>46237.850115740737</v>
       </c>
       <c r="J174" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K174" s="1" t="s">
         <v>11</v>
@@ -5430,22 +5514,22 @@
         <v>19</v>
       </c>
       <c r="C175">
-        <v>5742</v>
+        <v>5677</v>
       </c>
       <c r="D175" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F175" t="s">
         <v>16</v>
       </c>
       <c r="G175" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H175" s="2">
-        <v>0</v>
+        <v>6.8055555555555551E-3</v>
       </c>
       <c r="I175" s="1">
-        <v>46237.848726851851</v>
+        <v>46237.850115740737</v>
       </c>
       <c r="J175" s="2">
         <v>0</v>
@@ -5459,25 +5543,25 @@
         <v>19</v>
       </c>
       <c r="C176">
-        <v>5723</v>
+        <v>5685</v>
       </c>
       <c r="D176" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F176" t="s">
         <v>16</v>
       </c>
       <c r="G176" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H176" s="2">
-        <v>0</v>
+        <v>6.2962962962962964E-3</v>
       </c>
       <c r="I176" s="1">
-        <v>46237.848726851851</v>
+        <v>46237.850810185184</v>
       </c>
       <c r="J176" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K176" s="1" t="s">
         <v>11</v>
@@ -5488,25 +5572,25 @@
         <v>19</v>
       </c>
       <c r="C177">
-        <v>5706</v>
+        <v>5719</v>
       </c>
       <c r="D177" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F177" t="s">
         <v>16</v>
       </c>
       <c r="G177" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H177" s="2">
-        <v>0</v>
+        <v>6.4814814814814813E-3</v>
       </c>
       <c r="I177" s="1">
-        <v>46237.849421296298</v>
+        <v>46237.850810185184</v>
       </c>
       <c r="J177" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K177" s="1" t="s">
         <v>11</v>
@@ -5517,65 +5601,65 @@
         <v>19</v>
       </c>
       <c r="C178">
-        <v>5670</v>
+        <v>5728</v>
       </c>
       <c r="D178" t="s">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="F178" t="s">
         <v>16</v>
       </c>
       <c r="G178" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H178" s="2">
         <v>0</v>
       </c>
       <c r="I178" s="1">
-        <v>46237.850115740737</v>
+        <v>46254.585995370369</v>
       </c>
       <c r="J178" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K178" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="179" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H179" s="2"/>
-      <c r="I179" s="1"/>
-      <c r="J179" s="2"/>
+    <row r="179" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B179" t="s">
+        <v>19</v>
+      </c>
+      <c r="C179">
+        <v>5733</v>
+      </c>
+      <c r="D179" t="s">
+        <v>62</v>
+      </c>
+      <c r="F179" t="s">
+        <v>16</v>
+      </c>
+      <c r="G179" t="s">
+        <v>12</v>
+      </c>
+      <c r="H179" s="2">
+        <v>3.2407407407407406E-4</v>
+      </c>
+      <c r="I179" s="1">
+        <v>46254.585995370369</v>
+      </c>
+      <c r="J179" s="2">
+        <v>1</v>
+      </c>
       <c r="K179" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="180" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H180" s="2"/>
+      <c r="I180" s="1"/>
+      <c r="J180" s="2"/>
+      <c r="K180" s="1" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="180" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B180" t="s">
-        <v>19</v>
-      </c>
-      <c r="C180">
-        <v>5677</v>
-      </c>
-      <c r="D180" t="s">
-        <v>91</v>
-      </c>
-      <c r="F180" t="s">
-        <v>16</v>
-      </c>
-      <c r="G180" t="s">
-        <v>10</v>
-      </c>
-      <c r="H180" s="2">
-        <v>6.8055555555555551E-3</v>
-      </c>
-      <c r="I180" s="1">
-        <v>46237.850115740737</v>
-      </c>
-      <c r="J180" s="2">
-        <v>0</v>
-      </c>
-      <c r="K180" s="1" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="181" spans="2:11" x14ac:dyDescent="0.25">
@@ -5583,10 +5667,10 @@
         <v>19</v>
       </c>
       <c r="C181">
-        <v>5685</v>
+        <v>5726</v>
       </c>
       <c r="D181" t="s">
-        <v>92</v>
+        <v>67</v>
       </c>
       <c r="F181" t="s">
         <v>16</v>
@@ -5598,10 +5682,10 @@
         <v>0</v>
       </c>
       <c r="I181" s="1">
-        <v>46237.850810185184</v>
+        <v>46255.585532407407</v>
       </c>
       <c r="J181" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K181" s="1" t="s">
         <v>11</v>
@@ -5612,25 +5696,25 @@
         <v>19</v>
       </c>
       <c r="C182">
-        <v>5719</v>
+        <v>5723</v>
       </c>
       <c r="D182" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F182" t="s">
         <v>16</v>
       </c>
       <c r="G182" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H182" s="2">
-        <v>1.1226851851851851E-3</v>
+        <v>5.527777777777778E-2</v>
       </c>
       <c r="I182" s="1">
-        <v>46237.850810185184</v>
+        <v>46255.586226851854</v>
       </c>
       <c r="J182" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K182" s="1" t="s">
         <v>11</v>
@@ -5640,9 +5724,7 @@
       <c r="H183" s="2"/>
       <c r="I183" s="1"/>
       <c r="J183" s="2"/>
-      <c r="K183" s="1" t="s">
-        <v>15</v>
-      </c>
+      <c r="K183" s="1"/>
     </row>
     <row r="184" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H184" s="2"/>
@@ -5674,7 +5756,7 @@
       <c r="J188" s="2"/>
       <c r="K188" s="1"/>
     </row>
-    <row r="189" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="189" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H189" s="2"/>
       <c r="I189" s="1"/>
       <c r="J189" s="2"/>
@@ -5782,7 +5864,7 @@
       <c r="J206" s="2"/>
       <c r="K206" s="1"/>
     </row>
-    <row r="207" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="207" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H207" s="2"/>
       <c r="I207" s="1"/>
       <c r="J207" s="2"/>
@@ -5974,7 +6056,7 @@
       <c r="J238" s="2"/>
       <c r="K238" s="1"/>
     </row>
-    <row r="239" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="239" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H239" s="2"/>
       <c r="I239" s="1"/>
       <c r="J239" s="2"/>
@@ -6490,7 +6572,7 @@
       <c r="J324" s="2"/>
       <c r="K324" s="1"/>
     </row>
-    <row r="325" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="325" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H325" s="2"/>
       <c r="I325" s="1"/>
       <c r="J325" s="2"/>
@@ -6556,7 +6638,7 @@
       <c r="J335" s="2"/>
       <c r="K335" s="1"/>
     </row>
-    <row r="336" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="336" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H336" s="2"/>
       <c r="I336" s="1"/>
       <c r="J336" s="2"/>
@@ -6568,7 +6650,7 @@
       <c r="J337" s="2"/>
       <c r="K337" s="1"/>
     </row>
-    <row r="338" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="338" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H338" s="2"/>
       <c r="I338" s="1"/>
       <c r="J338" s="2"/>
@@ -6664,7 +6746,7 @@
       <c r="J353" s="2"/>
       <c r="K353" s="1"/>
     </row>
-    <row r="354" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="354" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H354" s="2"/>
       <c r="I354" s="1"/>
       <c r="J354" s="2"/>
@@ -6676,7 +6758,7 @@
       <c r="J355" s="2"/>
       <c r="K355" s="1"/>
     </row>
-    <row r="356" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="356" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H356" s="2"/>
       <c r="I356" s="1"/>
       <c r="J356" s="2"/>
@@ -6772,7 +6854,7 @@
       <c r="J371" s="2"/>
       <c r="K371" s="1"/>
     </row>
-    <row r="372" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="372" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H372" s="2"/>
       <c r="I372" s="1"/>
       <c r="J372" s="2"/>
@@ -6832,7 +6914,7 @@
       <c r="J381" s="2"/>
       <c r="K381" s="1"/>
     </row>
-    <row r="382" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="382" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H382" s="2"/>
       <c r="I382" s="1"/>
       <c r="J382" s="2"/>
@@ -16246,6 +16328,7 @@
       <c r="K1957" s="1"/>
     </row>
     <row r="1958" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1958" s="2"/>
       <c r="I1958" s="1"/>
       <c r="K1958" s="1"/>
     </row>
@@ -16283,6 +16366,7 @@
       <c r="K1964" s="1"/>
     </row>
     <row r="1965" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1965" s="2"/>
       <c r="I1965" s="1"/>
       <c r="K1965" s="1"/>
     </row>
@@ -16347,6 +16431,7 @@
       <c r="K1976" s="1"/>
     </row>
     <row r="1977" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1977" s="2"/>
       <c r="I1977" s="1"/>
     </row>
     <row r="1978" spans="8:11" x14ac:dyDescent="0.25">
@@ -16378,11 +16463,11 @@
       <c r="K1982" s="1"/>
     </row>
     <row r="1983" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H1983" s="2"/>
       <c r="I1983" s="1"/>
       <c r="K1983" s="1"/>
     </row>
     <row r="1984" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1984" s="2"/>
       <c r="I1984" s="1"/>
       <c r="K1984" s="1"/>
     </row>
@@ -16393,6 +16478,7 @@
       <c r="K1985" s="1"/>
     </row>
     <row r="1986" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H1986" s="2"/>
       <c r="I1986" s="1"/>
       <c r="K1986" s="1"/>
     </row>
@@ -16468,6 +16554,7 @@
       <c r="K1999" s="1"/>
     </row>
     <row r="2000" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H2000" s="2"/>
       <c r="I2000" s="1"/>
       <c r="K2000" s="1"/>
     </row>
@@ -16478,6 +16565,7 @@
       <c r="K2001" s="1"/>
     </row>
     <row r="2002" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H2002" s="2"/>
       <c r="I2002" s="1"/>
     </row>
     <row r="2003" spans="8:11" x14ac:dyDescent="0.25">
@@ -16509,7 +16597,6 @@
       <c r="K2007" s="1"/>
     </row>
     <row r="2008" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H2008" s="2"/>
       <c r="I2008" s="1"/>
       <c r="K2008" s="1"/>
     </row>
@@ -45802,6 +45889,7 @@
       <c r="K7005" s="1"/>
     </row>
     <row r="7006" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7006" s="2"/>
       <c r="I7006" s="1"/>
       <c r="K7006" s="1"/>
     </row>
@@ -46094,6 +46182,8 @@
       <c r="K7054" s="1"/>
     </row>
     <row r="7055" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7055" s="2"/>
+      <c r="I7055" s="1"/>
       <c r="J7055" s="2"/>
       <c r="K7055" s="1"/>
     </row>
@@ -46404,6 +46494,7 @@
       <c r="K7106" s="1"/>
     </row>
     <row r="7107" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7107" s="2"/>
       <c r="I7107" s="1"/>
       <c r="K7107" s="1"/>
     </row>
@@ -46528,6 +46619,7 @@
       <c r="K7127" s="1"/>
     </row>
     <row r="7128" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7128" s="2"/>
       <c r="I7128" s="1"/>
       <c r="J7128" s="2"/>
       <c r="K7128" s="1"/>
@@ -46539,6 +46631,7 @@
       <c r="K7129" s="1"/>
     </row>
     <row r="7130" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7130" s="2"/>
       <c r="I7130" s="1"/>
       <c r="K7130" s="1"/>
     </row>
@@ -46687,6 +46780,7 @@
       <c r="K7154" s="1"/>
     </row>
     <row r="7155" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7155" s="2"/>
       <c r="I7155" s="1"/>
       <c r="K7155" s="1"/>
     </row>
@@ -46697,10 +46791,12 @@
       <c r="K7156" s="1"/>
     </row>
     <row r="7157" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7157" s="2"/>
       <c r="I7157" s="1"/>
       <c r="K7157" s="1"/>
     </row>
     <row r="7158" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7158" s="2"/>
       <c r="I7158" s="1"/>
       <c r="J7158" s="2"/>
       <c r="K7158" s="1"/>
@@ -46734,15 +46830,18 @@
       <c r="K7163" s="1"/>
     </row>
     <row r="7164" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7164" s="2"/>
       <c r="I7164" s="1"/>
       <c r="K7164" s="1"/>
     </row>
     <row r="7165" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7165" s="2"/>
       <c r="I7165" s="1"/>
       <c r="J7165" s="2"/>
       <c r="K7165" s="1"/>
     </row>
     <row r="7166" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7166" s="2"/>
       <c r="I7166" s="1"/>
       <c r="K7166" s="1"/>
     </row>
@@ -46783,18 +46882,22 @@
       <c r="K7173" s="1"/>
     </row>
     <row r="7174" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7174" s="2"/>
       <c r="I7174" s="1"/>
       <c r="K7174" s="1"/>
     </row>
     <row r="7175" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7175" s="2"/>
       <c r="I7175" s="1"/>
       <c r="K7175" s="1"/>
     </row>
     <row r="7176" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7176" s="2"/>
       <c r="I7176" s="1"/>
       <c r="K7176" s="1"/>
     </row>
     <row r="7177" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7177" s="2"/>
       <c r="I7177" s="1"/>
       <c r="K7177" s="1"/>
     </row>
@@ -46810,6 +46913,7 @@
       <c r="K7179" s="1"/>
     </row>
     <row r="7180" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7180" s="2"/>
       <c r="I7180" s="1"/>
       <c r="K7180" s="1"/>
     </row>
@@ -46819,10 +46923,12 @@
       <c r="K7181" s="1"/>
     </row>
     <row r="7182" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7182" s="2"/>
       <c r="I7182" s="1"/>
       <c r="K7182" s="1"/>
     </row>
     <row r="7183" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7183" s="2"/>
       <c r="I7183" s="1"/>
       <c r="K7183" s="1"/>
     </row>
@@ -46858,10 +46964,12 @@
       <c r="K7189" s="1"/>
     </row>
     <row r="7190" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7190" s="2"/>
       <c r="I7190" s="1"/>
       <c r="K7190" s="1"/>
     </row>
     <row r="7191" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7191" s="2"/>
       <c r="I7191" s="1"/>
       <c r="K7191" s="1"/>
     </row>
@@ -46887,6 +46995,7 @@
       <c r="K7195" s="1"/>
     </row>
     <row r="7196" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7196" s="2"/>
       <c r="I7196" s="1"/>
       <c r="K7196" s="1"/>
     </row>
@@ -46901,6 +47010,7 @@
       <c r="K7198" s="1"/>
     </row>
     <row r="7199" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7199" s="2"/>
       <c r="I7199" s="1"/>
       <c r="K7199" s="1"/>
     </row>
@@ -46935,6 +47045,7 @@
       <c r="K7205" s="1"/>
     </row>
     <row r="7206" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7206" s="2"/>
       <c r="I7206" s="1"/>
       <c r="K7206" s="1"/>
     </row>
@@ -46944,6 +47055,7 @@
       <c r="K7207" s="1"/>
     </row>
     <row r="7208" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7208" s="2"/>
       <c r="I7208" s="1"/>
       <c r="K7208" s="1"/>
     </row>
@@ -46953,6 +47065,7 @@
       <c r="K7209" s="1"/>
     </row>
     <row r="7210" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7210" s="2"/>
       <c r="I7210" s="1"/>
       <c r="K7210" s="1"/>
     </row>
@@ -46967,15 +47080,16 @@
       <c r="K7212" s="1"/>
     </row>
     <row r="7213" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7213" s="2"/>
       <c r="I7213" s="1"/>
       <c r="K7213" s="1"/>
     </row>
     <row r="7214" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7214" s="2"/>
       <c r="I7214" s="1"/>
       <c r="K7214" s="1"/>
     </row>
     <row r="7215" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7215" s="2"/>
       <c r="I7215" s="1"/>
       <c r="K7215" s="1"/>
     </row>
@@ -47005,6 +47119,7 @@
       <c r="K7220" s="1"/>
     </row>
     <row r="7221" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7221" s="2"/>
       <c r="I7221" s="1"/>
       <c r="K7221" s="1"/>
     </row>
@@ -47025,11 +47140,13 @@
       <c r="K7224" s="1"/>
     </row>
     <row r="7225" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7225" s="2"/>
       <c r="I7225" s="1"/>
       <c r="J7225" s="2"/>
       <c r="K7225" s="1"/>
     </row>
     <row r="7226" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7226" s="2"/>
       <c r="I7226" s="1"/>
     </row>
     <row r="7227" spans="8:11" x14ac:dyDescent="0.25">
@@ -47038,6 +47155,7 @@
       <c r="K7227" s="1"/>
     </row>
     <row r="7228" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7228" s="2"/>
       <c r="I7228" s="1"/>
       <c r="K7228" s="1"/>
     </row>
@@ -47067,6 +47185,7 @@
       <c r="K7233" s="1"/>
     </row>
     <row r="7234" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7234" s="2"/>
       <c r="I7234" s="1"/>
       <c r="K7234" s="1"/>
     </row>
@@ -47076,10 +47195,12 @@
       <c r="K7235" s="1"/>
     </row>
     <row r="7236" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7236" s="2"/>
       <c r="I7236" s="1"/>
       <c r="K7236" s="1"/>
     </row>
     <row r="7237" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7237" s="2"/>
       <c r="I7237" s="1"/>
       <c r="K7237" s="1"/>
     </row>
@@ -47094,14 +47215,17 @@
       <c r="K7239" s="1"/>
     </row>
     <row r="7240" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7240" s="2"/>
       <c r="I7240" s="1"/>
       <c r="K7240" s="1"/>
     </row>
     <row r="7241" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7241" s="2"/>
       <c r="I7241" s="1"/>
       <c r="K7241" s="1"/>
     </row>
     <row r="7242" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7242" s="2"/>
       <c r="I7242" s="1"/>
       <c r="K7242" s="1"/>
     </row>
@@ -47121,10 +47245,12 @@
       <c r="K7245" s="1"/>
     </row>
     <row r="7246" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7246" s="2"/>
       <c r="I7246" s="1"/>
       <c r="K7246" s="1"/>
     </row>
     <row r="7247" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7247" s="2"/>
       <c r="I7247" s="1"/>
       <c r="K7247" s="1"/>
     </row>
@@ -47144,9 +47270,12 @@
       <c r="K7250" s="1"/>
     </row>
     <row r="7251" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7251" s="2"/>
+      <c r="I7251" s="1"/>
       <c r="K7251" s="1"/>
     </row>
     <row r="7252" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7252" s="2"/>
       <c r="I7252" s="1"/>
       <c r="K7252" s="1"/>
     </row>
@@ -47181,18 +47310,22 @@
       <c r="K7258" s="1"/>
     </row>
     <row r="7259" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7259" s="2"/>
       <c r="I7259" s="1"/>
       <c r="K7259" s="1"/>
     </row>
     <row r="7260" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7260" s="2"/>
       <c r="I7260" s="1"/>
       <c r="K7260" s="1"/>
     </row>
     <row r="7261" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7261" s="2"/>
       <c r="I7261" s="1"/>
       <c r="K7261" s="1"/>
     </row>
     <row r="7262" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7262" s="2"/>
       <c r="I7262" s="1"/>
       <c r="K7262" s="1"/>
     </row>
@@ -47207,12 +47340,12 @@
       <c r="I7264" s="1"/>
     </row>
     <row r="7265" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7265" s="2"/>
       <c r="I7265" s="1"/>
       <c r="J7265" s="2"/>
       <c r="K7265" s="1"/>
     </row>
     <row r="7266" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7266" s="2"/>
       <c r="I7266" s="1"/>
       <c r="K7266" s="1"/>
     </row>
@@ -47227,10 +47360,12 @@
       <c r="K7268" s="1"/>
     </row>
     <row r="7269" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7269" s="2"/>
       <c r="I7269" s="1"/>
       <c r="K7269" s="1"/>
     </row>
     <row r="7270" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7270" s="2"/>
       <c r="I7270" s="1"/>
       <c r="K7270" s="1"/>
     </row>
@@ -47250,6 +47385,7 @@
       <c r="K7273" s="1"/>
     </row>
     <row r="7274" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7274" s="2"/>
       <c r="I7274" s="1"/>
       <c r="K7274" s="1"/>
     </row>
@@ -47269,6 +47405,7 @@
       <c r="K7277" s="1"/>
     </row>
     <row r="7278" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7278" s="2"/>
       <c r="I7278" s="1"/>
       <c r="K7278" s="1"/>
     </row>
@@ -47278,6 +47415,7 @@
       <c r="K7279" s="1"/>
     </row>
     <row r="7280" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7280" s="2"/>
       <c r="I7280" s="1"/>
       <c r="J7280" s="2"/>
       <c r="K7280" s="1"/>
@@ -47323,6 +47461,7 @@
       <c r="K7288" s="1"/>
     </row>
     <row r="7289" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7289" s="2"/>
       <c r="I7289" s="1"/>
       <c r="K7289" s="1"/>
     </row>
@@ -47332,6 +47471,7 @@
       <c r="K7290" s="1"/>
     </row>
     <row r="7291" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7291" s="2"/>
       <c r="I7291" s="1"/>
       <c r="K7291" s="1"/>
     </row>
@@ -47346,6 +47486,7 @@
       <c r="K7293" s="1"/>
     </row>
     <row r="7294" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7294" s="2"/>
       <c r="I7294" s="1"/>
       <c r="K7294" s="1"/>
     </row>
@@ -47355,10 +47496,12 @@
       <c r="K7295" s="1"/>
     </row>
     <row r="7296" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7296" s="2"/>
       <c r="I7296" s="1"/>
       <c r="K7296" s="1"/>
     </row>
     <row r="7297" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7297" s="2"/>
       <c r="I7297" s="1"/>
       <c r="K7297" s="1"/>
     </row>
@@ -47373,6 +47516,7 @@
       <c r="K7299" s="1"/>
     </row>
     <row r="7300" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7300" s="2"/>
       <c r="I7300" s="1"/>
       <c r="K7300" s="1"/>
     </row>
@@ -47382,6 +47526,7 @@
       <c r="K7301" s="1"/>
     </row>
     <row r="7302" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7302" s="2"/>
       <c r="I7302" s="1"/>
       <c r="K7302" s="1"/>
     </row>
@@ -47401,6 +47546,7 @@
       <c r="K7305" s="1"/>
     </row>
     <row r="7306" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7306" s="2"/>
       <c r="I7306" s="1"/>
       <c r="K7306" s="1"/>
     </row>
@@ -47420,10 +47566,12 @@
       <c r="K7309" s="1"/>
     </row>
     <row r="7310" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7310" s="2"/>
       <c r="I7310" s="1"/>
       <c r="K7310" s="1"/>
     </row>
     <row r="7311" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7311" s="2"/>
       <c r="I7311" s="1"/>
       <c r="K7311" s="1"/>
     </row>
@@ -47433,6 +47581,7 @@
       <c r="K7312" s="1"/>
     </row>
     <row r="7313" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7313" s="2"/>
       <c r="I7313" s="1"/>
       <c r="J7313" s="2"/>
       <c r="K7313" s="1"/>
@@ -47443,10 +47592,12 @@
       <c r="K7314" s="1"/>
     </row>
     <row r="7315" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7315" s="2"/>
       <c r="I7315" s="1"/>
       <c r="K7315" s="1"/>
     </row>
     <row r="7316" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7316" s="2"/>
       <c r="I7316" s="1"/>
       <c r="K7316" s="1"/>
     </row>
@@ -47461,18 +47612,22 @@
       <c r="K7318" s="1"/>
     </row>
     <row r="7319" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7319" s="2"/>
       <c r="I7319" s="1"/>
       <c r="K7319" s="1"/>
     </row>
     <row r="7320" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7320" s="2"/>
       <c r="I7320" s="1"/>
       <c r="K7320" s="1"/>
     </row>
     <row r="7321" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7321" s="2"/>
       <c r="I7321" s="1"/>
       <c r="K7321" s="1"/>
     </row>
     <row r="7322" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7322" s="2"/>
       <c r="I7322" s="1"/>
       <c r="K7322" s="1"/>
     </row>
@@ -47492,10 +47647,12 @@
       <c r="K7325" s="1"/>
     </row>
     <row r="7326" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7326" s="2"/>
       <c r="I7326" s="1"/>
       <c r="K7326" s="1"/>
     </row>
     <row r="7327" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7327" s="2"/>
       <c r="I7327" s="1"/>
       <c r="K7327" s="1"/>
     </row>
@@ -47515,6 +47672,7 @@
       <c r="K7330" s="1"/>
     </row>
     <row r="7331" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7331" s="2"/>
       <c r="I7331" s="1"/>
       <c r="K7331" s="1"/>
     </row>
@@ -47545,7 +47703,6 @@
       <c r="K7336" s="1"/>
     </row>
     <row r="7337" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7337" s="2"/>
       <c r="I7337" s="1"/>
       <c r="K7337" s="1"/>
     </row>
@@ -47560,10 +47717,12 @@
       <c r="K7339" s="1"/>
     </row>
     <row r="7340" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7340" s="2"/>
       <c r="I7340" s="1"/>
       <c r="K7340" s="1"/>
     </row>
     <row r="7341" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7341" s="2"/>
       <c r="I7341" s="1"/>
       <c r="K7341" s="1"/>
     </row>
@@ -47578,6 +47737,7 @@
       <c r="K7343" s="1"/>
     </row>
     <row r="7344" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7344" s="2"/>
       <c r="I7344" s="1"/>
       <c r="K7344" s="1"/>
     </row>
@@ -47592,11 +47752,11 @@
       <c r="K7346" s="1"/>
     </row>
     <row r="7347" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7347" s="2"/>
       <c r="I7347" s="1"/>
       <c r="K7347" s="1"/>
     </row>
     <row r="7348" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7348" s="2"/>
       <c r="I7348" s="1"/>
       <c r="K7348" s="1"/>
     </row>
@@ -47606,6 +47766,7 @@
       <c r="K7349" s="1"/>
     </row>
     <row r="7350" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7350" s="2"/>
       <c r="I7350" s="1"/>
       <c r="J7350" s="2"/>
       <c r="K7350" s="1"/>
@@ -47621,6 +47782,7 @@
       <c r="K7352" s="1"/>
     </row>
     <row r="7353" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7353" s="2"/>
       <c r="I7353" s="1"/>
       <c r="K7353" s="1"/>
     </row>
@@ -47635,6 +47797,7 @@
       <c r="K7355" s="1"/>
     </row>
     <row r="7356" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7356" s="2"/>
       <c r="I7356" s="1"/>
       <c r="K7356" s="1"/>
     </row>
@@ -47655,6 +47818,7 @@
       <c r="K7359" s="1"/>
     </row>
     <row r="7360" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7360" s="2"/>
       <c r="I7360" s="1"/>
       <c r="J7360" s="2"/>
       <c r="K7360" s="1"/>
@@ -47680,11 +47844,13 @@
       <c r="K7364" s="1"/>
     </row>
     <row r="7365" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7365" s="2"/>
       <c r="I7365" s="1"/>
       <c r="J7365" s="2"/>
       <c r="K7365" s="1"/>
     </row>
     <row r="7366" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7366" s="2"/>
       <c r="I7366" s="1"/>
     </row>
     <row r="7367" spans="8:11" x14ac:dyDescent="0.25">
@@ -47703,15 +47869,16 @@
       <c r="K7369" s="1"/>
     </row>
     <row r="7370" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7370" s="2"/>
       <c r="I7370" s="1"/>
       <c r="K7370" s="1"/>
     </row>
     <row r="7371" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7371" s="2"/>
       <c r="I7371" s="1"/>
       <c r="K7371" s="1"/>
     </row>
     <row r="7372" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7372" s="2"/>
       <c r="I7372" s="1"/>
       <c r="K7372" s="1"/>
     </row>
@@ -47721,6 +47888,7 @@
       <c r="K7373" s="1"/>
     </row>
     <row r="7374" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7374" s="2"/>
       <c r="I7374" s="1"/>
       <c r="K7374" s="1"/>
     </row>
@@ -47740,6 +47908,7 @@
       <c r="K7377" s="1"/>
     </row>
     <row r="7378" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7378" s="2"/>
       <c r="I7378" s="1"/>
       <c r="K7378" s="1"/>
     </row>
@@ -47754,6 +47923,7 @@
       <c r="K7380" s="1"/>
     </row>
     <row r="7381" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7381" s="2"/>
       <c r="I7381" s="1"/>
       <c r="K7381" s="1"/>
     </row>
@@ -47773,10 +47943,12 @@
       <c r="K7384" s="1"/>
     </row>
     <row r="7385" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7385" s="2"/>
       <c r="I7385" s="1"/>
       <c r="K7385" s="1"/>
     </row>
     <row r="7386" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7386" s="2"/>
       <c r="I7386" s="1"/>
       <c r="K7386" s="1"/>
     </row>
@@ -47786,6 +47958,7 @@
       <c r="K7387" s="1"/>
     </row>
     <row r="7388" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7388" s="2"/>
       <c r="I7388" s="1"/>
       <c r="K7388" s="1"/>
     </row>
@@ -47796,6 +47969,7 @@
       <c r="K7389" s="1"/>
     </row>
     <row r="7390" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7390" s="2"/>
       <c r="I7390" s="1"/>
     </row>
     <row r="7391" spans="8:11" x14ac:dyDescent="0.25">
@@ -47832,7 +48006,6 @@
       <c r="I7397" s="1"/>
     </row>
     <row r="7398" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="I7398" s="1"/>
       <c r="K7398" s="1"/>
     </row>
     <row r="7399" spans="8:11" x14ac:dyDescent="0.25">
@@ -47841,6 +48014,7 @@
       <c r="K7399" s="1"/>
     </row>
     <row r="7400" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7400" s="2"/>
       <c r="I7400" s="1"/>
       <c r="K7400" s="1"/>
     </row>
@@ -47854,10 +48028,6 @@
     </row>
     <row r="7403" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7403" s="1"/>
-    </row>
-    <row r="7404" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7404" s="2"/>
-      <c r="I7404" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
